--- a/MinMax/scripts/comparison/time_totals_57.xlsx
+++ b/MinMax/scripts/comparison/time_totals_57.xlsx
@@ -46,25 +46,25 @@
     <t>Vr Vi Warm Start True</t>
   </si>
   <si>
-    <t>[1.5749199390411377, 0.7552480697631836, 0.8624560832977295, 0.7315552234649658, 1.2937049865722656, 0.8185069561004639, 0.796828031539917, 0.7551689147949219, 1.375852108001709, 1.1759231090545654, 1.7523620128631592, 1.1062920093536377, 3.9541258811950684, 0.7782590389251709, 10.775443077087402, 1.452157974243164, 1.2841229438781738, 1.8741228580474854, 1.4783649444580078, 1.7733302116394043, 2.7199490070343018, 1.382079839706421, 0.833867073059082, 0.8219490051269531, 0.9073500633239746, 0.8044939041137695, 0.8350040912628174, 0.7972939014434814, 1.2645819187164307, 2.3761959075927734, 1.311521053314209, 1.2451579570770264, 0.8749661445617676, 1.026608943939209, 1.341599941253662, 1.206157922744751, 0.8159279823303223, 0.8177158832550049, 1.4401040077209473, 0.7818920612335205, 1.4441249370574951, 1.2150580883026123, 0.8140640258789062, 3.2247371673583984, 1.4737238883972168, 1.3031690120697021, 1.0480260848999023, 0.9520611763000488, 1.6717970371246338, 2.9754979610443115, 0.9723448753356934, 1.0904998779296875, 0.7439777851104736, 1.6236650943756104, 1.374394178390503, 3.189851999282837, 0.8061208724975586, 0.7382678985595703, 0.7498130798339844, 0.9065229892730713, 0.6753449440002441, 1.810999870300293, 0.6738841533660889, 0.686939001083374, 2.3891100883483887, 1.300225019454956, 0.9036691188812256, 0.7613699436187744, 1.3140721321105957, 1.182121992111206, 0.8060719966888428, 0.8190779685974121, 0.7210249900817871, 1.2138659954071045, 1.0222091674804688, 1.16249680519104, 0.7779350280761719, 1.7656919956207275, 2.0522680282592773, 0.7620840072631836, 2.0761380195617676, 0.7855229377746582, 0.8360879421234131, 1.0521519184112549, 0.7550110816955566, 0.7476441860198975, 1.6643040180206299, 1.6431269645690918, 0.7829210758209229, 0.7490777969360352, 1.5099880695343018, 2.0358760356903076, 0.8590450286865234, 0.740847110748291, 0.866894006729126, 0.7795989513397217, 0.9763340950012207, 1.2626948356628418, 1.0906851291656494, 1.079948902130127, 0.6709229946136475, 0.8541848659515381, 2.003216028213501, 1.2670481204986572, 1.4007279872894287, 1.9633920192718506, 0.7363340854644775, 1.006890058517456, 0.712723970413208, 0.7647321224212646, 0.7360279560089111, 0.7820229530334473, 1.174232006072998, 0.789219856262207, 0.7872269153594971, 1.1457860469818115, 1.344330072402954, 0.8496408462524414, 0.8025169372558594, 2.415498971939087, 0.8466341495513916, 0.7124240398406982, 1.0791099071502686, 1.2213718891143799, 0.8165850639343262, 0.7360110282897949, 0.8211321830749512, 1.120879888534546, 2.4917640686035156, 0.8153090476989746, 0.987375020980835, 0.6935129165649414, 0.7631638050079346, 1.0970971584320068, 0.9670729637145996, 1.0227489471435547, 0.6739139556884766, 1.355381965637207, 0.648435115814209, 2.9704360961914062, 0.8154590129852295, 0.9206349849700928, 1.4288201332092285, 0.8849329948425293, 0.7740669250488281, 0.7777969837188721, 2.779555082321167, 1.6750578880310059, 0.6588749885559082, 1.134671926498413, 2.273135185241699, 0.8543570041656494, 0.7018239498138428, 1.3632631301879883, 0.7851951122283936, 0.7060480117797852, 1.0573639869689941, 0.8185620307922363, 0.7078320980072021, 0.7814998626708984, 0.7266380786895752, 0.7579391002655029, 0.7473719120025635, 0.7674980163574219, 1.2911779880523682, 1.675260066986084, 0.8064420223236084, 0.7767171859741211, 0.8018360137939453, 0.7783222198486328, 0.913398027420044, 0.9773650169372559, 0.8096389770507812, 1.5905909538269043, 1.168567180633545, 0.7184059619903564, 0.7634170055389404, 1.3749220371246338, 0.6133339405059814, 0.6211531162261963, 1.3124070167541504, 0.9185481071472168, 1.5581037998199463, 1.2378809452056885, 2.8840861320495605, 0.7461621761322021, 1.4462850093841553, 0.7726941108703613, 0.7575881481170654, 2.262294054031372, 0.8025221824645996, 1.5924088954925537, 0.9568037986755371, 0.8446040153503418, 0.8802518844604492, 1.3826329708099365, 1.043761968612671, 0.7141549587249756, 1.0061390399932861, 0.8064930438995361, 0.7857401371002197, 1.0699338912963867, 3.7561678886413574, 0.8134031295776367, 1.9257450103759766, 0.7670080661773682, 0.8442361354827881, 2.771989107131958, 1.3728771209716797, 0.7285881042480469, 2.282508134841919, 0.7215430736541748, 0.9084970951080322, 1.5685608386993408, 0.9123530387878418, 0.7612049579620361, 0.7138791084289551, 1.363968849182129, 2.7174720764160156, 1.4452450275421143, 1.0990729331970215, 0.7085649967193604, 0.821357011795044, 1.0608060359954834, 0.8228960037231445, 0.7713160514831543, 0.833975076675415, 5.471289873123169, 1.3733468055725098, 0.7819490432739258, 1.3496060371398926, 1.4413330554962158, 1.3849711418151855, 0.8472280502319336, 1.319728136062622, 0.8950669765472412, 0.8090569972991943, 1.1833510398864746, 0.9376859664916992, 1.4155988693237305, 0.8299970626831055, 0.7480669021606445, 1.1469700336456299, 0.7912709712982178, 2.454442024230957, 0.9308590888977051, 1.1013031005859375, 2.1379618644714355, 1.3098118305206299, 1.344027042388916, 0.7977361679077148, 0.9863259792327881, 0.7681479454040527, 1.1161930561065674, 0.9632480144500732, 0.6456258296966553, 1.3899259567260742, 0.9164178371429443, 2.9348278045654297, 0.81268310546875, 1.1049439907073975, 0.804326057434082, 1.534369945526123, 0.7074110507965088, 1.719139814376831, 0.7817590236663818, 2.099771022796631, 0.9949350357055664, 1.2566289901733398, 0.7107799053192139, 1.2126710414886475, 1.7509849071502686, 0.7838129997253418, 1.133147954940796, 0.6841239929199219, 0.933190107345581, 1.1822400093078613, 1.2461109161376953, 0.9921269416809082, 1.8517708778381348, 0.7851831912994385, 0.8133599758148193, 1.2524268627166748, 0.929495096206665, 1.3562700748443604, 1.3745388984680176, 0.6948800086975098, 2.397022008895874, 1.281708002090454, 1.7413079738616943, 0.8141610622406006, 1.3641350269317627, 1.0488018989562988, 1.7822730541229248, 1.456007957458496, 1.7087669372558594, 0.7754569053649902, 0.8233780860900879, 0.698422908782959, 1.2313718795776367, 0.8012220859527588, 1.5331828594207764, 0.7304990291595459, 0.7806189060211182, 1.0527358055114746, 1.049009084701538, 0.8687789440155029, 1.1074860095977783, 1.2212982177734375, 0.7743871212005615, 1.3464241027832031, 0.734644889831543, 0.9740860462188721, 0.808305025100708, 0.7684180736541748, 1.251857042312622, 0.8151228427886963, 2.4566988945007324, 0.7233791351318359, 1.252290964126587, 1.4338181018829346, 0.7514708042144775, 1.4745371341705322, 1.333085060119629, 0.8243200778961182, 0.8237979412078857, 1.5133709907531738, 1.1201140880584717, 0.8240020275115967, 3.046828031539917, 2.356126070022583, 0.8510041236877441, 0.8758730888366699, 0.8470990657806396, 0.8894062042236328, 0.8290832042694092, 0.86279296875, 1.5076649188995361, 1.8036890029907227, 1.150806188583374, 1.570173978805542, 0.7987010478973389, 1.2553000450134277, 1.2617311477661133, 3.0932159423828125, 3.888582944869995, 1.4132261276245117, 0.8041999340057373, 1.4257769584655762, 0.902209997177124, 1.0920400619506836, 0.6865301132202148, 0.8162500858306885, 1.5558559894561768, 0.8315639495849609, 2.0317440032958984, 1.9856650829315186, 0.7706189155578613, 2.7808640003204346, 0.9721620082855225, 1.626922845840454, 0.8117969036102295, 0.722027063369751, 1.0332579612731934, 1.1793549060821533, 0.7499139308929443, 1.6279430389404297, 0.8290410041809082, 0.8363320827484131, 0.7894299030303955, 1.168834924697876, 1.3781890869140625, 1.3141591548919678, 0.7610008716583252, 0.7774581909179688, 0.7113840579986572, 2.4684808254241943, 0.871877908706665, 1.272749900817871, 0.8529839515686035, 1.0809400081634521, 1.227545976638794, 1.0004348754882812, 0.837677001953125, 0.7165298461914062, 1.1897940635681152, 0.7417140007019043, 1.1372170448303223, 2.0830538272857666, 0.7298808097839355, 1.135929822921753, 2.5542569160461426, 1.361433982849121, 1.2240581512451172, 3.344318151473999, 0.8216969966888428, 0.7920751571655273, 0.7908651828765869, 0.9001507759094238, 0.784188985824585, 0.7813730239868164, 3.1705548763275146, 1.6452841758728027, 0.712090015411377, 0.8292229175567627, 0.896928071975708, 0.7834360599517822, 0.7047710418701172, 1.628511905670166, 1.0947060585021973, 0.8499960899353027, 1.098179817199707, 0.7660939693450928, 0.7297420501708984, 0.7841308116912842, 2.073086977005005, 0.8462619781494141, 1.6953818798065186, 0.8292648792266846, 0.7956640720367432, 0.8054862022399902, 1.766618013381958, 1.1737580299377441, 2.0771307945251465, 2.0861170291900635, 0.7085227966308594, 1.3543379306793213, 0.7383368015289307, 0.7940499782562256, 0.8762788772583008, 1.4774219989776611, 0.9501910209655762, 1.1835010051727295, 1.2068359851837158, 0.8330678939819336, 1.034796953201294, 1.1060831546783447, 0.9849059581756592, 0.7393100261688232, 0.8417739868164062, 1.0171608924865723, 0.8074131011962891, 2.875011920928955, 1.8700928688049316, 0.8409290313720703, 1.7297520637512207, 0.8377699851989746, 1.1518828868865967, 0.7702758312225342, 1.368082046508789, 1.134718894958496, 1.3176679611206055, 1.5503809452056885, 0.8901491165161133, 1.479029893875122, 1.4376208782196045, 1.1054728031158447, 1.648047924041748, 1.2029469013214111, 0.8643820285797119, 1.62595796585083, 0.7477350234985352, 0.7511789798736572, 0.7722749710083008, 1.3845219612121582, 1.2958650588989258, 0.8174901008605957, 1.2760369777679443, 0.6926710605621338, 1.8690259456634521, 1.7060980796813965, 1.680771827697754, 1.2662248611450195, 0.8194940090179443, 0.7561569213867188, 2.8362090587615967, 2.607253074645996, 0.8536829948425293, 1.2195169925689697, 4.619323015213013, 1.3123180866241455, 0.6774899959564209, 0.7677481174468994, 0.7446451187133789, 0.7439420223236084, 1.6459360122680664, 0.7502989768981934, 1.7580058574676514, 0.8493928909301758, 0.8143389225006104, 0.7088439464569092, 0.9037349224090576, 0.7377200126647949, 1.7349660396575928, 1.1479239463806152, 1.4381599426269531, 1.3954699039459229, 0.9489560127258301, 0.8137149810791016, 0.7485668659210205, 2.0254318714141846, 1.6124749183654785, 1.4008049964904785, 0.8163659572601318, 1.6378309726715088, 1.8135180473327637, 0.8823409080505371, 1.4683949947357178, 0.8179769515991211, 0.782397985458374, 1.544288158416748, 1.1384429931640625, 1.0983281135559082, 0.7356798648834229, 1.2243249416351318, 0.8099410533905029, 0.6747081279754639, 0.6726291179656982, 4.804159164428711, 0.8008558750152588, 1.3198461532592773, 0.804265022277832, 1.7720000743865967, 0.7716169357299805, 1.2259340286254883, 0.8325910568237305, 1.379500150680542, 1.0928289890289307, 1.89656400680542, 0.8089280128479004, 1.3264400959014893, 3.5825119018554688, 4.174883842468262, 0.7038428783416748, 0.66143798828125, 1.4519071578979492, 1.5060820579528809, 1.2521319389343262, 1.939723014831543, 0.7102491855621338, 0.7345011234283447, 1.707456111907959, 1.122838020324707, 0.7548229694366455, 0.7985210418701172, 1.8817310333251953, 0.8098368644714355, 1.1282768249511719, 2.558866024017334, 0.7285909652709961, 1.4847419261932373, 1.2854349613189697, 0.7095131874084473, 1.723897933959961, 0.7439439296722412, 1.289538860321045, 1.209460973739624, 0.8677270412445068, 1.293276071548462, 0.7146220207214355, 1.7920269966125488, 0.7798659801483154, 0.7516770362854004, 0.9332759380340576, 0.690248966217041, 0.8169329166412354, 0.8105618953704834, 0.7643768787384033, 2.226262092590332, 1.1431310176849365, 1.0111370086669922, 0.814985990524292, 0.7261300086975098, 0.7561740875244141, 0.71396803855896, 0.6699631214141846, 0.7277829647064209, 0.9656069278717041, 0.9707841873168945, 2.747359037399292, 0.7094049453735352, 1.3699629306793213, 2.7373759746551514, 0.7928850650787354, 1.674712896347046, 1.1614010334014893, 0.7573699951171875, 0.8601739406585693, 0.8022902011871338, 0.9212369918823242, 0.9253268241882324, 0.7980778217315674, 0.7514419555664062, 1.2194230556488037, 1.1607539653778076, 0.730104923248291, 0.7681639194488525, 1.3892018795013428, 2.3777198791503906, 0.7209370136260986, 0.7453200817108154, 0.7512590885162354, 2.5468151569366455, 1.256415843963623, 0.7172060012817383, 1.1841988563537598, 0.7697529792785645, 0.7883248329162598, 0.7722609043121338, 0.7499880790710449, 1.315891981124878, 0.9390602111816406, 0.8220970630645752, 0.9484560489654541, 1.3941600322723389, 1.3660259246826172, 2.4955339431762695, 1.0204429626464844, 1.8111381530761719, 2.1910059452056885, 1.4044849872589111, 2.2089030742645264, 2.884805917739868, 0.80165696144104, 1.8342840671539307, 0.7576761245727539, 1.607414960861206, 1.727139949798584, 1.3756990432739258, 0.7453699111938477, 1.2831640243530273, 1.300940990447998, 0.7225239276885986, 1.8868510723114014, 0.8293871879577637, 0.9966979026794434, 1.588667869567871, 0.7971100807189941, 0.7848649024963379, 0.6992499828338623, 1.753997802734375, 0.9020919799804688, 1.4810481071472168, 0.8417181968688965, 0.760890007019043, 0.9601008892059326, 0.7677350044250488, 1.0897550582885742, 0.736501932144165, 1.361232042312622, 3.780595064163208, 1.7461159229278564, 0.8613889217376709, 1.6569628715515137, 0.92221999168396, 0.746880054473877, 0.8489110469818115, 0.7821240425109863, 0.7355890274047852, 0.7531290054321289, 1.7640929222106934, 0.7352900505065918, 1.9482150077819824, 0.8527040481567383, 0.6611790657043457, 1.2867989540100098, 2.0817410945892334, 0.8646798133850098, 1.369978904724121, 0.7445108890533447, 0.8392150402069092, 1.0588810443878174, 1.3995192050933838, 1.1730940341949463, 0.8124978542327881, 0.832366943359375, 0.7574539184570312, 1.679049015045166, 0.7968881130218506, 1.0104870796203613, 0.7194249629974365, 1.2009708881378174, 1.0696310997009277, 1.7385239601135254, 0.8520069122314453, 0.8425178527832031, 1.620939016342163, 0.9607439041137695, 1.4675037860870361, 0.8900771141052246, 1.0242269039154053, 1.4621241092681885, 1.0104351043701172, 1.7766778469085693, 1.4194588661193848, 1.320080041885376, 1.2802009582519531, 0.9569931030273438, 1.4498100280761719, 0.8415670394897461, 0.8189918994903564, 1.3061370849609375, 2.6889920234680176, 0.7847869396209717, 2.199582099914551, 0.7519831657409668, 0.7637038230895996, 0.904670000076294, 0.8288710117340088, 1.2412619590759277, 0.8696801662445068, 1.6103549003601074, 0.7143149375915527, 0.8744909763336182, 0.8329730033874512, 0.9647600650787354, 1.328665018081665, 1.7327899932861328, 0.8296339511871338, 0.9037659168243408, 0.814215898513794, 1.2267029285430908, 0.8076071739196777, 0.8201689720153809, 0.7336950302124023, 1.5753629207611084, 0.7251009941101074, 2.248246908187866, 0.8001730442047119, 2.773047924041748, 0.8021249771118164, 0.7706289291381836, 0.7883551120758057, 1.5080740451812744, 1.2977750301361084, 1.9323148727416992, 1.307689905166626, 0.8057281970977783, 1.1908681392669678, 0.7971549034118652, 2.128196954727173, 1.1175169944763184, 1.3002660274505615, 0.936284065246582, 0.8526949882507324, 0.7685270309448242, 4.031266212463379, 0.7500061988830566, 0.8219199180603027, 0.7777400016784668, 1.3804478645324707, 0.7566928863525391, 0.6516661643981934, 0.8439700603485107, 1.0084991455078125, 2.955948829650879, 0.7754950523376465, 2.8836209774017334, 1.8332529067993164, 1.1486620903015137, 1.163020133972168, 1.289320945739746, 1.6702380180358887, 1.350165843963623, 0.8360838890075684, 0.7868049144744873, 1.4824111461639404, 1.6015350818634033, 2.133193016052246, 0.7670130729675293, 0.9541411399841309, 1.227203130722046, 0.9402649402618408, 0.915956974029541, 1.1386990547180176, 0.7987198829650879, 0.8005619049072266, 0.7397050857543945, 0.9029660224914551, 0.8012759685516357, 0.8867588043212891, 0.7883579730987549, 0.7972781658172607, 1.667698860168457, 1.3886189460754395, 1.3216710090637207, 0.6706700325012207, 0.7893850803375244, 1.409600019454956, 0.7763760089874268, 1.8470749855041504, 1.323127031326294, 0.7192130088806152, 0.7599480152130127, 1.36891508102417, 0.7646090984344482, 0.8122239112854004, 0.7870931625366211, 0.8293578624725342, 1.0365381240844727, 2.215986967086792, 0.9630951881408691, 0.7400531768798828, 2.8472859859466553, 0.7829210758209229, 1.1936321258544922, 0.7420129776000977, 0.7189619541168213, 1.4431240558624268, 1.9278531074523926, 0.7561030387878418, 2.5732901096343994, 0.795928955078125, 0.7681679725646973, 1.1169531345367432, 1.8920769691467285, 3.184746026992798, 0.7487280368804932, 1.0324599742889404, 0.7846980094909668, 0.7767629623413086, 1.5724859237670898, 0.8990750312805176, 0.8056309223175049, 4.005102157592773, 5.2782981395721436, 0.7633509635925293, 0.7527270317077637, 1.0564548969268799, 0.799562931060791, 1.3459930419921875, 0.8216609954833984, 0.9521610736846924, 0.7855391502380371, 1.4223871231079102, 1.3520879745483398, 0.8800759315490723, 0.8587589263916016, 2.300092935562134, 1.722024917602539, 1.2018070220947266, 0.6474659442901611, 0.7976968288421631, 0.757861852645874, 0.7779090404510498, 1.5079538822174072, 1.1908669471740723, 0.6377871036529541, 1.36503005027771, 0.633173942565918, 0.7563738822937012, 0.8433051109313965, 1.3322679996490479, 1.4391570091247559, 1.769906997680664, 2.0456178188323975, 1.6601200103759766, 1.3092498779296875, 1.0996201038360596, 1.2675471305847168, 5.089038133621216, 0.8433809280395508, 2.2630410194396973, 2.7084848880767822, 1.3934831619262695, 2.3173840045928955, 1.1003460884094238, 0.7694189548492432, 0.787869930267334, 1.3552730083465576, 0.7716360092163086, 1.731760025024414, 0.8686721324920654, 1.4282381534576416, 0.9201819896697998, 0.8124599456787109, 2.4064559936523438, 2.0804240703582764, 1.063661813735962, 0.767158031463623, 0.8929359912872314, 1.4975919723510742, 1.623718023300171, 1.4558470249176025, 0.8375899791717529, 1.303786039352417, 1.361649990081787, 0.7104678153991699, 0.98427414894104, 1.4564108848571777, 1.0999729633331299, 1.3415191173553467, 1.3225691318511963, 1.0796411037445068, 1.6792430877685547, 1.0316741466522217, 0.8303720951080322, 0.6889920234680176, 0.8265328407287598, 0.6243381500244141, 1.4962339401245117, 1.192060947418213, 1.0772311687469482, 0.9700789451599121, 0.7846019268035889, 1.173980951309204, 1.041666030883789, 1.3160529136657715, 0.8200938701629639, 1.8467438220977783, 0.7638711929321289, 1.180237054824829, 3.520325183868408, 1.2563190460205078, 1.0465638637542725, 1.4193098545074463, 0.7804970741271973, 1.3781981468200684, 0.8035600185394287, 1.0310518741607666, 0.695112943649292, 0.740297794342041, 0.7492938041687012, 0.7858397960662842, 1.7872300148010254, 0.7877228260040283, 2.831200122833252, 1.5560438632965088, 0.7348179817199707, 1.7536771297454834, 1.5836689472198486, 0.6925420761108398, 0.7674400806427002, 1.338413953781128, 1.0733671188354492, 0.8505218029022217, 1.7447309494018555, 1.4100310802459717, 0.9351749420166016, 0.7980589866638184, 1.6563670635223389, 1.2361741065979004, 1.5672380924224854, 0.7039129734039307, 0.7314510345458984, 1.5685558319091797, 2.953444004058838, 1.6629359722137451, 1.4623069763183594, 1.524949073791504, 0.9043121337890625, 0.8121459484100342, 3.8939049243927, 1.2845158576965332, 0.771446943283081, 0.8345811367034912, 0.760382890701294, 1.288362979888916, 2.510101079940796, 2.6891329288482666, 0.7675278186798096, 1.8430140018463135, 0.7321479320526123, 2.001107931137085, 1.5491211414337158, 1.4452948570251465, 1.8072888851165771, 1.4658820629119873, 0.8972361087799072, 0.9388790130615234, 0.949019193649292, 0.9256429672241211, 0.7872610092163086, 1.5421240329742432, 0.8180389404296875, 1.3562688827514648, 1.1634821891784668, 0.8018150329589844, 0.9266660213470459, 1.0029809474945068, 0.8023121356964111, 0.9254560470581055, 0.9561471939086914, 1.5696370601654053, 0.7077059745788574, 1.023190975189209, 1.1607179641723633, 1.208259105682373, 0.8397040367126465, 0.761138916015625, 2.6309189796447754, 2.223461866378784, 0.7993080615997314, 1.0533630847930908, 1.17405104637146, 1.7374649047851562, 1.122338056564331, 0.7537550926208496, 0.800771951675415, 1.1877338886260986]</t>
-  </si>
-  <si>
-    <t>[0.9193120002746582, 0.7374470233917236, 0.6191830635070801, 0.764927864074707, 1.0381009578704834, 0.6239738464355469, 0.6239979267120361, 0.6304800510406494, 1.0172100067138672, 0.7105081081390381, 1.0734200477600098, 0.6542840003967285, 1.0799369812011719, 0.5975148677825928, 1.1772620677947998, 1.0983760356903076, 0.9429240226745605, 1.5366530418395996, 0.8356561660766602, 0.9225468635559082, 0.902188777923584, 1.0684480667114258, 0.7407000064849854, 0.7314708232879639, 0.7036590576171875, 0.8036899566650391, 0.7187759876251221, 0.7221958637237549, 1.063283920288086, 1.0734939575195312, 1.2124741077423096, 0.8133840560913086, 0.8191289901733398, 0.8465189933776855, 1.5547878742218018, 0.729205846786499, 0.7776050567626953, 0.7561709880828857, 0.8172211647033691, 0.5923759937286377, 0.7241621017456055, 0.754727840423584, 0.7408039569854736, 1.0249488353729248, 0.8898429870605469, 0.7859268188476562, 0.6994829177856445, 0.6277670860290527, 1.1099510192871094, 0.7205021381378174, 0.7468578815460205, 0.898266077041626, 0.687514066696167, 0.6707010269165039, 0.9132869243621826, 0.9396488666534424, 0.7540609836578369, 0.8449640274047852, 0.7582290172576904, 0.8863580226898193, 0.7978770732879639, 0.9328269958496094, 0.672001838684082, 0.8823158740997314, 0.7964389324188232, 1.0859630107879639, 0.6886460781097412, 0.8877379894256592, 0.9287970066070557, 0.9806458950042725, 0.7393429279327393, 0.7714531421661377, 0.7087709903717041, 0.9994959831237793, 0.6820240020751953, 0.6435110569000244, 0.7572100162506104, 0.9758298397064209, 0.8674728870391846, 0.7428810596466064, 0.8296079635620117, 0.7105410099029541, 0.7251870632171631, 0.7818100452423096, 0.9090361595153809, 0.7816469669342041, 0.7547459602355957, 0.7412400245666504, 0.6214299201965332, 0.7055349349975586, 1.404520034790039, 0.6531438827514648, 0.860637903213501, 0.7091550827026367, 0.6716060638427734, 0.7092900276184082, 0.9333620071411133, 0.8953709602355957, 0.8497560024261475, 0.7338509559631348, 0.6682751178741455, 0.670360803604126, 1.596728801727295, 0.6976408958435059, 1.104525089263916, 0.9936151504516602, 0.628371000289917, 0.7911319732666016, 0.7524259090423584, 0.7388839721679688, 0.765056848526001, 0.6675469875335693, 1.0297610759735107, 0.6676440238952637, 0.9284329414367676, 0.7305140495300293, 0.7217519283294678, 0.6444058418273926, 0.7853960990905762, 0.7373261451721191, 0.7651848793029785, 0.7250659465789795, 0.6859791278839111, 1.2199139595031738, 0.6816391944885254, 0.8895180225372314, 0.6532580852508545, 0.6682519912719727, 1.5321199893951416, 0.7202420234680176, 0.6653800010681152, 0.7757840156555176, 0.7317769527435303, 0.8613660335540771, 0.896204948425293, 0.7308528423309326, 0.7591328620910645, 1.4167940616607666, 0.6710388660430908, 0.7158918380737305, 0.835982084274292, 0.9259858131408691, 0.8220951557159424, 0.7691130638122559, 0.9325799942016602, 0.9346821308135986, 0.8520891666412354, 0.8426260948181152, 0.6460080146789551, 0.6091341972351074, 0.7101049423217773, 0.6012029647827148, 0.8051290512084961, 0.9515480995178223, 0.7197680473327637, 0.7841260433197021, 0.8917691707611084, 0.7749249935150146, 0.8456859588623047, 0.6764020919799805, 0.7087829113006592, 0.7284832000732422, 0.7410638332366943, 0.8845710754394531, 0.6562328338623047, 0.9572880268096924, 0.8002569675445557, 0.6588468551635742, 0.8160631656646729, 0.7850508689880371, 0.7343249320983887, 0.6738760471343994, 0.7469890117645264, 0.8207981586456299, 1.3804199695587158, 0.7153708934783936, 0.7431471347808838, 0.6789040565490723, 0.6716799736022949, 0.6534380912780762, 1.036505937576294, 0.6979589462280273, 0.7267611026763916, 0.9183270931243896, 0.7281339168548584, 0.7514488697052002, 0.6836979389190674, 0.7284529209136963, 0.6334228515625, 0.6268961429595947, 0.7378411293029785, 0.8075411319732666, 0.8583571910858154, 0.9067189693450928, 0.6884281635284424, 1.524183988571167, 0.8254821300506592, 0.8328897953033447, 0.744938850402832, 0.8622341156005859, 0.7413220405578613, 0.9196970462799072, 0.8589000701904297, 0.6338109970092773, 0.8193759918212891, 0.6950337886810303, 1.064946174621582, 0.9764368534088135, 0.9645919799804688, 0.958259105682373, 1.0798239707946777, 0.6304118633270264, 0.8107051849365234, 0.9595952033996582, 0.8317620754241943, 1.0210609436035156, 0.9056229591369629, 1.0988078117370605, 1.15562105178833, 0.7187590599060059, 0.9234089851379395, 0.7738728523254395, 0.6503779888153076, 1.0627050399780273, 1.0444531440734863, 0.7887468338012695, 0.8820750713348389, 1.5706920623779297, 1.1764330863952637, 0.7400190830230713, 0.9293191432952881, 1.0396029949188232, 1.0149309635162354, 0.6332011222839355, 0.8699929714202881, 0.7306158542633057, 1.0291011333465576, 0.8048748970031738, 0.6820697784423828, 1.1146330833435059, 0.753864049911499, 0.6938550472259521, 0.9642939567565918, 0.8951938152313232, 1.0973081588745117, 0.7217669486999512, 0.9696938991546631, 1.1184051036834717, 0.7412960529327393, 0.7232909202575684, 0.7607660293579102, 0.8693718910217285, 0.7569429874420166, 0.7247400283813477, 0.7315070629119873, 0.7581899166107178, 1.0649170875549316, 0.749363899230957, 0.8764829635620117, 0.8928289413452148, 0.6759560108184814, 0.7367300987243652, 0.7174639701843262, 0.8893721103668213, 0.6966440677642822, 0.9219241142272949, 1.4454100131988525, 0.7009439468383789, 0.7377707958221436, 0.714695930480957, 0.8309288024902344, 1.2288401126861572, 0.6885149478912354, 0.7467989921569824, 0.6875560283660889, 0.9184110164642334, 0.867872953414917, 1.2052521705627441, 0.6453649997711182, 0.855402946472168, 0.9567649364471436, 0.7144091129302979, 0.7755119800567627, 0.7115788459777832, 0.9272239208221436, 0.5838770866394043, 0.7670769691467285, 1.065782070159912, 0.7278361320495605, 0.7577178478240967, 0.7388401031494141, 1.2320408821105957, 0.7359261512756348, 0.7065210342407227, 1.0568311214447021, 1.0232582092285156, 0.6986310482025146, 0.7188310623168945, 0.7104270458221436, 1.1696970462799072, 0.648629903793335, 0.9382069110870361, 0.7275609970092773, 0.6602599620819092, 1.044471025466919, 0.9484779834747314, 0.6495420932769775, 0.7755358219146729, 0.9776248931884766, 0.7669680118560791, 1.0462470054626465, 0.7812349796295166, 0.9034590721130371, 0.7583541870117188, 0.9655821323394775, 1.031554937362671, 0.757997989654541, 1.017914056777954, 0.6607320308685303, 0.9961481094360352, 0.7986080646514893, 0.7126410007476807, 0.7360339164733887, 0.9012980461120605, 0.6547229290008545, 0.6567587852478027, 1.129992961883545, 1.0295641422271729, 0.6481640338897705, 1.128504991531372, 0.7973771095275879, 0.9026639461517334, 0.670604944229126, 0.724250078201294, 0.765556812286377, 0.8427340984344482, 0.6997551918029785, 1.2038648128509521, 0.8916118144989014, 0.9403328895568848, 0.7378089427947998, 0.6169531345367432, 0.8854591846466064, 1.006141185760498, 1.0299580097198486, 1.085831880569458, 1.4234809875488281, 0.6348390579223633, 0.7158141136169434, 0.8437368869781494, 0.8530621528625488, 0.7545609474182129, 0.6930670738220215, 1.434587001800537, 0.7505810260772705, 0.7841989994049072, 1.1695640087127686, 0.7218649387359619, 1.1256940364837646, 0.7448289394378662, 1.0889809131622314, 0.7753908634185791, 0.6839618682861328, 0.7295730113983154, 1.0223150253295898, 0.6074259281158447, 1.0311639308929443, 0.9915289878845215, 0.885667085647583, 0.607140064239502, 1.0714359283447266, 1.0954749584197998, 0.7236649990081787, 1.031033992767334, 0.8062200546264648, 0.7561109066009521, 1.0635931491851807, 0.637117862701416, 0.9607460498809814, 1.0518429279327393, 1.014418125152588, 0.9961919784545898, 0.812734842300415, 0.7355139255523682, 0.6469378471374512, 1.2061901092529297, 0.7408130168914795, 1.0362370014190674, 0.7959799766540527, 0.712212085723877, 0.7026820182800293, 1.0504601001739502, 0.7200021743774414, 1.220047950744629, 1.0505669116973877, 0.9905939102172852, 0.6533689498901367, 0.7182838916778564, 0.7477900981903076, 0.9888019561767578, 0.8513970375061035, 1.165153980255127, 1.2645111083984375, 0.9122118949890137, 0.618675947189331, 0.7122209072113037, 0.6722919940948486, 0.7028758525848389, 1.1541950702667236, 0.7383019924163818, 0.7481918334960938, 1.1721980571746826, 0.6914980411529541, 0.8672008514404297, 0.9627649784088135, 1.0704889297485352, 0.6334168910980225, 0.7600090503692627, 0.757256031036377, 0.649705171585083, 0.814579963684082, 1.176326036453247, 0.8162169456481934, 0.7407917976379395, 0.7312109470367432, 0.6775979995727539, 0.991642951965332, 0.7250001430511475, 0.7660281658172607, 0.6471900939941406, 0.6370549201965332, 0.8737778663635254, 0.9020190238952637, 0.8767490386962891, 0.7454938888549805, 1.1323280334472656, 0.8036808967590332, 0.7485411167144775, 0.9051439762115479, 0.6771728992462158, 0.6877100467681885, 0.6605668067932129, 1.1821191310882568, 1.0828170776367188, 0.6522490978240967, 0.9235749244689941, 0.8185038566589355, 0.6878621578216553, 0.7139420509338379, 1.1419179439544678, 0.775036096572876, 0.7529599666595459, 0.9332730770111084, 0.652292013168335, 0.6634938716888428, 0.9324460029602051, 0.6513850688934326, 0.6229140758514404, 0.7005188465118408, 1.0366249084472656, 1.1466331481933594, 0.9047188758850098, 0.9029679298400879, 0.9482529163360596, 1.201490879058838, 1.1857049465179443, 0.7913248538970947, 0.6566450595855713, 0.7608559131622314, 0.9467329978942871, 0.7987840175628662, 1.2517530918121338, 0.7237300872802734, 0.7202057838439941, 0.708327054977417, 1.0604159832000732, 0.8106329441070557, 0.679764986038208, 0.8164620399475098, 0.7651360034942627, 0.7378280162811279, 0.9642128944396973, 0.7260749340057373, 0.7173380851745605, 0.6721899509429932, 0.987678050994873, 0.8122110366821289, 0.7275450229644775, 0.6301438808441162, 0.6545360088348389, 0.7238531112670898, 0.8794031143188477, 0.8431439399719238, 0.6688878536224365, 0.6692609786987305, 0.9032189846038818, 1.1313138008117676, 0.8383660316467285, 0.6914169788360596, 0.7408409118652344, 0.9722239971160889, 1.05489182472229, 0.9866530895233154, 0.7819781303405762, 1.0231668949127197, 1.1989459991455078, 0.7052080631256104, 1.5464670658111572, 0.6614940166473389, 0.7733480930328369, 0.7762610912322998, 0.7693209648132324, 0.7118639945983887, 0.7516031265258789, 0.6679949760437012, 0.6226139068603516, 0.709352970123291, 0.8661208152770996, 0.8645358085632324, 0.7129089832305908, 0.994765043258667, 0.6654329299926758, 0.8701519966125488, 0.7671921253204346, 0.7162308692932129, 0.7677969932556152, 0.6890089511871338, 0.9523799419403076, 0.99617600440979, 0.9710648059844971, 1.014159917831421, 1.0081040859222412, 0.9978439807891846, 0.9480800628662109, 0.7772388458251953, 0.9160220623016357, 0.6785941123962402, 0.6909949779510498, 0.7207300662994385, 0.7505240440368652, 0.7405810356140137, 0.646320104598999, 1.1349828243255615, 0.9732990264892578, 0.6721289157867432, 1.1961770057678223, 0.8621079921722412, 1.0808148384094238, 1.1947031021118164, 0.888685941696167, 0.8751318454742432, 0.8536338806152344, 0.719857931137085, 0.823800802230835, 0.7660040855407715, 0.9751589298248291, 0.6873419284820557, 0.7727041244506836, 0.6399219036102295, 0.758465051651001, 0.9261648654937744, 0.8627448081970215, 0.6950521469116211, 0.7160801887512207, 0.7030150890350342, 0.765254020690918, 0.5734679698944092, 0.9117128849029541, 0.8517379760742188, 0.971315860748291, 0.7697389125823975, 0.624208927154541, 0.7460298538208008, 0.8079259395599365, 0.7578439712524414, 0.7334599494934082, 0.7391300201416016, 0.7252159118652344, 0.6257960796356201, 0.6121890544891357, 0.7530241012573242, 1.215620994567871, 0.8505690097808838, 0.7225728034973145, 0.9512341022491455, 0.8783440589904785, 0.8044681549072266, 0.8822588920593262, 0.8926858901977539, 0.9945859909057617, 0.9588329792022705, 0.6365621089935303, 0.7244710922241211, 0.6802229881286621, 1.0735540390014648, 0.7200460433959961, 0.7157390117645264, 0.6465718746185303, 0.9361820220947266, 0.7991290092468262, 0.9657540321350098, 0.8598988056182861, 0.7177379131317139, 0.9378030300140381, 0.7569489479064941, 0.7334399223327637, 0.6845369338989258, 0.7223179340362549, 0.7204728126525879, 0.6632769107818604, 0.8473727703094482, 0.6223549842834473, 0.7548160552978516, 0.9120998382568359, 0.7185769081115723, 0.6979620456695557, 1.129654884338379, 0.9332840442657471, 1.0852370262145996, 1.302178144454956, 0.9732739925384521, 0.7797379493713379, 0.784437894821167, 0.8850438594818115, 0.6293351650238037, 0.6750640869140625, 0.6492619514465332, 1.0671088695526123, 1.1621599197387695, 0.7242250442504883, 1.0550968647003174, 0.6336288452148438, 0.727402925491333, 0.9130599498748779, 0.7667708396911621, 0.7029969692230225, 0.8165731430053711, 0.6460721492767334, 0.7027230262756348, 0.9332938194274902, 0.9640121459960938, 0.7417168617248535, 1.0701889991760254, 0.7199959754943848, 0.7139959335327148, 0.7776389122009277, 0.7296431064605713, 0.581538200378418, 0.7217481136322021, 0.915398120880127, 1.152440071105957, 1.0417799949645996, 0.67948317527771, 0.9801180362701416, 0.7486469745635986, 0.629378080368042, 0.6391539573669434, 0.6765329837799072, 0.7650058269500732, 0.9392340183258057, 1.0950100421905518, 0.8609409332275391, 0.7096800804138184, 0.7657639980316162, 0.6577548980712891, 1.1889660358428955, 0.9151058197021484, 0.704679012298584, 1.0729241371154785, 0.6645760536193848, 0.7205390930175781, 0.681488037109375, 1.4713218212127686, 0.7377009391784668, 0.7426929473876953, 0.8284671306610107, 0.8903610706329346, 0.6719508171081543, 0.7511520385742188, 0.9054501056671143, 0.7690770626068115, 0.7263967990875244, 0.8784799575805664, 0.6106908321380615, 0.7773218154907227, 0.706942081451416, 1.0765650272369385, 0.7018048763275146, 0.8259868621826172, 0.6929099559783936, 0.757957935333252, 0.8904829025268555, 0.8014512062072754, 1.0627000331878662, 0.8571631908416748, 1.462019920349121, 1.3262240886688232, 0.7171051502227783, 1.152846097946167, 1.0503439903259277, 0.7563719749450684, 0.817471981048584, 1.0809378623962402, 0.6907031536102295, 0.6768739223480225, 0.7630620002746582, 0.7705988883972168, 0.685723066329956, 0.79563307762146, 0.8101050853729248, 0.7379641532897949, 1.0797209739685059, 0.7675819396972656, 0.8770208358764648, 0.7049398422241211, 0.80013108253479, 1.0698449611663818, 0.7306358814239502, 0.7704129219055176, 0.7420990467071533, 0.6475889682769775, 0.7428970336914062, 0.699275016784668, 0.8128049373626709, 0.6787810325622559, 0.7327899932861328, 0.7796769142150879, 1.0601248741149902, 0.9921779632568359, 0.9834549427032471, 0.667820930480957, 0.7334098815917969, 0.9052948951721191, 0.7195980548858643, 1.0235118865966797, 0.7461118698120117, 1.2164452075958252, 0.6164531707763672, 1.006653070449829, 0.7820529937744141, 0.5807290077209473, 0.6559028625488281, 0.7629978656768799, 0.7388060092926025, 0.8482699394226074, 0.7673768997192383, 0.8534948825836182, 0.7127339839935303, 0.6501450538635254, 0.77115797996521, 1.072676181793213, 0.7474260330200195, 0.7660529613494873, 0.7279539108276367, 0.8309509754180908, 0.9334018230438232, 0.6672799587249756, 0.9083378314971924, 0.67498779296875, 0.6574139595031738, 0.686499834060669, 1.202544927597046, 0.860975980758667, 0.9867448806762695, 0.730172872543335, 0.9396100044250488, 0.6782150268554688, 0.7359709739685059, 1.08754301071167, 0.6423671245574951, 0.8075871467590332, 0.8330540657043457, 0.8090569972991943, 0.8066060543060303, 0.8600080013275146, 0.69293212890625, 0.7777409553527832, 0.7195110321044922, 0.6829230785369873, 0.7348120212554932, 0.7925629615783691, 0.6004209518432617, 0.7251548767089844, 1.0344619750976562, 0.8750090599060059, 1.1684699058532715, 0.7218539714813232, 0.7953979969024658, 0.8575329780578613, 0.971930980682373, 0.8219578266143799, 1.1448709964752197, 0.8653950691223145, 0.9084479808807373, 0.7756340503692627, 0.8601529598236084, 0.7301299571990967, 0.8970699310302734, 0.677232027053833, 0.7327039241790771, 0.8021070957183838, 0.6383440494537354, 0.7237460613250732, 0.8356671333312988, 0.6382589340209961, 0.9480328559875488, 0.8572039604187012, 0.8922491073608398, 0.7105021476745605, 0.7788941860198975, 0.7095561027526855, 0.6108810901641846, 0.7575199604034424, 0.7495319843292236, 1.0705678462982178, 0.810338020324707, 1.1345319747924805, 0.687230110168457, 0.8833239078521729, 0.7144598960876465, 0.6428029537200928, 0.8891739845275879, 0.721933126449585, 0.5954151153564453, 1.2585129737854004, 0.8913500308990479, 0.8192222118377686, 0.8053989410400391, 0.7150490283966064, 0.7577030658721924, 0.6636900901794434, 0.6568119525909424, 0.954226016998291, 0.9699711799621582, 0.7507858276367188, 1.0316119194030762, 0.8915979862213135, 0.7354719638824463, 0.9901280403137207, 1.210972785949707, 0.9467439651489258, 0.7390389442443848, 0.7411749362945557, 0.7729411125183105, 0.6962800025939941, 0.8534979820251465, 1.1933801174163818, 0.8057639598846436, 0.8545160293579102, 0.7579531669616699, 0.7677857875823975, 0.6207451820373535, 1.077192783355713, 1.3205130100250244, 0.7474980354309082, 1.1202011108398438, 0.7438051700592041, 0.7675480842590332, 0.7175781726837158, 0.577862024307251, 0.7106428146362305, 0.7066450119018555, 1.2437291145324707, 1.174767017364502, 0.8660538196563721, 0.984489917755127, 0.8966012001037598, 0.7108750343322754, 0.6370940208435059, 0.8011469841003418, 0.7163341045379639, 1.0316970348358154, 0.7715721130371094, 1.1644480228424072, 0.7340350151062012, 0.6419029235839844, 0.9387130737304688, 0.6794779300689697, 0.9141099452972412, 0.7082159519195557, 0.6433451175689697, 0.6168880462646484, 0.8768019676208496, 1.169175148010254, 0.9155600070953369, 0.7753660678863525, 1.0497210025787354, 0.9127838611602783, 0.9642181396484375, 1.1906311511993408, 0.8731951713562012, 0.9682180881500244, 0.6716010570526123, 0.9426100254058838, 0.6564540863037109, 0.8934459686279297, 0.7860438823699951, 0.8808088302612305, 0.7086279392242432, 0.6564939022064209, 0.7448458671569824, 0.7627160549163818, 0.7205290794372559, 0.8101370334625244, 0.982450008392334, 0.6192500591278076, 0.6769800186157227, 0.8611288070678711, 0.6472840309143066, 0.9004800319671631, 0.8053560256958008, 0.8865339756011963, 1.1270110607147217, 0.9549028873443604, 0.7466959953308105, 0.9200570583343506, 0.6754879951477051, 1.1123909950256348, 0.8912169933319092, 0.7618629932403564, 0.7865750789642334, 0.8837850093841553, 0.7109329700469971, 0.6801488399505615, 0.8147401809692383, 0.7958958148956299, 1.1441640853881836, 1.0277838706970215, 0.7201039791107178, 0.6484420299530029, 1.3350088596343994, 0.8378989696502686, 0.6626749038696289, 1.425300121307373, 0.9642319679260254, 0.9019219875335693, 1.1220829486846924, 0.9627368450164795, 0.7248630523681641, 0.8369760513305664, 0.818695068359375, 1.1773638725280762, 0.7424740791320801, 0.7254807949066162, 0.6890778541564941, 0.7116580009460449, 0.7885260581970215, 0.8879690170288086, 0.8276128768920898, 1.174994945526123, 0.7215280532836914, 0.7391459941864014, 0.900230884552002, 1.1231639385223389, 0.7711939811706543, 0.7173788547515869, 0.6710920333862305, 0.9894349575042725, 0.9652860164642334, 0.8284561634063721, 0.7888240814208984, 0.9691629409790039, 0.6872937679290771, 0.862177848815918, 0.6556360721588135, 0.8823928833007812, 1.0489399433135986, 0.7620141506195068, 0.8551690578460693, 0.6405048370361328, 0.8911030292510986, 0.7676880359649658, 0.8769791126251221, 0.8475911617279053, 0.7588589191436768, 1.042220115661621, 0.683290958404541, 0.6915850639343262, 0.766010046005249, 0.7284698486328125, 0.6202249526977539, 0.6258139610290527, 0.689777135848999, 0.8898811340332031, 0.8380470275878906, 0.6813240051269531, 0.8583829402923584, 0.8912620544433594, 0.7330179214477539, 0.7626359462738037, 1.088543176651001, 1.1125140190124512, 0.7423858642578125, 0.7226958274841309, 0.9809038639068604, 0.6999821662902832, 0.7139191627502441, 0.9205350875854492, 0.7914478778839111, 0.7892799377441406]</t>
-  </si>
-  <si>
-    <t>[0.447113037109375, 0.4751858711242676, 0.34243297576904297, 0.46933698654174805, 0.471660852432251, 0.4907550811767578, 0.4364349842071533, 0.4896719455718994, 0.4119601249694824, 0.4348599910736084, 0.46299290657043457, 0.43206787109375, 0.48618602752685547, 0.8167970180511475, 0.5201730728149414, 0.4413268566131592, 0.4296448230743408, 0.8253037929534912, 0.4027748107910156, 0.44742679595947266, 0.43062901496887207, 0.5702030658721924, 0.40106701850891113, 0.40561699867248535, 0.4731910228729248, 0.4292888641357422, 0.42714977264404297, 0.4888010025024414, 0.4357128143310547, 0.4506039619445801, 0.5300209522247314, 0.4760451316833496, 0.49533796310424805, 0.3904099464416504, 0.6291849613189697, 0.37519001960754395, 0.4575638771057129, 0.4311180114746094, 0.414776086807251, 0.7652881145477295, 0.5376420021057129, 0.4561738967895508, 0.45360302925109863, 0.4847710132598877, 0.4971327781677246, 0.47374916076660156, 0.5059859752655029, 0.3588738441467285, 0.6340889930725098, 0.46726393699645996, 0.5458569526672363, 0.4467129707336426, 0.4238090515136719, 0.5302438735961914, 0.42795896530151367, 0.407196044921875, 0.5591299533843994, 0.48552513122558594, 0.4821438789367676, 0.39795398712158203, 0.45421314239501953, 0.49648022651672363, 0.45632195472717285, 0.5369398593902588, 0.41721296310424805, 0.515977144241333, 0.6155200004577637, 0.47736191749572754, 0.467879056930542, 0.49310302734375, 0.555898904800415, 0.3907020092010498, 0.38936614990234375, 0.5439698696136475, 0.42358899116516113, 0.4188249111175537, 0.4597198963165283, 0.547637939453125, 0.3693699836730957, 0.4705851078033447, 0.46181607246398926, 0.45833778381347656, 0.5227560997009277, 0.45174598693847656, 0.4317471981048584, 0.6125929355621338, 0.4283459186553955, 0.37610316276550293, 0.4550769329071045, 0.44071006774902344, 0.565500020980835, 0.5474870204925537, 0.46762704849243164, 0.494736909866333, 0.40981101989746094, 0.4386119842529297, 0.38558197021484375, 0.49459195137023926, 0.400209903717041, 0.41663193702697754, 0.4908301830291748, 0.4539330005645752, 0.6160237789154053, 0.46758294105529785, 0.7094299793243408, 0.3847329616546631, 0.48380208015441895, 0.3500349521636963, 0.4653739929199219, 0.4947218894958496, 0.47881007194519043, 0.47110581398010254, 0.4166691303253174, 0.45452404022216797, 0.49005699157714844, 0.43095993995666504, 0.4183359146118164, 0.400468111038208, 0.47966909408569336, 0.4822671413421631, 0.4566929340362549, 0.5610179901123047, 0.47436094284057617, 0.5201928615570068, 0.5228738784790039, 0.5035500526428223, 0.43422985076904297, 0.3730008602142334, 0.6142678260803223, 0.42962193489074707, 0.484544038772583, 0.4202110767364502, 0.5114738941192627, 0.5896561145782471, 0.4932429790496826, 0.42180514335632324, 0.5242869853973389, 0.548861026763916, 0.538769006729126, 0.45157599449157715, 0.4077329635620117, 0.4535360336303711, 0.5352671146392822, 0.40720510482788086, 0.8828699588775635, 0.42127394676208496, 0.49192118644714355, 0.4090108871459961, 0.48395800590515137, 0.4081289768218994, 0.37911105155944824, 0.4909369945526123, 0.4387500286102295, 0.5164339542388916, 0.49265193939208984, 0.44602298736572266, 0.5236129760742188, 0.4343109130859375, 0.37659597396850586, 0.4760169982910156, 0.5065059661865234, 0.4808530807495117, 0.48656201362609863, 0.5053019523620605, 0.46413207054138184, 0.4279470443725586, 0.39603209495544434, 0.5459511280059814, 0.4798929691314697, 0.5536830425262451, 0.46869421005249023, 0.5216989517211914, 0.4568610191345215, 0.43964505195617676, 0.6558389663696289, 0.4380459785461426, 0.36868810653686523, 0.4182710647583008, 0.4791219234466553, 0.46411800384521484, 0.8340508937835693, 0.3884241580963135, 0.37230706214904785, 0.4413878917694092, 0.46402716636657715, 0.5131611824035645, 0.4536290168762207, 0.45978689193725586, 0.46207284927368164, 0.8676540851593018, 0.40880703926086426, 0.4874379634857178, 0.41329312324523926, 0.47818899154663086, 0.48477697372436523, 0.6200129985809326, 0.40206098556518555, 0.43898582458496094, 0.4033091068267822, 0.41961121559143066, 0.3590531349182129, 0.5244479179382324, 0.44336390495300293, 0.4876089096069336, 0.598625898361206, 0.48267412185668945, 0.4230620861053467, 0.4320640563964844, 0.4963860511779785, 0.5576510429382324, 0.48061418533325195, 0.5105588436126709, 0.39301490783691406, 0.5646340847015381, 0.4462590217590332, 0.5031039714813232, 0.4377100467681885, 0.5863430500030518, 0.5771651268005371, 0.4279451370239258, 0.440014123916626, 0.4146749973297119, 0.5337629318237305, 0.3888280391693115, 0.42237401008605957, 0.5741589069366455, 0.4567890167236328, 0.5927219390869141, 0.5252079963684082, 0.507047176361084, 0.4318830966949463, 0.6249139308929443, 0.5261731147766113, 0.4229471683502197, 0.40531206130981445, 0.4216330051422119, 0.49941396713256836, 0.4304389953613281, 0.430217981338501, 0.5539028644561768, 0.4398369789123535, 0.42284417152404785, 0.8394370079040527, 0.40735888481140137, 0.483457088470459, 0.42742085456848145, 0.45071887969970703, 0.551642894744873, 0.5155410766601562, 0.4641120433807373, 0.6087791919708252, 0.4329559803009033, 0.447786808013916, 0.49031996726989746, 0.4246189594268799, 0.4621751308441162, 0.8936948776245117, 0.5053260326385498, 0.4392549991607666, 0.5424418449401855, 0.49951601028442383, 0.5043530464172363, 0.525170087814331, 0.4914090633392334, 0.5148561000823975, 0.4574849605560303, 0.629688024520874, 0.819331169128418, 0.6517958641052246, 0.4110720157623291, 0.44055700302124023, 0.6441071033477783, 0.4275500774383545, 0.48076796531677246, 0.4834470748901367, 0.40969204902648926, 0.4874379634857178, 0.6388058662414551, 0.5121359825134277, 0.5264251232147217, 0.4884018898010254, 0.48126697540283203, 0.5175590515136719, 0.4748070240020752, 0.5319149494171143, 0.3510551452636719, 0.4766991138458252, 0.5523209571838379, 0.47413015365600586, 0.450685977935791, 0.40628480911254883, 0.6331501007080078, 0.4743638038635254, 0.441087007522583, 0.5103681087493896, 0.5477659702301025, 0.45093393325805664, 0.4339160919189453, 0.5121328830718994, 0.48751091957092285, 0.45350217819213867, 0.4303879737854004, 0.4291341304779053, 0.4454519748687744, 0.6346850395202637, 0.5298550128936768, 0.6954829692840576, 0.36480093002319336, 0.5073680877685547, 0.5239651203155518, 0.5169370174407959, 0.45487499237060547, 0.5199809074401855, 0.4409599304199219, 0.39818501472473145, 0.8096868991851807, 0.5364370346069336, 0.4506690502166748, 0.4866359233856201, 0.5503339767456055, 0.46402812004089355, 0.4477500915527344, 0.45174288749694824, 0.45252203941345215, 0.4621119499206543, 0.4615919589996338, 0.5703151226043701, 0.4593050479888916, 0.47869300842285156, 0.46358418464660645, 0.3844161033630371, 0.39391088485717773, 0.46570301055908203, 0.44336485862731934, 0.4886350631713867, 0.5255749225616455, 0.44696807861328125, 0.6795048713684082, 0.46125197410583496, 0.4708700180053711, 0.4767940044403076, 0.485522985458374, 0.5234789848327637, 0.43391895294189453, 0.5388739109039307, 0.43486785888671875, 0.7260861396789551, 0.5140149593353271, 0.3907768726348877, 0.48180294036865234, 0.4765000343322754, 0.4200410842895508, 0.48995304107666016, 0.5862441062927246, 0.5453479290008545, 0.3990190029144287, 0.5620100498199463, 0.5159509181976318, 0.4974639415740967, 0.43041300773620605, 0.7122809886932373, 0.42401814460754395, 0.4255411624908447, 0.5195989608764648, 0.6259219646453857, 0.4781179428100586, 0.48520612716674805, 0.4449648857116699, 0.3858790397644043, 0.5253269672393799, 0.5189540386199951, 0.9205601215362549, 0.4292140007019043, 0.5369720458984375, 0.42119503021240234, 0.43938112258911133, 0.37343478202819824, 0.4249899387359619, 0.42603611946105957, 0.39050912857055664, 0.48218607902526855, 0.44761180877685547, 0.41902709007263184, 0.39916396141052246, 0.4634220600128174, 0.5494778156280518, 0.4882011413574219, 0.5156080722808838, 0.38429713249206543, 0.5054540634155273, 0.43667006492614746, 0.5308201313018799, 0.4570329189300537, 0.5856060981750488, 0.4091618061065674, 0.3759171962738037, 0.5218210220336914, 0.4563760757446289, 0.48178696632385254, 0.47504520416259766, 0.454071044921875, 0.594228982925415, 0.5736908912658691, 0.4163939952850342, 0.5517940521240234, 0.47460508346557617, 0.4260730743408203, 0.5537281036376953, 0.6589350700378418, 0.5424292087554932, 0.49519896507263184, 0.46245312690734863, 0.7028400897979736, 0.5719349384307861, 0.46683216094970703, 0.4555549621582031, 0.5550189018249512, 0.5205328464508057, 0.42037200927734375, 0.5467607975006104, 0.44061279296875, 0.5223522186279297, 0.5661251544952393, 0.5009069442749023, 0.3894038200378418, 0.5535469055175781, 0.6459970474243164, 0.6214380264282227, 0.48654890060424805, 0.44078516960144043, 0.396212100982666, 0.5259959697723389, 0.4740920066833496, 0.4441709518432617, 0.49449920654296875, 0.5130019187927246, 0.4648430347442627, 0.43628406524658203, 0.5151820182800293, 0.38912105560302734, 0.4265460968017578, 0.5053949356079102, 0.6592748165130615, 0.3973979949951172, 0.5083551406860352, 0.5808160305023193, 0.48230504989624023, 0.5330958366394043, 0.5475380420684814, 0.5540399551391602, 0.4529860019683838, 0.4656379222869873, 0.4692039489746094, 0.3794100284576416, 0.39394593238830566, 0.5588181018829346, 0.3943510055541992, 0.48527097702026367, 0.4866368770599365, 0.4237101078033447, 0.5690760612487793, 0.3784909248352051, 0.43694114685058594, 0.49895691871643066, 0.6635220050811768, 0.9030559062957764, 0.41210293769836426, 0.5412280559539795, 0.470020055770874, 0.5300819873809814, 0.5375580787658691, 0.5522851943969727, 0.3981201648712158, 0.5773921012878418, 0.4990699291229248, 0.4684109687805176, 0.5527410507202148, 0.44589996337890625, 0.4911839962005615, 0.49220705032348633, 0.4883608818054199, 0.4403040409088135, 0.42423105239868164, 0.4131760597229004, 0.4227018356323242, 0.5128810405731201, 0.44875597953796387, 0.44222593307495117, 0.49254322052001953, 0.4817640781402588, 0.5777819156646729, 0.40198302268981934, 0.5000269412994385, 0.38829994201660156, 0.42239809036254883, 0.4908030033111572, 0.5802679061889648, 0.43664097785949707, 0.45876288414001465, 0.42392396926879883, 0.5680642127990723, 0.5441858768463135, 0.44394803047180176, 0.4643900394439697, 0.439594030380249, 0.5241520404815674, 0.4169020652770996, 0.6811399459838867, 0.45856380462646484, 0.42767882347106934, 0.42135190963745117, 0.407879114151001, 0.35555005073547363, 0.7183651924133301, 0.44574785232543945, 0.4804079532623291, 0.43977808952331543, 0.3820021152496338, 0.39160799980163574, 0.4623861312866211, 0.39490199089050293, 0.46135377883911133, 0.7868368625640869, 0.4009871482849121, 0.4532310962677002, 0.4537508487701416, 0.37970805168151855, 0.4089219570159912, 0.4086129665374756, 0.4486401081085205, 0.4759390354156494, 0.40124011039733887, 1.0567009449005127, 0.6827399730682373, 0.5215401649475098, 0.4282419681549072, 0.5011570453643799, 0.44407200813293457, 0.46080899238586426, 0.44559788703918457, 0.4580841064453125, 0.4212770462036133, 0.590583086013794, 0.4718141555786133, 0.4248521327972412, 0.6524519920349121, 0.5017638206481934, 0.5189199447631836, 0.8360729217529297, 0.484389066696167, 0.46184682846069336, 0.9937789440155029, 0.4401359558105469, 0.42111802101135254, 0.5465750694274902, 0.4802250862121582, 0.41584300994873047, 0.5254619121551514, 0.4119069576263428, 0.4368610382080078, 0.5289461612701416, 0.4275791645050049, 0.4595150947570801, 0.40033793449401855, 0.45768308639526367, 0.5015368461608887, 0.43869614601135254, 0.41243720054626465, 0.4474189281463623, 0.37952685356140137, 0.3873579502105713, 0.41725921630859375, 0.468386173248291, 0.4372060298919678, 0.49194908142089844, 0.5122871398925781, 0.506767988204956, 0.39040398597717285, 0.47902989387512207, 0.43084001541137695, 0.4646570682525635, 0.5311710834503174, 0.4816429615020752, 0.41986680030822754, 0.40442490577697754, 0.38672614097595215, 0.5429239273071289, 0.42549896240234375, 0.386807918548584, 0.39659714698791504, 0.43317413330078125, 0.44984912872314453, 0.5868368148803711, 0.41901302337646484, 0.45859408378601074, 0.508450984954834, 0.4015538692474365, 0.4540131092071533, 0.4858419895172119, 0.5461840629577637, 0.45380711555480957, 0.4489109516143799, 0.4693601131439209, 0.47722816467285156, 0.4908909797668457, 0.46299004554748535, 0.4564361572265625, 0.44565796852111816, 0.46239709854125977, 0.3925750255584717, 0.5170049667358398, 0.40076589584350586, 0.48798394203186035, 0.39855194091796875, 0.5089378356933594, 0.4350719451904297, 0.49444580078125, 0.3833470344543457, 0.6350269317626953, 0.6334109306335449, 0.4400901794433594, 0.3900279998779297, 0.4421260356903076, 0.45188307762145996, 0.4083831310272217, 0.46632909774780273, 0.4836461544036865, 0.6408779621124268, 0.556067943572998, 0.4450368881225586, 0.501737117767334, 0.4647800922393799, 0.4862830638885498, 0.4762740135192871, 0.5462350845336914, 0.4464881420135498, 0.4093360900878906, 0.522334098815918, 0.478687047958374, 0.544666051864624, 0.4277667999267578, 0.4659249782562256, 0.4126319885253906, 0.48894596099853516, 0.4248950481414795, 0.4815709590911865, 0.4325590133666992, 0.4350240230560303, 0.3843100070953369, 0.40070104598999023, 0.8223950862884521, 0.55942702293396, 0.3397049903869629, 0.5134320259094238, 0.48082709312438965, 0.41187596321105957, 0.4489099979400635, 0.45933103561401367, 0.5626921653747559, 0.41534900665283203, 0.37591004371643066, 0.3491220474243164, 0.4481208324432373, 0.43899106979370117, 0.5130090713500977, 0.5925741195678711, 0.5168201923370361, 0.3908529281616211, 0.46387600898742676, 0.49721598625183105, 0.38027000427246094, 0.45304393768310547, 0.5868160724639893, 0.481220006942749, 0.40152597427368164, 0.39014196395874023, 0.41551899909973145, 0.7705910205841064, 0.4576900005340576, 0.4819350242614746, 0.4961419105529785, 0.396679162979126, 0.4678030014038086, 0.3651700019836426, 0.6755318641662598, 0.5041909217834473, 0.38187599182128906, 0.4205160140991211, 0.46115708351135254, 0.44803786277770996, 0.5338950157165527, 0.8362231254577637, 0.37968993186950684, 0.5000929832458496, 0.37047314643859863, 0.6020309925079346, 0.9202568531036377, 0.44680094718933105, 0.5677549839019775, 0.38010215759277344, 0.45937395095825195, 0.38432908058166504, 0.43050408363342285, 0.47650694847106934, 0.42638492584228516, 0.42284488677978516, 0.43807387351989746, 0.5036659240722656, 0.4443070888519287, 0.512380838394165, 0.39459705352783203, 0.4403519630432129, 0.47222399711608887, 0.3659069538116455, 0.4225649833679199, 0.6309869289398193, 0.4939720630645752, 0.38802003860473633, 0.480482816696167, 0.394899845123291, 0.47595691680908203, 0.47293591499328613, 0.48577404022216797, 0.4877488613128662, 0.5000269412994385, 0.4167940616607666, 0.39612913131713867, 0.5895440578460693, 0.36577796936035156, 0.40428900718688965, 0.34365081787109375, 0.5357780456542969, 0.4558539390563965, 0.4146568775177002, 0.5112950801849365, 0.4084031581878662, 0.5762040615081787, 0.44097304344177246, 0.4796779155731201, 0.4685649871826172, 0.8928930759429932, 0.6921169757843018, 0.435535192489624, 0.4843790531158447, 0.43167901039123535, 0.40564703941345215, 0.9770119190216064, 0.4928619861602783, 0.3879730701446533, 0.5546338558197021, 0.4896399974822998, 0.47153496742248535, 0.5043070316314697, 0.3833580017089844, 0.4076981544494629, 0.492218017578125, 0.4170968532562256, 0.4290928840637207, 0.4657628536224365, 0.5080709457397461, 0.4101259708404541, 0.5316710472106934, 0.4415469169616699, 0.40100598335266113, 0.4451310634613037, 0.48282694816589355, 0.45408105850219727, 0.43830108642578125, 0.566364049911499, 0.4414980411529541, 0.42105793952941895, 0.4503328800201416, 0.7428269386291504, 0.36937904357910156, 0.5267350673675537, 0.539154052734375, 0.5101702213287354, 0.4566650390625, 0.5094780921936035, 0.4622478485107422, 0.4260270595550537, 0.5143170356750488, 0.49147987365722656, 0.47408413887023926, 0.4650390148162842, 0.5188500881195068, 0.47237491607666016, 0.40529894828796387, 0.5182058811187744, 0.4785342216491699, 0.5045249462127686, 0.5807540416717529, 0.5362541675567627, 0.5067799091339111, 0.555548906326294, 0.39458298683166504, 0.5577771663665771, 0.42983293533325195, 0.4526240825653076, 0.47245121002197266, 0.4203150272369385, 0.42803406715393066, 0.4903700351715088, 0.5257959365844727, 0.48969292640686035, 0.4447782039642334, 0.5025031566619873, 0.5059261322021484, 0.6773309707641602, 0.44119715690612793, 0.4125189781188965, 0.5338649749755859, 0.46631503105163574, 0.3585219383239746, 0.5195488929748535, 0.5024487972259521, 0.5405600070953369, 0.46516895294189453, 0.41620612144470215, 0.4499499797821045, 0.7902750968933105, 0.34139299392700195, 0.423145055770874, 0.447113037109375, 0.5132508277893066, 0.4522578716278076, 0.415330171585083, 0.4661378860473633, 0.5520341396331787, 0.45838117599487305, 0.4527139663696289, 0.46756505966186523, 0.5273928642272949, 0.4095921516418457, 0.4546501636505127, 0.4839460849761963, 0.7109699249267578, 0.5287039279937744, 0.6835548877716064, 0.6126999855041504, 0.5669221878051758, 0.4981520175933838, 0.4832141399383545, 0.5044450759887695, 0.42585015296936035, 0.45081019401550293, 0.6261320114135742, 0.5043530464172363, 0.4181370735168457, 0.3938710689544678, 0.5052599906921387, 0.4693899154663086, 0.5679361820220947, 0.5865099430084229, 0.42678380012512207, 0.5001049041748047, 0.4863710403442383, 0.4697690010070801, 0.4163799285888672, 0.46264100074768066, 0.4583439826965332, 0.42762207984924316, 0.62339186668396, 0.4896230697631836, 0.3908669948577881, 0.7262320518493652, 0.49816107749938965, 0.4703359603881836, 0.5361180305480957, 0.4527609348297119, 0.4173610210418701, 0.3636898994445801, 0.4317951202392578, 0.4199540615081787, 0.5235669612884521, 0.4689021110534668, 0.45051097869873047, 0.45357704162597656, 0.49796605110168457, 0.4460470676422119, 0.3623650074005127, 0.43326306343078613, 0.47684502601623535, 0.9048099517822266, 0.5848019123077393, 0.4669508934020996, 0.4866979122161865, 0.4566190242767334, 0.4247758388519287, 0.5386490821838379, 0.4997529983520508, 0.4115321636199951, 0.4481499195098877, 0.46982502937316895, 0.3938140869140625, 0.42711901664733887, 0.5281848907470703, 0.49049997329711914, 0.4658658504486084, 0.4715571403503418, 0.4644029140472412, 0.46776604652404785, 0.42703914642333984, 0.5424981117248535, 0.49442410469055176, 0.49159693717956543, 0.48861098289489746, 0.49482083320617676, 0.46965599060058594, 0.5515768527984619, 0.5028300285339355, 0.4795188903808594, 0.5560760498046875, 0.4105079174041748, 0.36928510665893555, 0.46074795722961426, 0.45023012161254883, 0.6372759342193604, 0.431124210357666, 0.3614227771759033, 0.4417119026184082, 0.3355369567871094, 0.44012904167175293, 0.4677598476409912, 0.4658639430999756, 0.4693479537963867, 0.6201980113983154, 0.4531428813934326, 0.4442470073699951, 0.5048708915710449, 0.6069591045379639, 0.43279099464416504, 0.47870397567749023, 0.5679879188537598, 0.40866899490356445, 0.40428996086120605, 0.4574441909790039, 0.4329371452331543, 0.45009899139404297, 0.5366368293762207, 0.9910891056060791, 0.4467201232910156, 0.35910892486572266, 0.4465811252593994, 0.39423298835754395, 0.4560208320617676, 0.4479072093963623, 0.36908984184265137, 0.4363739490509033, 0.5560770034790039, 0.453991174697876, 0.37965893745422363, 0.3861100673675537, 0.6415090560913086, 0.4171011447906494, 0.494549036026001, 0.47553205490112305, 0.4046149253845215, 0.47405290603637695, 0.46982407569885254, 0.4513380527496338, 0.38140320777893066, 0.5850961208343506, 0.46753406524658203, 0.3634929656982422, 0.5172080993652344, 0.643211841583252, 0.349668025970459, 0.4221189022064209, 0.4853169918060303, 0.4216170310974121, 0.49785900115966797, 0.4386880397796631, 0.4166419506072998, 0.46201395988464355, 0.5433619022369385, 0.4288809299468994, 0.419144868850708, 0.42641401290893555, 0.4838747978210449, 0.49551987648010254, 0.48505115509033203, 0.43576693534851074, 0.4525458812713623, 0.5773270130157471, 0.4544799327850342, 0.46825599670410156, 0.4407498836517334, 0.40424108505249023, 0.5998919010162354, 0.5627539157867432, 0.629734992980957, 0.4458189010620117, 0.5182080268859863, 0.4326169490814209, 0.40680694580078125, 0.5374100208282471, 0.48065686225891113, 0.4290139675140381, 0.7391140460968018]</t>
-  </si>
-  <si>
-    <t>[0.8229281902313232, 0.869575023651123, 1.1300280094146729, 1.4135940074920654, 1.5653889179229736, 0.8506979942321777, 0.8443679809570312, 0.8057889938354492, 1.3920819759368896, 2.4066829681396484, 4.474940061569214, 1.489048957824707, 2.926961898803711, 0.806236982345581, 8.893784046173096, 1.503587007522583, 1.3489551544189453, 1.3446309566497803, 3.5136499404907227, 1.6979758739471436, 2.0652570724487305, 2.703564167022705, 0.8277311325073242, 0.8528928756713867, 1.1380000114440918, 0.8578479290008545, 2.104340076446533, 0.7875528335571289, 1.090602159500122, 3.144695997238159, 1.310520887374878, 0.8802480697631836, 1.2967479228973389, 0.9124801158905029, 1.6554951667785645, 1.2239789962768555, 0.8431868553161621, 0.8314459323883057, 1.526839017868042, 0.829326868057251, 0.8069078922271729, 1.0467579364776611, 0.847153902053833, 1.698287010192871, 1.8133459091186523, 1.160207986831665, 0.7730591297149658, 1.060168981552124, 2.417531967163086, 1.0937840938568115, 0.8411989212036133, 0.8253860473632812, 0.7633028030395508, 0.9229269027709961, 1.8167908191680908, 1.8614308834075928, 0.7977159023284912, 0.7717399597167969, 0.7621350288391113, 1.0394480228424072, 0.8880810737609863, 0.731529951095581, 0.7519059181213379, 0.8188250064849854, 2.4579179286956787, 1.237743854522705, 0.918936014175415, 0.7561988830566406, 1.1707170009613037, 1.402345895767212, 0.8497180938720703, 0.786262035369873, 0.9125499725341797, 1.2574870586395264, 1.046949863433838, 0.7341430187225342, 0.8186430931091309, 2.2390859127044678, 0.8165569305419922, 0.8271589279174805, 1.6412761211395264, 0.8312740325927734, 0.8377010822296143, 1.2724628448486328, 0.7129449844360352, 0.8422908782958984, 1.7449619770050049, 1.208385944366455, 2.1089978218078613, 0.6838259696960449, 1.4416260719299316, 0.8585560321807861, 0.781419038772583, 0.8173260688781738, 0.9441659450531006, 0.8050191402435303, 3.3213119506835938, 1.6724767684936523, 1.192363977432251, 0.8472650051116943, 0.7586917877197266, 1.192690134048462, 2.2801458835601807, 1.1455628871917725, 2.786283016204834, 1.755640983581543, 0.7613799571990967, 1.157973051071167, 0.8153281211853027, 0.7768330574035645, 0.7651731967926025, 0.8220958709716797, 2.7465200424194336, 0.8422319889068604, 1.83768892288208, 1.4723930358886719, 0.7837679386138916, 0.8519630432128906, 0.7556829452514648, 0.8531389236450195, 0.816241979598999, 0.7683420181274414, 1.1385419368743896, 2.020656108856201, 1.5861492156982422, 0.8490188121795654, 0.8328671455383301, 1.4311599731445312, 2.014686107635498, 0.8161981105804443, 0.994441032409668, 0.8126881122589111, 0.8564260005950928, 1.0774180889129639, 0.9817049503326416, 0.9612460136413574, 2.1489999294281006, 1.4636130332946777, 0.8570809364318848, 3.1275529861450195, 0.7869420051574707, 0.9112038612365723, 1.545522928237915, 1.1224870681762695, 0.7766151428222656, 1.6355431079864502, 1.6897430419921875, 1.4155781269073486, 0.5464000701904297, 1.3539490699768066, 0.9837989807128906, 0.8230669498443604, 1.8197309970855713, 1.109717845916748, 0.8381080627441406, 0.7464981079101562, 1.5993938446044922, 0.9157159328460693, 0.741455078125, 0.9509940147399902, 0.7223989963531494, 0.7987890243530273, 0.7522799968719482, 0.7753028869628906, 1.8635101318359375, 1.6839039325714111, 0.9220330715179443, 0.7995209693908691, 1.491934061050415, 1.0386841297149658, 1.3577299118041992, 0.7363817691802979, 0.9345550537109375, 1.0320699214935303, 1.384187936782837, 0.7483510971069336, 0.8146440982818604, 1.2982778549194336, 0.6432890892028809, 1.3506112098693848, 2.4390180110931396, 0.7978310585021973, 1.205604076385498, 1.3010129928588867, 1.0499200820922852, 0.7812070846557617, 0.8379490375518799, 0.7772130966186523, 0.817781925201416, 0.8290050029754639, 2.068031072616577, 1.5259108543395996, 1.5807621479034424, 0.8158490657806396, 0.7816720008850098, 1.360267162322998, 0.7443192005157471, 0.7591979503631592, 0.8117220401763916, 0.8696520328521729, 0.8574850559234619, 1.2434089183807373, 1.4040720462799072, 0.9557368755340576, 2.42244815826416, 0.7896180152893066, 1.0244948863983154, 1.4270479679107666, 1.5255959033966064, 0.7412190437316895, 1.6430158615112305, 0.7975280284881592, 0.8842940330505371, 1.6583499908447266, 1.0295360088348389, 0.7831640243530273, 0.7970120906829834, 1.4793789386749268, 1.0703198909759521, 0.7364180088043213, 1.4672629833221436, 0.7941608428955078, 0.828481912612915, 2.949172019958496, 1.5246870517730713, 0.7952971458435059, 0.8210070133209229, 2.6883468627929688, 1.5927419662475586, 0.7563440799713135, 1.7011380195617676, 1.641038179397583, 3.457360029220581, 0.8477540016174316, 1.2808201313018799, 0.901900053024292, 0.8339941501617432, 0.7514698505401611, 2.4698281288146973, 1.4157040119171143, 0.8095710277557373, 0.7601139545440674, 0.8577880859375, 0.7856569290161133, 2.574204921722412, 0.9563639163970947, 1.3963291645050049, 1.1516101360321045, 1.2129509449005127, 1.0698981285095215, 0.8889992237091064, 0.9867091178894043, 0.7913539409637451, 1.46077299118042, 1.017124891281128, 0.8204789161682129, 1.2422847747802734, 0.9145479202270508, 0.9104399681091309, 0.8011460304260254, 0.8460550308227539, 0.8273320198059082, 0.758864164352417, 0.7353479862213135, 1.5394909381866455, 0.9189198017120361, 2.999340057373047, 0.8791611194610596, 2.3983218669891357, 0.7446489334106445, 1.4789760112762451, 1.974133014678955, 0.7573962211608887, 1.0827288627624512, 0.7385110855102539, 0.9008901119232178, 1.173576831817627, 1.1812758445739746, 0.8664679527282715, 1.6214070320129395, 0.8282430171966553, 0.8273510932922363, 3.153765916824341, 1.5609540939331055, 1.544585943222046, 1.8661820888519287, 0.767448902130127, 2.227782964706421, 0.6827099323272705, 0.8336961269378662, 0.9222769737243652, 1.5112390518188477, 0.8325459957122803, 1.7734301090240479, 2.6646339893341064, 1.3262901306152344, 0.7541348934173584, 0.8421680927276611, 0.7072679996490479, 3.0631909370422363, 0.9150300025939941, 1.4474339485168457, 0.8049111366271973, 0.9002277851104736, 1.4498422145843506, 1.1439270973205566, 0.7993040084838867, 2.037229061126709, 1.319093942642212, 0.8035540580749512, 1.2208459377288818, 0.6885740756988525, 1.0997250080108643, 0.8318150043487549, 0.7732231616973877, 1.245147943496704, 0.7646470069885254, 3.32658314704895, 1.604621171951294, 1.3001859188079834, 1.1955559253692627, 0.7283220291137695, 1.7436270713806152, 1.2461750507354736, 0.794389009475708, 0.8046479225158691, 2.3553431034088135, 1.210465908050537, 0.796328067779541, 1.3946120738983154, 0.9566829204559326, 0.9283149242401123, 0.8506429195404053, 0.819072961807251, 0.7039721012115479, 0.7419857978820801, 0.818152904510498, 1.0436909198760986, 2.0040199756622314, 2.023355007171631, 1.4150118827819824, 0.865847110748291, 1.3389530181884766, 1.131155014038086, 1.3900959491729736, 1.4945030212402344, 1.3985438346862793, 1.168125867843628, 1.5721421241760254, 0.8767809867858887, 1.5884490013122559, 0.859853982925415, 0.7720987796783447, 2.3969318866729736, 0.8484399318695068, 1.241166114807129, 1.0696570873260498, 0.7841150760650635, 1.3988020420074463, 2.1632559299468994, 2.4864509105682373, 0.7883408069610596, 0.7352330684661865, 0.6495099067687988, 2.8786098957061768, 0.9643368721008301, 1.1539027690887451, 0.7927060127258301, 0.8290369510650635, 1.8134901523590088, 1.1170239448547363, 1.2536120414733887, 0.8063240051269531, 0.7202329635620117, 0.7572708129882812, 0.7035858631134033, 1.1202020645141602, 0.7592098712921143, 1.7267489433288574, 1.0025579929351807, 3.4608020782470703, 1.1548449993133545, 0.8572430610656738, 0.7356150150299072, 0.6897988319396973, 0.9938981533050537, 0.7582828998565674, 2.717700958251953, 1.2148768901824951, 1.3363940715789795, 1.0555830001831055, 1.1266520023345947, 1.0756940841674805, 1.3196489810943604, 1.6957120895385742, 0.7420289516448975, 0.8033721446990967, 1.0666720867156982, 0.8467259407043457, 1.249539852142334, 0.7608251571655273, 1.3747401237487793, 1.3880021572113037, 0.6919479370117188, 0.7736120223999023, 0.864281177520752, 0.8074250221252441, 0.7062880992889404, 2.185032844543457, 0.6198680400848389, 0.8129799365997314, 1.0007832050323486, 1.228543996810913, 0.856132984161377, 0.7468359470367432, 1.3114850521087646, 0.8193228244781494, 0.7365951538085938, 0.7915198802947998, 0.7984049320220947, 0.7842550277709961, 1.6840999126434326, 0.6658270359039307, 0.8051228523254395, 1.5119388103485107, 0.7175850868225098, 2.952547073364258, 0.7160041332244873, 0.849931001663208, 0.8040099143981934, 1.4017930030822754, 0.9232728481292725, 1.7579431533813477, 1.761754035949707, 2.005373954772949, 1.3198809623718262, 0.7112588882446289, 0.9936127662658691, 0.7299680709838867, 0.815561056137085, 1.185258150100708, 0.7806520462036133, 2.8536219596862793, 0.9136028289794922, 0.8462100028991699, 1.7688839435577393, 0.8105688095092773, 0.7269439697265625, 0.922137975692749, 1.208801031112671, 0.8060288429260254, 0.7801220417022705, 3.522998094558716, 0.7773339748382568, 1.091623067855835, 1.4539759159088135, 1.0222361087799072, 3.1673500537872314, 1.6783850193023682, 3.1967930793762207, 1.8169608116149902, 1.1361241340637207, 1.2064869403839111, 0.731112003326416, 2.739531993865967, 1.6691391468048096, 3.4690589904785156, 0.8221838474273682, 1.0748229026794434, 1.5646181106567383, 2.5005111694335938, 2.2441070079803467, 0.9223918914794922, 0.983180046081543, 0.7109580039978027, 2.4248008728027344, 3.2655441761016846, 0.8295061588287354, 1.3040921688079834, 1.0954279899597168, 1.2862560749053955, 0.890639066696167, 0.7050020694732666, 0.7306249141693115, 1.4000239372253418, 1.5619890689849854, 0.7448070049285889, 1.2468738555908203, 0.7889418601989746, 0.7529449462890625, 0.6860690116882324, 3.110504150390625, 0.8745951652526855, 1.8210620880126953, 1.0115699768066406, 0.9514491558074951, 1.3360130786895752, 1.324617862701416, 0.8139269351959229, 0.6704750061035156, 2.6197729110717773, 1.4114570617675781, 1.4439330101013184, 0.7308118343353271, 2.305509090423584, 1.5707547664642334, 0.7588348388671875, 1.2507269382476807, 0.7824699878692627, 0.7463819980621338, 1.7082889080047607, 1.7812399864196777, 1.0972011089324951, 0.6744480133056641, 1.0872600078582764, 0.8084259033203125, 1.9611108303070068, 0.7809929847717285, 4.980141878128052, 0.7973589897155762, 1.0202720165252686, 0.9127180576324463, 1.5070240497589111, 0.6970579624176025, 0.7830088138580322, 0.8070540428161621, 0.7457661628723145, 1.0150079727172852, 3.0039708614349365, 1.7789709568023682, 1.3262879848480225, 1.2959849834442139, 3.1212620735168457, 0.7205619812011719, 0.9626069068908691, 1.4802119731903076, 1.6987688541412354, 0.9185049533843994, 0.9510970115661621, 2.7397358417510986, 0.7288479804992676, 1.6213798522949219, 1.8433830738067627, 0.8299131393432617, 0.7621471881866455, 1.1551971435546875, 0.8051681518554688, 1.4502971172332764, 1.173063039779663, 0.7978620529174805, 3.357667922973633, 1.5549380779266357, 2.4874579906463623, 0.8132870197296143, 0.7442290782928467, 1.1723289489746094, 1.56231689453125, 0.8381998538970947, 1.1939268112182617, 0.8157169818878174, 1.5346319675445557, 0.7750630378723145, 0.719074010848999, 0.9133920669555664, 0.8250679969787598, 0.8119289875030518, 0.650493860244751, 0.7072229385375977, 1.276893138885498, 1.355423927307129, 0.8183290958404541, 1.1073658466339111, 1.2833797931671143, 0.7370250225067139, 0.7795209884643555, 0.7922258377075195, 0.7218430042266846, 0.7655129432678223, 1.0015599727630615, 0.7203369140625, 0.6776549816131592, 2.688822031021118, 2.393131971359253, 0.8018970489501953, 1.210418939590454, 1.1144568920135498, 0.7549080848693848, 0.9194118976593018, 0.7944819927215576, 0.8784141540527344, 0.8576741218566895, 0.8134849071502686, 1.3558769226074219, 1.4165658950805664, 1.3149049282073975, 0.7383151054382324, 0.7530779838562012, 1.5787270069122314, 1.3066279888153076, 0.7363481521606445, 0.7597010135650635, 0.8237218856811523, 2.741586923599243, 1.5583610534667969, 0.8122239112854004, 0.6126630306243896, 0.8300797939300537, 1.1566689014434814, 0.746708869934082, 0.7043430805206299, 1.4685049057006836, 0.9404840469360352, 0.8693161010742188, 0.9289419651031494, 1.0393669605255127, 1.3106358051300049, 2.4290778636932373, 0.9321868419647217, 1.3613579273223877, 2.394021987915039, 1.6332590579986572, 1.2758219242095947, 0.7677478790283203, 0.6985759735107422, 4.891009092330933, 0.76015305519104, 0.8652939796447754, 1.7222990989685059, 2.243109941482544, 0.7982330322265625, 1.4077670574188232, 1.1074159145355225, 0.7372269630432129, 3.515886068344116, 0.8208670616149902, 0.944526195526123, 1.876338005065918, 1.500683069229126, 1.0753240585327148, 1.0905890464782715, 1.0932447910308838, 1.0365550518035889, 1.1993260383605957, 0.8183300495147705, 0.8997688293457031, 0.9494469165802002, 0.7015361785888672, 1.0042319297790527, 0.7760188579559326, 1.154608964920044, 1.1973679065704346, 1.4658420085906982, 0.8108189105987549, 1.7578039169311523, 1.4064991474151611, 0.7276840209960938, 0.8213269710540771, 0.8285870552062988, 0.8224618434906006, 0.7320690155029297, 0.987839937210083, 0.732841968536377, 2.2397868633270264, 0.7846939563751221, 1.095296859741211, 1.2139520645141602, 1.207024097442627, 0.8324480056762695, 1.2834649085998535, 0.7302069664001465, 1.3669848442077637, 1.3128740787506104, 1.2908971309661865, 1.502135992050171, 0.8689351081848145, 0.8267600536346436, 0.7284600734710693, 1.4804778099060059, 0.7548480033874512, 1.7099311351776123, 0.7166779041290283, 1.2182769775390625, 1.3209819793701172, 1.0883071422576904, 0.9260530471801758, 1.0316240787506104, 1.4552569389343262, 2.341928005218506, 1.6705150604248047, 1.1468300819396973, 1.9692821502685547, 1.564850091934204, 0.7803390026092529, 4.3265769481658936, 1.3027448654174805, 1.4035990238189697, 1.1208648681640625, 0.93868088722229, 2.905441999435425, 0.8543438911437988, 0.7656669616699219, 1.794632911682129, 1.9311327934265137, 0.8098561763763428, 1.299043893814087, 0.888037919998169, 0.8502020835876465, 1.4540328979492188, 0.7997961044311523, 1.5636701583862305, 0.6484880447387695, 1.8326880931854248, 0.8096330165863037, 1.00620698928833, 0.8534910678863525, 0.921389102935791, 2.3650760650634766, 0.7720539569854736, 0.86928391456604, 0.8812649250030518, 0.8087890148162842, 0.8284018039703369, 0.97688889503479, 0.8299498558044434, 0.6969959735870361, 1.6346471309661865, 0.851701021194458, 3.7065389156341553, 0.7772090435028076, 1.1547799110412598, 1.289146900177002, 0.8516459465026855, 0.7776379585266113, 1.2521979808807373, 1.3341920375823975, 1.332902193069458, 1.1028411388397217, 1.625560998916626, 1.0750799179077148, 0.7962019443511963, 0.7964768409729004, 1.1668009757995605, 0.7931249141693115, 0.840008020401001, 0.7236850261688232, 2.918799877166748, 1.1661598682403564, 0.7030370235443115, 0.8404629230499268, 0.6923708915710449, 1.5493040084838867, 0.8349390029907227, 0.7371189594268799, 0.8535640239715576, 0.951153039932251, 1.7688369750976562, 0.7604951858520508, 0.8313949108123779, 0.7803130149841309, 0.6381309032440186, 1.5069360733032227, 1.295720100402832, 1.2764568328857422, 1.1751270294189453, 0.7707710266113281, 0.8318967819213867, 1.0719749927520752, 1.5511510372161865, 1.4092299938201904, 0.7556290626525879, 1.589022159576416, 3.2473580837249756, 0.7652261257171631, 0.8932409286499023, 1.5944900512695312, 0.7543559074401855, 0.7409451007843018, 0.7502551078796387, 0.8976469039916992, 0.7596409320831299, 0.8567872047424316, 0.7615489959716797, 1.4788250923156738, 1.187304973602295, 1.6805989742279053, 1.5806360244750977, 0.672806978225708, 0.7713229656219482, 1.2502620220184326, 0.7202379703521729, 2.1816117763519287, 1.4138619899749756, 0.7599530220031738, 0.7968778610229492, 0.8546009063720703, 1.2329139709472656, 1.111250877380371, 0.7439608573913574, 0.8503460884094238, 0.8684401512145996, 0.8360419273376465, 0.9315199851989746, 0.7378950119018555, 1.9810161590576172, 0.7372639179229736, 1.6303341388702393, 0.8571410179138184, 0.700253963470459, 1.2400028705596924, 1.2380850315093994, 0.7568800449371338, 0.7734990119934082, 1.1862242221832275, 0.7755692005157471, 1.0677587985992432, 1.454827070236206, 1.5765819549560547, 1.1268539428710938, 0.7643241882324219, 0.7342391014099121, 1.0836551189422607, 1.5593500137329102, 0.8052921295166016, 0.7896168231964111, 7.364774942398071, 0.7199788093566895, 0.6833600997924805, 0.7865889072418213, 0.8986740112304688, 0.7529587745666504, 0.6377630233764648, 0.8294539451599121, 1.4528639316558838, 0.762030839920044, 0.7133870124816895, 3.1520729064941406, 3.333150863647461, 0.8578929901123047, 1.8307240009307861, 3.3504691123962402, 1.8669300079345703, 1.0401508808135986, 0.853234052658081, 1.2952289581298828, 0.6889121532440186, 1.6115741729736328, 1.9317901134490967, 0.7771811485290527, 1.2605171203613281, 0.7461559772491455, 0.7969329357147217, 1.4073059558868408, 2.8757271766662598, 3.012666940689087, 0.9604418277740479, 1.4216461181640625, 1.2730610370635986, 1.0538089275360107, 1.1087379455566406, 1.6265678405761719, 6.343950986862183, 0.8229739665985107, 2.2504608631134033, 1.5658059120178223, 1.413708209991455, 1.2907259464263916, 2.1858930587768555, 0.8090779781341553, 0.7784469127655029, 1.809481143951416, 0.7700738906860352, 1.5687670707702637, 1.03298020362854, 1.4773008823394775, 1.1803350448608398, 0.8272199630737305, 2.1554248332977295, 1.141097068786621, 1.5225980281829834, 0.7477619647979736, 2.2590479850769043, 0.8430719375610352, 1.454573154449463, 1.0820770263671875, 0.8065500259399414, 3.2445971965789795, 1.387416124343872, 0.7817268371582031, 0.7883141040802002, 3.0196189880371094, 1.1018309593200684, 1.4071249961853027, 0.7551670074462891, 1.3693909645080566, 1.2536420822143555, 1.1324808597564697, 0.8030481338500977, 0.7488701343536377, 0.8229711055755615, 0.9961540699005127, 1.723121166229248, 0.7917349338531494, 1.089818000793457, 0.9511799812316895, 0.8447360992431641, 0.723689079284668, 1.6777050495147705, 1.3265600204467773, 0.7919878959655762, 3.3460569381713867, 0.7671878337860107, 1.4655640125274658, 1.3920550346374512, 1.2927000522613525, 1.1311519145965576, 1.0955040454864502, 1.3600599765777588, 1.418403148651123, 0.8522849082946777, 1.034386157989502, 0.7411060333251953, 0.7676079273223877, 0.8496861457824707, 0.8105077743530273, 2.721966028213501, 0.7354450225830078, 3.244152069091797, 1.8120031356811523, 0.7592449188232422, 1.0693321228027344, 1.392637014389038, 0.8610439300537109, 0.7472500801086426, 1.2549071311950684, 1.356632947921753, 0.8947219848632812, 1.0000028610229492, 0.822998046875, 1.5886790752410889, 1.8569800853729248, 1.7189810276031494, 1.416100025177002, 1.563391923904419, 1.3455710411071777, 0.7590048313140869, 1.1338579654693604, 2.3854849338531494, 1.8621668815612793, 1.559324026107788, 1.533451795578003, 0.9064748287200928, 1.2197349071502686, 1.3636200428009033, 2.3518099784851074, 1.2920639514923096, 0.8573410511016846, 1.601072072982788, 1.237454891204834, 2.6794538497924805, 1.4732389450073242, 0.8308360576629639, 1.7243239879608154, 0.6601660251617432, 0.8667950630187988, 3.1592390537261963, 1.071314811706543, 1.3543369770050049, 2.0780818462371826, 0.8639769554138184, 0.8923740386962891, 0.8647921085357666, 0.9013957977294922, 0.8110661506652832, 1.3711988925933838, 0.831477165222168, 1.6147489547729492, 0.9719328880310059, 0.7268698215484619, 0.9801740646362305, 1.2440919876098633, 0.7649209499359131, 0.8997271060943604, 4.078489065170288, 1.7403779029846191, 0.7245831489562988, 0.8147799968719482, 0.8327059745788574, 1.139638900756836, 0.8098790645599365, 1.2484118938446045, 1.5686120986938477, 1.268686056137085, 0.9748601913452148, 1.498492956161499, 1.0958669185638428, 0.8091850280761719, 0.6977429389953613, 0.7284460067749023, 0.8099479675292969, 0.9400899410247803]</t>
-  </si>
-  <si>
-    <t>[1.0989019870758057, 1.0790588855743408, 1.1280200481414795, 1.0994210243225098, 1.0636229515075684, 0.7612481117248535, 1.1990680694580078, 0.9492909908294678, 0.8550820350646973, 1.0669028759002686, 1.074455976486206, 1.055002212524414, 1.0227439403533936, 0.8839538097381592, 0.9921479225158691, 1.0857880115509033, 1.033972978591919, 2.1467738151550293, 1.0133159160614014, 1.2064731121063232, 1.2119450569152832, 1.0227909088134766, 1.0418119430541992, 1.0958549976348877, 0.9542908668518066, 1.1028258800506592, 1.070533037185669, 1.1305341720581055, 0.8869500160217285, 0.9120979309082031, 1.0939531326293945, 1.2106969356536865, 1.0413081645965576, 0.9836220741271973, 2.148716926574707, 1.0139391422271729, 1.046494960784912, 1.0901339054107666, 1.0754108428955078, 0.7313041687011719, 1.0966010093688965, 1.097107172012329, 1.0596048831939697, 0.973268985748291, 0.9687008857727051, 1.0713419914245605, 1.0327458381652832, 1.0002050399780273, 1.2509829998016357, 0.8183879852294922, 1.1009089946746826, 1.04335618019104, 1.1140449047088623, 0.9039318561553955, 0.9159860610961914, 1.0796430110931396, 1.1633720397949219, 1.0791480541229248, 1.0957610607147217, 1.0427000522613525, 1.1787312030792236, 1.066960096359253, 1.0565791130065918, 1.109123945236206, 1.05228590965271, 0.8681669235229492, 0.9626741409301758, 1.1996221542358398, 0.8895339965820312, 0.8321750164031982, 1.045125961303711, 1.173888921737671, 1.0109879970550537, 1.188823938369751, 1.126643180847168, 0.94569993019104, 1.0750949382781982, 0.9382829666137695, 1.0677878856658936, 1.0764250755310059, 1.1330270767211914, 1.0804979801177979, 1.064774990081787, 0.9112050533294678, 1.0647039413452148, 1.1068668365478516, 1.0818572044372559, 1.0530691146850586, 1.0235090255737305, 1.175915002822876, 2.025653839111328, 0.7658178806304932, 1.0734081268310547, 1.0608940124511719, 1.0601558685302734, 1.0777161121368408, 1.129084825515747, 1.2070209980010986, 1.111994981765747, 1.1010329723358154, 1.080085039138794, 0.9252841472625732, 2.126404047012329, 1.0406830310821533, 1.0299320220947266, 1.073364019393921, 1.1324079036712646, 1.1143770217895508, 1.062319040298462, 1.0954229831695557, 1.057624101638794, 0.9435300827026367, 0.7740521430969238, 1.0832979679107666, 1.1201279163360596, 1.0755560398101807, 1.0152931213378906, 1.14394211769104, 1.0641858577728271, 1.0731971263885498, 1.068842887878418, 1.0708601474761963, 1.0036530494689941, 0.9731309413909912, 1.0869410037994385, 1.0635778903961182, 1.0750420093536377, 1.0881810188293457, 2.252997875213623, 1.1494910717010498, 1.014681100845337, 1.2113969326019287, 1.093724012374878, 1.0723249912261963, 1.1000490188598633, 1.0774948596954346, 1.0570969581604004, 1.2025091648101807, 0.8595399856567383, 1.0205349922180176, 1.0868730545043945, 1.0324609279632568, 1.3448889255523682, 1.1246719360351562, 1.0942142009735107, 1.2223050594329834, 1.2431960105895996, 1.0400629043579102, 0.9834599494934082, 1.2045538425445557, 1.078718900680542, 0.7739789485931396, 1.1678438186645508, 0.9990239143371582, 1.0461750030517578, 1.0640299320220947, 1.1737170219421387, 1.0799620151519775, 1.0893659591674805, 1.0616230964660645, 1.2089698314666748, 1.062384843826294, 1.0664210319519043, 0.9004490375518799, 1.0640199184417725, 1.0941040515899658, 1.026702880859375, 1.2058539390563965, 1.0438811779022217, 1.1014621257781982, 1.0503461360931396, 1.0468039512634277, 1.077578067779541, 0.9882872104644775, 1.119499921798706, 1.0724501609802246, 1.0220770835876465, 0.9940268993377686, 1.1423289775848389, 0.905839204788208, 0.9772870540618896, 1.17258620262146, 1.1133391857147217, 1.020211935043335, 0.7344570159912109, 1.1214969158172607, 1.0398688316345215, 1.056283950805664, 0.9007668495178223, 0.9893319606781006, 1.080336093902588, 1.2602980136871338, 0.9297299385070801, 1.2119998931884766, 1.0826919078826904, 2.0346908569335938, 1.076408863067627, 1.0958900451660156, 1.0797889232635498, 0.9772739410400391, 0.9902751445770264, 1.1168160438537598, 0.989354133605957, 1.0393080711364746, 0.973146915435791, 0.8603010177612305, 1.0969431400299072, 1.2331299781799316, 0.9499378204345703, 1.1000611782073975, 1.2444641590118408, 0.9284639358520508, 1.101059913635254, 0.9654178619384766, 1.0828230381011963, 1.0676889419555664, 1.0040969848632812, 1.0841498374938965, 1.270354986190796, 1.0894758701324463, 0.909538984298706, 0.8341009616851807, 0.884641170501709, 0.9355931282043457, 1.0761699676513672, 1.1020889282226562, 1.1569700241088867, 2.019381046295166, 1.1041719913482666, 1.200834035873413, 1.0628740787506104, 1.0771241188049316, 0.9308741092681885, 1.0649380683898926, 0.9414379596710205, 1.0832068920135498, 1.0436959266662598, 1.0712368488311768, 1.0823891162872314, 0.9733130931854248, 1.0842859745025635, 1.0651471614837646, 0.9786238670349121, 1.0347201824188232, 1.1588358879089355, 0.9737589359283447, 0.9210150241851807, 1.1034111976623535, 1.0735039710998535, 1.1445629596710205, 1.1347239017486572, 1.1056687831878662, 0.9689741134643555, 1.0932300090789795, 1.0392098426818848, 1.230086088180542, 1.0864698886871338, 1.0653629302978516, 0.9176030158996582, 1.0613899230957031, 1.0813720226287842, 1.101912021636963, 1.1678988933563232, 1.0838291645050049, 0.9311530590057373, 1.064054012298584, 1.9843809604644775, 1.035898208618164, 1.137666940689087, 1.1795129776000977, 0.9285759925842285, 1.0342590808868408, 1.0936667919158936, 1.2247810363769531, 1.06650710105896, 1.0518629550933838, 0.9300379753112793, 1.1277520656585693, 0.8731560707092285, 0.9384400844573975, 0.9326629638671875, 1.0839130878448486, 0.9349088668823242, 1.0879580974578857, 0.886436939239502, 1.1019330024719238, 1.0757429599761963, 1.0115020275115967, 1.2025620937347412, 1.0654261112213135, 1.0757739543914795, 1.0132360458374023, 1.1526739597320557, 1.0274810791015625, 1.0178470611572266, 1.3501977920532227, 1.0957551002502441, 1.0070679187774658, 1.0667848587036133, 1.088926076889038, 0.7582621574401855, 0.9905128479003906, 1.1048650741577148, 1.0571880340576172, 0.9607398509979248, 0.9913430213928223, 1.098351001739502, 1.0526227951049805, 1.2012081146240234, 1.1457481384277344, 1.1622569561004639, 1.0833179950714111, 1.05112886428833, 1.0721220970153809, 1.1510019302368164, 0.9365639686584473, 1.0785391330718994, 0.9517698287963867, 1.0928730964660645, 1.0595579147338867, 1.088866949081421, 1.167860984802246, 0.9923279285430908, 0.9594261646270752, 1.0574860572814941, 1.1615209579467773, 1.0318949222564697, 1.0523808002471924, 0.8886508941650391, 1.230638027191162, 0.9339389801025391, 1.0960819721221924, 0.9628498554229736, 1.0843918323516846, 1.073958158493042, 1.0709929466247559, 0.9685351848602295, 1.045356035232544, 1.1650879383087158, 1.0105760097503662, 1.1616520881652832, 0.9962921142578125, 0.997952938079834, 1.0422899723052979, 1.144239902496338, 0.9364709854125977, 1.8627300262451172, 1.02634596824646, 1.0494568347930908, 1.0801570415496826, 0.9950649738311768, 1.148742914199829, 1.074908971786499, 2.143746852874756, 1.2398900985717773, 1.0919630527496338, 1.0486729145050049, 1.10579514503479, 1.1691408157348633, 1.095167875289917, 1.0292160511016846, 1.1015779972076416, 1.0851850509643555, 1.1008780002593994, 1.2151060104370117, 1.149428129196167, 1.1132521629333496, 0.7519669532775879, 0.9675271511077881, 0.8553340435028076, 0.9184269905090332, 1.0659358501434326, 0.9300799369812012, 1.237004041671753, 1.184114933013916, 1.0659677982330322, 0.7651000022888184, 1.1585919857025146, 0.930178165435791, 1.1697998046875, 1.3671648502349854, 1.0380299091339111, 0.8176069259643555, 0.989569902420044, 1.0424010753631592, 1.0370500087738037, 1.1059041023254395, 1.0016729831695557, 1.1208899021148682, 1.098268985748291, 1.1116840839385986, 1.275421142578125, 1.0744960308074951, 1.1493051052093506, 1.0172240734100342, 0.679314136505127, 0.9111249446868896, 1.078287124633789, 0.9946520328521729, 0.8024539947509766, 1.105334997177124, 1.0866150856018066, 0.9512050151824951, 1.1837890148162842, 1.0203680992126465, 1.0986859798431396, 1.0558819770812988, 1.161484956741333, 1.1404712200164795, 1.073065996170044, 1.0482139587402344, 1.3858928680419922, 1.060399055480957, 1.0746400356292725, 1.1825509071350098, 1.0099501609802246, 1.0696921348571777, 1.0659070014953613, 1.0360429286956787, 1.0804789066314697, 1.0978779792785645, 0.9649219512939453, 1.0503809452056885, 1.0773358345031738, 0.6476819515228271, 1.140679121017456, 0.9411249160766602, 1.0885050296783447, 1.1213281154632568, 1.0087330341339111, 1.1835300922393799, 1.0315580368041992, 0.9505159854888916, 1.0390410423278809, 1.0781891345977783, 0.9193270206451416, 1.0859370231628418, 1.09824800491333, 1.0564649105072021, 0.7816970348358154, 0.9957871437072754, 1.0642459392547607, 1.005713939666748, 0.9698178768157959, 1.0537199974060059, 1.0817530155181885, 1.1271800994873047, 1.0934569835662842, 1.119053840637207, 1.0305190086364746, 1.0540878772735596, 1.070497989654541, 1.0638699531555176, 0.8181719779968262, 0.9900400638580322, 0.9490060806274414, 1.0811669826507568, 0.8670730590820312, 1.0307188034057617, 0.7642378807067871, 1.050025224685669, 1.065605878829956, 1.1800708770751953, 1.0767340660095215, 0.9619450569152832, 1.0616669654846191, 0.9864029884338379, 1.065108060836792, 1.0799829959869385, 1.1995508670806885, 0.922238826751709, 1.2281181812286377, 1.0970840454101562, 1.0444278717041016, 1.0813169479370117, 1.0132331848144531, 1.1843571662902832, 1.0926010608673096, 0.9388790130615234, 0.9828791618347168, 1.0822389125823975, 1.0482261180877686, 1.1404569149017334, 1.1187188625335693, 0.9252238273620605, 0.9714620113372803, 1.187877893447876, 1.0859401226043701, 0.7659111022949219, 1.0617971420288086, 1.0896389484405518, 1.0512769222259521, 1.0315449237823486, 1.0216569900512695, 0.9638659954071045, 0.9596519470214844, 0.9887759685516357, 1.0084869861602783, 0.9814391136169434, 1.0663070678710938, 1.1817131042480469, 1.1640429496765137, 0.9701259136199951, 1.0681920051574707, 0.8062710762023926, 1.0879621505737305, 1.0726749897003174, 1.117093801498413, 1.066133975982666, 1.2395598888397217, 1.0639889240264893, 1.0977089405059814, 1.111473798751831, 1.0487828254699707, 1.104647159576416, 1.0693418979644775, 1.045639991760254, 1.0202131271362305, 1.0655851364135742, 1.0708680152893066, 0.7783069610595703, 0.8949170112609863, 1.0427119731903076, 1.168008804321289, 1.230381965637207, 1.1005449295043945, 1.0205109119415283, 1.077984094619751, 1.0236799716949463, 1.0863549709320068, 0.952847957611084, 1.0527257919311523, 1.1830968856811523, 1.092616081237793, 1.0610837936401367, 1.3116881847381592, 1.0638070106506348, 1.0669169425964355, 1.0786950588226318, 1.1450250148773193, 1.0863730907440186, 1.0473620891571045, 1.0164737701416016, 1.0568370819091797, 1.0378069877624512, 1.0197551250457764, 1.080247163772583, 0.9899420738220215, 1.1743440628051758, 1.0787029266357422, 0.913909912109375, 1.0350630283355713, 1.0979721546173096, 1.1363189220428467, 1.2570850849151611, 1.0358819961547852, 0.9516270160675049, 1.0995099544525146, 1.067521095275879, 0.9529280662536621, 1.0933640003204346, 1.091068983078003, 1.0897080898284912, 1.0799109935760498, 1.0665369033813477, 1.0491998195648193, 1.03193998336792, 1.0838282108306885, 0.9923999309539795, 1.200819969177246, 1.0547630786895752, 1.0457160472869873, 1.0648019313812256, 1.2224798202514648, 1.0977251529693604, 1.1110970973968506, 1.067533016204834, 0.947376012802124, 0.8829760551452637, 0.8007597923278809, 1.055811882019043, 1.247615098953247, 1.2115578651428223, 1.081974983215332, 0.7448201179504395, 0.9882769584655762, 1.0813179016113281, 1.0553350448608398, 1.197127103805542, 1.0529999732971191, 1.05234694480896, 1.0647718906402588, 1.1943740844726562, 1.0110859870910645, 1.0052120685577393, 1.052509069442749, 1.101167917251587, 0.9770729541778564, 0.9486091136932373, 1.0549991130828857, 0.8900430202484131, 1.0402319431304932, 0.681725025177002, 0.964479923248291, 1.0676791667938232, 1.0700209140777588, 1.0647368431091309, 0.778249979019165, 1.0714111328125, 1.082170009613037, 0.8445439338684082, 0.9674899578094482, 1.0064270496368408, 1.0761499404907227, 1.0593969821929932, 1.0420901775360107, 0.9912469387054443, 0.9629430770874023, 1.0708789825439453, 1.3507411479949951, 1.0187931060791016, 1.0470690727233887, 1.0827581882476807, 1.1726408004760742, 0.9947009086608887, 1.1130878925323486, 1.0930449962615967, 1.0372488498687744, 1.2152459621429443, 1.0568628311157227, 0.9841570854187012, 1.042729139328003, 1.079906940460205, 1.130444049835205, 1.1887760162353516, 1.1344528198242188, 0.8646860122680664, 0.9614050388336182, 1.1825339794158936, 1.0772838592529297, 1.0313279628753662, 1.0641858577728271, 0.9079189300537109, 1.0798940658569336, 1.0907211303710938, 0.9164481163024902, 0.9459009170532227, 0.9172608852386475, 1.0946390628814697, 1.0108749866485596, 1.0785338878631592, 1.2471990585327148, 1.036864995956421, 1.0265259742736816, 1.050333023071289, 1.0710060596466064, 0.8998939990997314, 0.9465348720550537, 0.9507548809051514, 1.0589790344238281, 0.9731340408325195, 1.0859158039093018, 0.9001879692077637, 1.1909680366516113, 0.9410910606384277, 1.3555588722229004, 0.9997749328613281, 1.0555899143218994, 1.0908830165863037, 1.1930930614471436, 1.0370559692382812, 1.0661070346832275, 2.291851043701172, 1.102114200592041, 1.1252720355987549, 1.0582048892974854, 1.2006452083587646, 1.0239789485931396, 1.074903964996338, 1.0040130615234375, 1.1009328365325928, 1.0277090072631836, 1.2450520992279053, 0.9670298099517822, 1.056330919265747, 1.067322015762329, 0.7914788722991943, 1.0867550373077393, 1.0395290851593018, 0.9523341655731201, 0.9486501216888428, 0.8946719169616699, 1.0301728248596191, 0.8881919384002686, 0.961726188659668, 1.2407779693603516, 0.9944798946380615, 1.0615718364715576, 0.891869068145752, 0.8139948844909668, 1.0546748638153076, 1.048327922821045, 0.9055378437042236, 1.2038209438323975, 0.9645209312438965, 1.0816929340362549, 1.0599420070648193, 1.1334171295166016, 1.1070170402526855, 1.0001721382141113, 1.067072868347168, 1.1059191226959229, 1.082042932510376, 0.9708130359649658, 1.0102810859680176, 1.243298053741455, 1.0002529621124268, 0.9977848529815674, 1.0602829456329346, 1.008918046951294, 1.0857880115509033, 1.0718629360198975, 1.070930004119873, 1.0833191871643066, 1.065777063369751, 1.0217678546905518, 1.0811569690704346, 1.1021509170532227, 0.9718441963195801, 0.9967658519744873, 1.214555025100708, 1.0651869773864746, 1.0798461437225342, 1.1339430809020996, 1.125396966934204, 1.0841538906097412, 0.9791750907897949, 0.8137378692626953, 1.2130279541015625, 1.0847198963165283, 0.864901065826416, 0.9597868919372559, 1.2308599948883057, 1.093916893005371, 1.0828590393066406, 1.1213569641113281, 1.227686882019043, 1.05973219871521, 0.9646108150482178, 1.0659770965576172, 1.3108010292053223, 1.058480978012085, 1.035588026046753, 1.1496219635009766, 0.9231348037719727, 1.158797025680542, 1.0343880653381348, 1.0011329650878906, 1.0999438762664795, 0.8194451332092285, 1.0867810249328613, 1.0058059692382812, 1.0687289237976074, 1.0580461025238037, 1.0412940979003906, 1.221283197402954, 1.0654640197753906, 1.0976181030273438, 1.080881118774414, 1.144556999206543, 0.940140962600708, 0.8263990879058838, 1.0902369022369385, 1.054042100906372, 1.2587320804595947, 1.0784940719604492, 1.0887479782104492, 1.1719861030578613, 1.0687358379364014, 1.0622730255126953, 1.1243820190429688, 0.7482540607452393, 1.087296962738037, 1.0486550331115723, 0.8122758865356445, 1.2181189060211182, 1.086352825164795, 1.0911760330200195, 1.0893709659576416, 1.096092939376831, 0.8936800956726074, 1.0257651805877686, 1.121471881866455, 1.1076271533966064, 1.0927820205688477, 0.8449420928955078, 1.0793168544769287, 1.1095120906829834, 1.0698919296264648, 1.0831968784332275, 1.0277090072631836, 0.8769989013671875, 1.0791490077972412, 1.0473041534423828, 0.9391589164733887, 1.1000020503997803, 1.1618618965148926, 1.1215088367462158, 1.1259307861328125, 0.9500901699066162, 1.1481668949127197, 1.0140440464019775, 1.097146987915039, 1.058042049407959, 1.272320032119751, 1.0660021305084229, 0.9389729499816895, 1.1651391983032227, 1.0061619281768799, 1.1063528060913086, 1.1715209484100342, 1.0685880184173584, 0.7761099338531494, 0.7517337799072266, 1.1407649517059326, 0.9218130111694336, 1.099337100982666, 1.1174800395965576, 1.257908821105957, 1.1467080116271973, 1.0681469440460205, 1.0733990669250488, 1.0986409187316895, 0.9271650314331055, 1.0972111225128174, 0.9652848243713379, 1.4462270736694336, 1.1020700931549072, 1.0549700260162354, 1.2071270942687988, 1.0013110637664795, 1.0684850215911865, 1.146177053451538, 1.0510950088500977, 1.0693871974945068, 0.9106640815734863, 1.0521199703216553, 1.1272730827331543, 1.0882530212402344, 1.126878023147583, 1.1258599758148193, 1.1460380554199219, 1.018557071685791, 0.9805381298065186, 1.070915937423706, 1.1161890029907227, 1.0526950359344482, 0.9828410148620605, 1.0884490013122559, 1.216209888458252, 1.018406867980957, 1.0898759365081787, 0.9958381652832031, 1.1483590602874756, 1.2577509880065918, 1.064424991607666, 1.0789821147918701, 1.1555171012878418, 1.041795015335083, 1.1005451679229736, 1.0991160869598389, 1.0776050090789795, 1.0593369007110596, 1.0716359615325928, 1.0617239475250244, 0.8953771591186523, 1.0238149166107178, 1.0140020847320557, 1.0392570495605469, 1.0520038604736328, 0.9638431072235107, 0.946990966796875, 1.0652399063110352, 1.078261137008667, 1.130648136138916, 1.124596118927002, 1.2750561237335205, 1.079254150390625, 0.992440938949585, 0.9928188323974609, 1.01344895362854, 0.9832448959350586, 0.9749701023101807, 1.2386598587036133, 1.1424670219421387, 1.0846121311187744, 1.0808839797973633, 1.0770628452301025, 1.038506031036377, 1.0945699214935303, 1.0806920528411865, 1.0922670364379883, 1.2553768157958984, 1.098365068435669, 0.9573640823364258, 1.0750291347503662, 0.9809098243713379, 1.008131980895996, 1.0944721698760986, 1.0826621055603027, 1.223351001739502, 1.12005615234375, 1.1090338230133057, 1.041731834411621, 1.2695798873901367, 0.912916898727417, 1.0843908786773682, 1.0880489349365234, 1.1272149085998535, 1.059154987335205, 1.0743420124053955, 1.0247211456298828, 1.2678589820861816, 1.1625189781188965, 1.2504498958587646, 1.127593994140625, 1.1622099876403809, 1.0360500812530518, 1.0447280406951904, 0.9251399040222168, 1.131314992904663, 1.1316790580749512, 1.0902161598205566, 2.037385940551758, 0.6555700302124023, 0.991657018661499, 1.033005952835083, 1.2902448177337646, 1.0403468608856201, 1.1057541370391846, 1.0089361667633057, 1.089050054550171, 1.060884952545166, 1.1401560306549072, 1.0918781757354736, 1.0867021083831787, 0.8492929935455322, 1.0265800952911377, 1.0270841121673584, 1.236130952835083, 1.0973570346832275, 1.0051920413970947, 1.0256190299987793, 1.1397700309753418, 1.1116938591003418, 1.0916240215301514, 1.0232548713684082, 0.8850271701812744, 1.1617939472198486, 1.097132921218872, 1.0842809677124023, 1.1443278789520264, 1.0757339000701904, 1.1082658767700195, 1.110177993774414, 1.1050739288330078, 1.123426914215088, 0.928015947341919, 0.9700210094451904, 0.9258239269256592, 1.1235239505767822, 1.1131329536437988, 0.9708168506622314, 0.9557337760925293, 1.0839600563049316, 0.9495968818664551, 1.0788969993591309, 1.1038269996643066, 1.106942892074585, 1.1027600765228271, 1.0210418701171875, 0.9573159217834473, 0.9952929019927979, 1.0468127727508545, 1.0664279460906982, 1.1143798828125, 1.0776419639587402, 1.0310020446777344, 1.131654977798462, 1.1055748462677002, 1.050374984741211, 1.256627082824707, 1.2165000438690186, 1.0734050273895264, 1.046036958694458, 1.1389429569244385, 1.2316489219665527, 1.0983390808105469, 1.0970351696014404, 1.0970652103424072]</t>
-  </si>
-  <si>
-    <t>[0.42812108993530273, 0.5042920112609863, 0.40627193450927734, 0.5258140563964844, 0.392376184463501, 0.4688229560852051, 0.4934659004211426, 0.5094702243804932, 0.43325114250183105, 0.5117688179016113, 0.40630006790161133, 0.3909311294555664, 0.618941068649292, 0.5061078071594238, 0.5807199478149414, 0.4166901111602783, 0.47765302658081055, 0.6085329055786133, 0.37480711936950684, 0.44625401496887207, 0.4348640441894531, 0.8169760704040527, 0.36975693702697754, 0.3802039623260498, 0.42418599128723145, 0.7019519805908203, 0.44231581687927246, 0.432204008102417, 0.6335339546203613, 0.43724489212036133, 0.6720480918884277, 0.48119592666625977, 0.42615795135498047, 0.35492420196533203, 0.6937830448150635, 0.4339010715484619, 0.3730030059814453, 0.4294419288635254, 0.4866809844970703, 0.46982693672180176, 0.5241909027099609, 0.48424601554870605, 0.7295100688934326, 0.4812009334564209, 0.4404020309448242, 0.4509768486022949, 0.6143579483032227, 0.3783600330352783, 0.4602038860321045, 0.3568079471588135, 0.4599440097808838, 0.4918079376220703, 0.5009760856628418, 0.4396629333496094, 0.4154179096221924, 0.36368513107299805, 0.38005995750427246, 0.4406130313873291, 0.6040360927581787, 0.3630049228668213, 0.5007750988006592, 0.5938360691070557, 0.42632102966308594, 0.540255069732666, 0.4757208824157715, 0.4306449890136719, 0.4042088985443115, 0.4821619987487793, 0.48148298263549805, 0.5014300346374512, 0.494657039642334, 0.445220947265625, 0.38546204566955566, 0.46740007400512695, 0.5025780200958252, 0.35920000076293945, 0.4267308712005615, 0.43498897552490234, 0.3674919605255127, 0.46832799911499023, 0.6152989864349365, 0.488353967666626, 0.46000099182128906, 0.5699479579925537, 0.44492006301879883, 0.4635889530181885, 0.3975789546966553, 0.40381407737731934, 0.4217691421508789, 0.4962179660797119, 0.49167895317077637, 0.466472864151001, 0.4844191074371338, 0.4701399803161621, 0.3694419860839844, 0.5039448738098145, 0.3744659423828125, 0.5962820053100586, 0.35009312629699707, 0.517125129699707, 0.4781801700592041, 0.4442410469055176, 0.7286031246185303, 0.4233260154724121, 0.5975899696350098, 0.39795804023742676, 0.5047481060028076, 0.4845099449157715, 0.5158588886260986, 0.4731879234313965, 0.4268510341644287, 0.4709599018096924, 0.36885499954223633, 0.4999849796295166, 0.511735200881958, 0.4475209712982178, 0.41849613189697266, 0.3696579933166504, 0.47371387481689453, 0.4697999954223633, 0.4360990524291992, 0.5454208850860596, 0.4161529541015625, 0.6226880550384521, 0.45009779930114746, 0.4005749225616455, 0.4641118049621582, 0.5723850727081299, 0.5404901504516602, 0.413470983505249, 0.41508913040161133, 0.37459397315979004, 0.6001420021057129, 0.5049431324005127, 0.4470329284667969, 0.4292130470275879, 5.497116804122925, 0.5761449337005615, 0.4515550136566162, 0.4163539409637451, 0.46439099311828613, 0.3676180839538574, 0.5302720069885254, 0.4610879421234131, 0.44619083404541016, 0.39420223236083984, 0.42578601837158203, 0.4168407917022705, 0.46440815925598145, 0.45026087760925293, 0.4911320209503174, 0.44446897506713867, 0.4597890377044678, 0.4641001224517822, 0.49247288703918457, 0.538642168045044, 0.38372302055358887, 0.38050007820129395, 0.42839598655700684, 0.48835110664367676, 0.6207330226898193, 0.48722004890441895, 0.4154019355773926, 0.4861900806427002, 0.47879815101623535, 0.4016749858856201, 0.3885509967803955, 0.5141651630401611, 0.44682908058166504, 1.9207420349121094, 0.4252619743347168, 0.4922499656677246, 0.5259659290313721, 0.39455699920654297, 0.5324568748474121, 0.4304671287536621, 0.4127919673919678, 0.40033698081970215, 0.464555025100708, 0.5077559947967529, 0.4310760498046875, 0.36266207695007324, 0.427401065826416, 0.9536521434783936, 0.4347100257873535, 5.497986078262329, 0.5507969856262207, 0.4399440288543701, 0.47489190101623535, 0.4741380214691162, 0.5606420040130615, 0.4276847839355469, 0.45287108421325684, 0.48656797409057617, 0.8541381359100342, 0.6420300006866455, 0.37839508056640625, 0.4698021411895752, 0.4608180522918701, 0.35756993293762207, 0.37349796295166016, 0.4191019535064697, 0.46680593490600586, 0.47655606269836426, 0.5025432109832764, 0.4561769962310791, 0.43110013008117676, 0.41695380210876465, 0.4837310314178467, 0.5086438655853271, 0.4667937755584717, 0.4949319362640381, 0.4117288589477539, 0.49985289573669434, 0.4182398319244385, 0.49138402938842773, 0.37857604026794434, 0.5464150905609131, 0.5403721332550049, 0.5609550476074219, 0.5469129085540771, 0.5082271099090576, 0.5024359226226807, 0.3723747730255127, 0.39092016220092773, 0.47799110412597656, 0.5251460075378418, 0.6542088985443115, 0.49911999702453613, 0.42777585983276367, 0.4421100616455078, 0.5923678874969482, 0.4997408390045166, 0.4272310733795166, 0.40146398544311523, 0.42736005783081055, 0.5223062038421631, 0.4303140640258789, 0.480698823928833, 0.7558779716491699, 0.40665292739868164, 0.4628629684448242, 0.45211100578308105, 0.3823881149291992, 0.4061558246612549, 0.3850700855255127, 0.40328288078308105, 0.5092720985412598, 0.5201101303100586, 0.3910660743713379, 0.6980879306793213, 0.42727184295654297, 0.4029669761657715, 0.39014506340026855, 0.4587399959564209, 0.4422450065612793, 0.6261858940124512, 0.44521188735961914, 0.43822789192199707, 0.4253978729248047, 0.3732740879058838, 0.4559650421142578, 0.5238020420074463, 0.524014949798584, 0.40782904624938965, 0.45491504669189453, 0.5266790390014648, 0.502147912979126, 0.6379330158233643, 0.4259638786315918, 0.4306600093841553, 1.1640090942382812, 0.4110379219055176, 0.45946383476257324, 0.46735715866088867, 0.39764904975891113, 0.4153480529785156, 0.6469738483428955, 0.4883589744567871, 0.4360041618347168, 0.4008810520172119, 0.4484541416168213, 0.44620609283447266, 0.42915892601013184, 0.4269249439239502, 0.35858607292175293, 0.42740607261657715, 0.4605100154876709, 0.4530200958251953, 0.6092021465301514, 0.42543601989746094, 0.5009281635284424, 0.5941147804260254, 0.3821289539337158, 0.484544038772583, 0.8422510623931885, 0.4134101867675781, 0.4889059066772461, 0.508821964263916, 0.7049951553344727, 0.4477560520172119, 0.4355449676513672, 0.44683003425598145, 0.4349961280822754, 0.8220419883728027, 0.5480611324310303, 0.7353000640869141, 0.388685941696167, 0.5182168483734131, 0.4545300006866455, 0.5657219886779785, 0.511728048324585, 0.4616830348968506, 0.4390439987182617, 0.35895490646362305, 0.5253138542175293, 0.4747178554534912, 0.40300416946411133, 0.45958709716796875, 0.5775790214538574, 0.45493197441101074, 0.4681730270385742, 0.35015010833740234, 0.4404129981994629, 0.509505033493042, 0.4600260257720947, 0.5773398876190186, 0.45234012603759766, 0.4535200595855713, 0.4747159481048584, 0.40926694869995117, 0.43616700172424316, 0.43754005432128906, 0.56768798828125, 0.48293304443359375, 0.4794189929962158, 0.46222805976867676, 0.5645730495452881, 0.4812958240509033, 0.4207651615142822, 0.546205997467041, 0.4819800853729248, 0.4710109233856201, 0.43055295944213867, 0.7573750019073486, 0.3550529479980469, 0.6239058971405029, 0.46920108795166016, 0.43254995346069336, 0.41443300247192383, 0.4777719974517822, 0.4864058494567871, 0.47299981117248535, 0.591933012008667, 0.4369490146636963, 0.3536491394042969, 0.551826000213623, 0.42229413986206055, 0.4981958866119385, 0.45290207862854004, 0.5681560039520264, 0.43576884269714355, 0.4602060317993164, 0.530695915222168, 0.7664330005645752, 0.4676530361175537, 0.4323258399963379, 0.4107170104980469, 0.4902310371398926, 0.5842039585113525, 0.5026321411132812, 0.650540828704834, 0.3942389488220215, 0.4975168704986572, 0.4496760368347168, 0.5092349052429199, 0.3472409248352051, 0.4308488368988037, 0.39278697967529297, 0.3595149517059326, 0.44156813621520996, 0.3756089210510254, 0.3496739864349365, 0.4202420711517334, 0.5640089511871338, 0.4915440082550049, 0.46554112434387207, 0.446134090423584, 0.40828609466552734, 0.5370011329650879, 0.42698001861572266, 0.561208963394165, 0.3784620761871338, 0.5273540019989014, 0.5349500179290771, 0.35404300689697266, 0.4615190029144287, 0.4049499034881592, 0.4143099784851074, 0.5508418083190918, 0.4476339817047119, 0.7154309749603271, 0.5237538814544678, 0.4512782096862793, 0.5410919189453125, 0.35532498359680176, 0.4831058979034424, 0.46801304817199707, 0.5724139213562012, 6.478392839431763, 0.8035190105438232, 0.4531848430633545, 0.6377739906311035, 0.4862189292907715, 0.4234910011291504, 0.4139680862426758, 0.48964715003967285, 0.5862782001495361, 0.38506197929382324, 0.489501953125, 0.4608879089355469, 0.40864109992980957, 0.46754908561706543, 0.49583888053894043, 0.3693249225616455, 0.4279639720916748, 0.6629772186279297, 0.622528076171875, 0.4971590042114258, 0.36656880378723145, 0.4694850444793701, 0.4462571144104004, 0.47624802589416504, 0.43293190002441406, 0.5078299045562744, 0.43254590034484863, 0.45998382568359375, 0.38077592849731445, 0.4798409938812256, 0.395313024520874, 0.4274578094482422, 0.43741893768310547, 0.5412449836730957, 0.464367151260376, 0.4920837879180908, 0.6305789947509766, 0.37406206130981445, 0.4630908966064453, 0.468919038772583, 0.4046459197998047, 0.46391916275024414, 0.4719579219818115, 0.41002988815307617, 0.4255709648132324, 0.43780016899108887, 0.5217790603637695, 0.39128589630126953, 0.49873805046081543, 0.4095652103424072, 0.43985891342163086, 0.6123781204223633, 0.3740220069885254, 0.40405797958374023, 0.532966136932373, 0.5337650775909424, 0.4411289691925049, 0.38588500022888184, 0.44753098487854004, 0.4248208999633789, 0.537067174911499, 0.5778040885925293, 0.5346980094909668, 0.4228489398956299, 0.47564101219177246, 0.49701404571533203, 0.4665820598602295, 0.4884979724884033, 0.6386611461639404, 0.6646690368652344, 0.39992809295654297, 0.4270501136779785, 0.5076439380645752, 0.4043090343475342, 0.41176295280456543, 0.4296150207519531, 0.534743070602417, 0.5789670944213867, 0.48775410652160645, 0.5203909873962402, 0.4539320468902588, 0.49947595596313477, 0.4263269901275635, 0.5098459720611572, 0.40175485610961914, 0.4202601909637451, 0.48728299140930176, 0.6546070575714111, 0.42998504638671875, 0.3827550411224365, 0.46205997467041016, 0.5786738395690918, 0.5224020481109619, 0.45244693756103516, 0.48303914070129395, 0.364300012588501, 0.7278761863708496, 0.44751501083374023, 0.5636100769042969, 0.44142603874206543, 0.38727307319641113, 0.3660459518432617, 0.5352418422698975, 0.4221479892730713, 0.3977019786834717, 0.38995909690856934, 0.46510982513427734, 0.5691170692443848, 0.40758490562438965, 0.382037878036499, 0.530102014541626, 0.45241498947143555, 0.480349063873291, 0.532681941986084, 0.4076650142669678, 0.4082498550415039, 0.45516300201416016, 0.4085121154785156, 0.4479649066925049, 0.4021139144897461, 0.41242384910583496, 0.4392409324645996, 0.3821730613708496, 0.48427891731262207, 0.6326818466186523, 0.4803619384765625, 0.4499940872192383, 0.4022328853607178, 0.48129701614379883, 0.4824531078338623, 0.4296560287475586, 0.4260520935058594, 0.3909339904785156, 0.5411248207092285, 0.5056099891662598, 0.4360690116882324, 0.6336658000946045, 0.5180070400238037, 0.4231741428375244, 0.5525720119476318, 0.4526669979095459, 0.464263916015625, 0.6826810836791992, 0.420072078704834, 0.4507601261138916, 0.44365382194519043, 0.44786596298217773, 0.545525074005127, 0.41750192642211914, 0.37796878814697266, 0.5065531730651855, 0.4384431838989258, 0.39408111572265625, 0.4695620536804199, 0.45969390869140625, 0.41249704360961914, 0.45470118522644043, 0.4736599922180176, 0.34768104553222656, 0.6039950847625732, 0.3934600353240967, 0.4062659740447998, 0.4509720802307129, 0.4429051876068115, 0.4548320770263672, 0.6526100635528564, 0.5379068851470947, 0.5916531085968018, 0.4196469783782959, 0.4839630126953125, 0.3663790225982666, 0.45058608055114746, 0.6389269828796387, 0.4338967800140381, 0.529292106628418, 0.35231900215148926, 0.43498897552490234, 0.6509299278259277, 0.4992032051086426, 0.3558499813079834, 0.34981298446655273, 0.3630969524383545, 0.5072450637817383, 0.4757809638977051, 0.3842899799346924, 0.4380030632019043, 0.44386816024780273, 0.38742709159851074, 0.39986491203308105, 0.4319319725036621, 0.5215620994567871, 0.4035332202911377, 0.3863959312438965, 0.4445810317993164, 0.4935269355773926, 0.46995091438293457, 0.5295619964599609, 0.4508640766143799, 0.5277979373931885, 0.5465848445892334, 0.4517359733581543, 0.4811520576477051, 0.38524389266967773, 0.459259033203125, 0.4210371971130371, 0.35422396659851074, 0.4446070194244385, 0.4266700744628906, 0.3617980480194092, 0.6402158737182617, 0.47138500213623047, 0.4863560199737549, 0.3841559886932373, 0.5546469688415527, 0.4827229976654053, 0.373060941696167, 0.4356679916381836, 0.4835519790649414, 0.5674271583557129, 0.5289068222045898, 0.42757606506347656, 0.4713129997253418, 0.3970460891723633, 0.49599194526672363, 0.46517086029052734, 0.5086431503295898, 0.37048912048339844, 0.4167008399963379, 0.4733560085296631, 0.48712897300720215, 0.4999959468841553, 0.41780686378479004, 0.49289703369140625, 0.4030008316040039, 0.516110897064209, 0.4151029586791992, 0.5080609321594238, 0.3506619930267334, 0.5996592044830322, 0.4429030418395996, 0.40642309188842773, 5.837017059326172, 0.4906129837036133, 0.38965296745300293, 0.4032559394836426, 0.4752490520477295, 0.5098171234130859, 0.5769281387329102, 0.49460697174072266, 0.38223791122436523, 0.4764738082885742, 0.3814089298248291, 0.3294069766998291, 0.4336709976196289, 0.4072108268737793, 0.4546010494232178, 0.4824340343475342, 0.4570200443267822, 0.3777921199798584, 0.4796018600463867, 0.48212504386901855, 0.3732759952545166, 0.3837168216705322, 0.6103858947753906, 0.4766669273376465, 0.4276139736175537, 0.36936092376708984, 0.4105219841003418, 0.4722769260406494, 0.4423828125, 0.46409082412719727, 0.4764430522918701, 0.36939501762390137, 0.4435908794403076, 0.44582200050354004, 0.47144484519958496, 0.5046539306640625, 0.35959601402282715, 0.4769608974456787, 0.43976378440856934, 0.460968017578125, 0.44180798530578613, 0.5686469078063965, 0.3949241638183594, 0.4541480541229248, 0.3651127815246582, 0.6002378463745117, 0.6756770610809326, 0.46999502182006836, 0.514807939529419, 0.3902089595794678, 0.4526638984680176, 0.40876197814941406, 0.46248793601989746, 0.4876232147216797, 0.40677905082702637, 0.40515708923339844, 0.40729689598083496, 0.709359884262085, 0.43053388595581055, 0.47031593322753906, 0.38236403465270996, 0.41616106033325195, 0.4463989734649658, 0.40399599075317383, 0.36318206787109375, 0.3935120105743408, 0.4295811653137207, 0.37508106231689453, 0.48242902755737305, 0.41742587089538574, 0.5319840908050537, 0.4554479122161865, 0.48040008544921875, 0.47153401374816895, 0.4491109848022461, 0.6376609802246094, 0.3867471218109131, 0.5975401401519775, 0.37790703773498535, 0.3733530044555664, 0.35196805000305176, 0.38544201850891113, 0.42092204093933105, 0.4767038822174072, 0.5729720592498779, 0.41854286193847656, 0.5283908843994141, 0.40574002265930176, 0.48290395736694336, 0.450761079788208, 0.46924304962158203, 0.408966064453125, 0.5785629749298096, 0.42680883407592773, 0.47900390625, 0.4342172145843506, 0.527458906173706, 0.6856000423431396, 0.37923717498779297, 0.4680190086364746, 0.46912097930908203, 0.5156009197235107, 0.4662950038909912, 0.4112579822540283, 0.37276601791381836, 0.444904088973999, 0.37436604499816895, 0.3974878787994385, 0.478579044342041, 0.4947688579559326, 0.49132513999938965, 0.5168359279632568, 0.38700199127197266, 0.4306340217590332, 0.5932409763336182, 0.4188680648803711, 0.42467808723449707, 0.4656369686126709, 0.5772700309753418, 0.4573488235473633, 0.4139559268951416, 0.6150929927825928, 0.47348785400390625, 0.36896800994873047, 0.45501089096069336, 0.5036380290985107, 0.5152959823608398, 0.4329710006713867, 0.41966700553894043, 0.4517228603363037, 0.4447619915008545, 0.45705485343933105, 0.5182669162750244, 0.38471484184265137, 0.4263498783111572, 0.5865979194641113, 0.46456098556518555, 0.4774019718170166, 0.5185620784759521, 0.5005950927734375, 0.3877439498901367, 0.4975399971008301, 0.45416808128356934, 0.42230796813964844, 0.7262988090515137, 0.3758881092071533, 0.46233201026916504, 0.48572707176208496, 0.46666598320007324, 0.43056607246398926, 0.4174628257751465, 0.5014851093292236, 0.7635858058929443, 0.5522840023040771, 0.482896089553833, 0.4550049304962158, 0.4224281311035156, 0.4664428234100342, 0.5503120422363281, 0.5279080867767334, 0.4463181495666504, 0.48358893394470215, 0.42041683197021484, 0.36758995056152344, 0.7669539451599121, 0.4802131652832031, 0.5628840923309326, 0.4225349426269531, 0.3958170413970947, 0.4947328567504883, 0.49985694885253906, 0.491685152053833, 0.3970670700073242, 0.46468091011047363, 0.604435920715332, 0.4476900100708008, 0.4368278980255127, 0.45049500465393066, 0.4099428653717041, 0.5033719539642334, 0.44995999336242676, 0.5008809566497803, 0.4911019802093506, 0.3922238349914551, 0.4379758834838867, 0.4807090759277344, 0.45462799072265625, 0.4892559051513672, 0.7908120155334473, 0.7181539535522461, 0.5103988647460938, 0.41919803619384766, 0.49220991134643555, 0.5772910118103027, 0.4361581802368164, 0.43413591384887695, 0.5814259052276611, 0.4726850986480713, 0.615386962890625, 0.381911039352417, 0.47139811515808105, 0.47730398178100586, 0.5277619361877441, 0.7478289604187012, 0.438748836517334, 0.6323790550231934, 0.43480896949768066, 0.4584479331970215, 0.5704569816589355, 0.4197080135345459, 0.4593930244445801, 0.6707148551940918, 0.5932111740112305, 0.5608940124511719, 0.44062018394470215, 0.39629697799682617, 0.45297908782958984, 0.46270108222961426, 0.5010650157928467, 0.42154812812805176, 0.4096400737762451, 0.37368202209472656, 0.4179189205169678, 0.43646907806396484, 0.4241330623626709, 0.45297718048095703, 0.46563005447387695, 0.3637430667877197, 0.44600892066955566, 0.5730528831481934, 0.34867095947265625, 0.4498460292816162, 0.4823648929595947, 0.6604278087615967, 0.6222620010375977, 0.596203088760376, 0.48456907272338867, 0.4551270008087158, 0.4194009304046631, 0.6839470863342285, 0.4332709312438965, 0.395021915435791, 0.39518094062805176, 0.45968008041381836, 0.39434003829956055, 0.4360239505767822, 0.5873949527740479, 0.4288020133972168, 0.3742339611053467, 0.5311729907989502, 0.49512720108032227, 0.5105938911437988, 0.46111607551574707, 0.4399869441986084, 0.45048999786376953, 0.5027599334716797, 0.7393219470977783, 0.4499049186706543, 0.4173581600189209, 0.6232740879058838, 0.5108129978179932, 0.48216700553894043, 0.6136119365692139, 0.34727001190185547, 0.3779020309448242, 0.4987030029296875, 0.48948216438293457, 0.5686941146850586, 0.3667290210723877, 0.4069540500640869, 0.43836498260498047, 0.3344449996948242, 0.48580408096313477, 0.462968111038208, 0.450563907623291, 0.4631199836730957, 0.5216231346130371, 0.46152496337890625, 0.4209611415863037, 0.39383888244628906, 0.5507760047912598, 0.40457606315612793, 0.4966130256652832, 0.5799198150634766, 0.3552989959716797, 0.38013386726379395, 0.4341909885406494, 0.4133131504058838, 0.4518711566925049, 0.4514150619506836, 0.4754929542541504, 0.5893781185150146, 0.3959178924560547, 0.46115899085998535, 0.5147221088409424, 0.5055670738220215, 0.3997950553894043, 0.3756599426269531, 0.48421382904052734, 0.5531690120697021, 0.4443349838256836, 0.375093936920166, 0.3909130096435547, 0.5756680965423584, 0.4943549633026123, 0.42432403564453125, 0.42176198959350586, 0.4157881736755371, 0.4170339107513428, 0.43793606758117676, 0.4287409782409668, 0.42437005043029785, 0.7325749397277832, 0.4921882152557373, 0.34487104415893555, 0.4663848876953125, 0.6396968364715576, 0.36560988426208496, 0.41914796829223633, 0.5237290859222412, 0.44942593574523926, 0.49939393997192383, 0.38286590576171875, 0.40472912788391113, 0.42681097984313965, 0.422853946685791, 0.5043771266937256, 0.45749688148498535, 0.42903685569763184, 0.48732995986938477, 0.5212810039520264, 0.46181797981262207, 0.3831639289855957, 0.5034840106964111, 0.5078010559082031, 0.40184807777404785, 0.4838089942932129, 0.37355804443359375, 0.535315990447998, 0.5376520156860352, 0.5075368881225586, 0.6556990146636963, 0.4130110740661621, 0.6310539245605469, 0.396960973739624, 0.4275779724121094, 0.4845869541168213, 0.44050002098083496, 0.5496060848236084, 0.6179511547088623]</t>
-  </si>
-  <si>
-    <t>[0.8707997798919678, 0.6615719795227051, 0.6590831279754639, 0.7540988922119141, 1.2142610549926758, 0.5800409317016602, 0.6345679759979248, 0.6625649929046631, 0.9304819107055664, 0.658703088760376, 0.877903938293457, 0.6621050834655762, 1.2984991073608398, 0.5685520172119141, 1.3062310218811035, 0.9129929542541504, 0.8116040229797363, 1.5811669826507568, 1.0106549263000488, 1.193533182144165, 0.8368759155273438, 1.3114070892333984, 0.6840879917144775, 0.8763329982757568, 0.6724929809570312, 0.7068638801574707, 0.6638050079345703, 0.7726340293884277, 0.912714958190918, 0.8985278606414795, 1.2090590000152588, 0.6909530162811279, 0.9567348957061768, 0.6958568096160889, 1.482438087463379, 0.8936550617218018, 0.6796970367431641, 0.6642000675201416, 0.986475944519043, 0.5618021488189697, 0.6529641151428223, 0.6602270603179932, 0.705496072769165, 0.8469440937042236, 0.8523941040039062, 0.7404239177703857, 0.8271989822387695, 0.9519481658935547, 0.8091440200805664, 0.9727730751037598, 0.828361988067627, 0.6759049892425537, 0.6507778167724609, 0.6127140522003174, 0.7840068340301514, 0.7373290061950684, 0.6467359066009521, 0.6985468864440918, 0.7062170505523682, 0.6368200778961182, 0.8170030117034912, 0.9024760723114014, 0.6663639545440674, 0.7783172130584717, 0.6883039474487305, 0.9917740821838379, 0.6933639049530029, 0.7083640098571777, 0.7923941612243652, 0.8442351818084717, 0.9704158306121826, 0.6758770942687988, 0.6735780239105225, 0.8704791069030762, 0.6153700351715088, 0.8715178966522217, 0.661466121673584, 0.8135421276092529, 0.6448628902435303, 0.6773509979248047, 0.9331049919128418, 0.655911922454834, 0.6932969093322754, 0.7729439735412598, 0.8776280879974365, 0.6207358837127686, 0.668632984161377, 0.8736340999603271, 0.5523619651794434, 0.6385979652404785, 1.490185022354126, 0.6157569885253906, 0.6776728630065918, 0.6679658889770508, 0.6020328998565674, 0.6525790691375732, 0.6721107959747314, 0.9333879947662354, 0.9336819648742676, 0.7654240131378174, 0.6644260883331299, 0.6755199432373047, 1.5861999988555908, 0.6995971202850342, 0.9052901268005371, 0.9403600692749023, 0.6707439422607422, 0.9335389137268066, 0.7823340892791748, 0.6977179050445557, 0.6833100318908691, 0.6251869201660156, 0.8435420989990234, 0.7499148845672607, 0.9387269020080566, 0.6880459785461426, 0.6905961036682129, 0.6421380043029785, 0.7879951000213623, 0.6786620616912842, 0.6750640869140625, 0.7362768650054932, 0.9997439384460449, 0.9520869255065918, 0.6830739974975586, 0.7240300178527832, 0.6892330646514893, 0.7695720195770264, 1.552746057510376, 0.7640237808227539, 0.805060863494873, 0.8278110027313232, 0.6999180316925049, 0.8409550189971924, 0.8291568756103516, 0.6352860927581787, 0.6664950847625732, 1.5757288932800293, 0.6312911510467529, 0.8473479747772217, 0.7998790740966797, 0.6748631000518799, 0.8748550415039062, 0.744940996170044, 0.698267936706543, 0.6699559688568115, 0.8816440105438232, 0.6611068248748779, 0.6494059562683105, 0.9315760135650635, 0.7541890144348145, 0.6245629787445068, 0.7504429817199707, 0.888200044631958, 0.6731472015380859, 0.6563458442687988, 1.279007911682129, 0.6762311458587646, 0.7642221450805664, 0.6820528507232666, 0.6631131172180176, 0.801232099533081, 0.7199180126190186, 0.9290499687194824, 0.7072031497955322, 0.8665080070495605, 0.6414768695831299, 0.7380080223083496, 0.7828450202941895, 0.9214451313018799, 0.6746780872344971, 0.6450109481811523, 0.7248728275299072, 0.9214181900024414, 1.3755309581756592, 0.795557975769043, 0.8197638988494873, 0.6923251152038574, 0.6214039325714111, 0.6265668869018555, 0.8899340629577637, 0.9275579452514648, 0.8035399913787842, 0.8758440017700195, 0.6457359790802002, 1.0787148475646973, 0.6953330039978027, 0.6658468246459961, 0.6138589382171631, 0.5951390266418457, 1.6691901683807373, 0.7981710433959961, 0.9226489067077637, 0.9215199947357178, 0.840831995010376, 1.4590420722961426, 0.9056789875030518, 0.7632451057434082, 0.7972490787506104, 0.760706901550293, 0.7411060333251953, 0.7106139659881592, 0.7940351963043213, 0.6091921329498291, 1.1345388889312744, 0.6663680076599121, 0.9414911270141602, 0.8643331527709961, 0.8654570579528809, 0.6925339698791504, 1.0212059020996094, 0.6330158710479736, 0.7408170700073242, 0.9433329105377197, 0.685621976852417, 0.6947319507598877, 0.6583638191223145, 1.061720848083496, 1.1590869426727295, 0.6816821098327637, 0.8405799865722656, 0.6634490489959717, 0.6294350624084473, 0.9998071193695068, 0.650806188583374, 0.6930909156799316, 0.8007369041442871, 1.6755340099334717, 0.9407539367675781, 0.6916370391845703, 0.7910170555114746, 1.3236720561981201, 0.8996598720550537, 0.6466779708862305, 0.9784979820251465, 0.6549108028411865, 0.8665158748626709, 0.6920740604400635, 0.6793100833892822, 1.2997241020202637, 0.6890449523925781, 0.6447141170501709, 0.8280580043792725, 0.6539211273193359, 1.3015539646148682, 0.6633269786834717, 0.7728290557861328, 1.1495990753173828, 0.6639418601989746, 0.9838042259216309, 0.9459478855133057, 0.6714339256286621, 0.9031209945678711, 0.8294150829315186, 0.6962709426879883, 0.9290008544921875, 0.8216068744659424, 0.6631488800048828, 1.0018961429595947, 0.6914818286895752, 0.6887869834899902, 0.6943118572235107, 0.6682400703430176, 0.6805770397186279, 0.8489151000976562, 0.8817930221557617, 1.4889578819274902, 0.7181389331817627, 0.8007230758666992, 0.6964540481567383, 0.8438398838043213, 0.8401539325714111, 0.6506850719451904, 0.6959679126739502, 0.7152190208435059, 0.6601829528808594, 0.841353178024292, 1.294316053390503, 0.6327419281005859, 0.8845250606536865, 0.8031270503997803, 0.8025648593902588, 0.858971118927002, 0.7076940536499023, 0.8883740901947021, 0.6166880130767822, 0.6453421115875244, 0.9297308921813965, 0.8590641021728516, 0.6715600490570068, 0.8399038314819336, 1.2959120273590088, 0.7617721557617188, 0.6728100776672363, 0.7743799686431885, 0.9821720123291016, 0.672961950302124, 0.681394100189209, 0.6810779571533203, 0.8039140701293945, 0.6132979393005371, 0.8850760459899902, 0.6960239410400391, 0.6372220516204834, 1.1124639511108398, 0.8724269866943359, 0.6933119297027588, 0.725175142288208, 0.7873249053955078, 0.9796650409698486, 1.3384850025177002, 0.820667028427124, 0.6600720882415771, 0.6811509132385254, 0.8990349769592285, 0.9873940944671631, 0.7073719501495361, 0.8045711517333984, 0.7858378887176514, 0.8152439594268799, 0.7403099536895752, 0.6834619045257568, 0.6613559722900391, 1.0571651458740234, 0.6118738651275635, 0.6357250213623047, 1.1705131530761719, 0.8820781707763672, 0.6417520046234131, 1.2925770282745361, 0.9602370262145996, 0.7002179622650146, 0.6475470066070557, 0.6470680236816406, 0.6961350440979004, 0.7565228939056396, 0.9081621170043945, 1.1950039863586426, 0.9105739593505859, 0.9016849994659424, 0.6877977848052979, 1.0020968914031982, 0.7992010116577148, 0.6897120475769043, 1.3064677715301514, 1.0846610069274902, 1.5784990787506104, 0.6061670780181885, 0.7707831859588623, 0.6745579242706299, 0.8069097995758057, 0.6897389888763428, 0.6690068244934082, 1.4832978248596191, 0.8290090560913086, 0.8577718734741211, 1.2896530628204346, 0.8033440113067627, 0.8174891471862793, 0.7780971527099609, 1.2378771305084229, 0.7040190696716309, 0.6159169673919678, 0.838716983795166, 0.9120850563049316, 0.5982091426849365, 0.7468879222869873, 0.6752791404724121, 0.6624851226806641, 0.5935380458831787, 0.8100671768188477, 1.1718971729278564, 0.6310651302337646, 0.7771079540252686, 0.789665937423706, 0.6942248344421387, 0.9758858680725098, 0.5900349617004395, 0.7510008811950684, 0.895482063293457, 0.9774808883666992, 0.9585909843444824, 0.677264928817749, 0.6959919929504395, 0.7541730403900146, 1.33113694190979, 0.7892029285430908, 0.798612117767334, 0.8330650329589844, 0.6388058662414551, 0.6657650470733643, 1.269232988357544, 0.6782059669494629, 1.0723011493682861, 0.9093410968780518, 1.0379538536071777, 0.6043779850006104, 0.6801319122314453, 0.7815439701080322, 0.9703259468078613, 0.9409489631652832, 1.3168830871582031, 1.3174278736114502, 0.7487578392028809, 0.7272648811340332, 0.6772890090942383, 0.6876189708709717, 0.6726150512695312, 1.1301279067993164, 0.9750769138336182, 0.6876318454742432, 0.9057230949401855, 0.6858792304992676, 0.671964168548584, 0.6681969165802002, 0.9841511249542236, 0.6579349040985107, 0.6345181465148926, 0.6880137920379639, 0.6397700309753418, 0.715062141418457, 0.8547120094299316, 0.7283868789672852, 0.6441709995269775, 0.9599368572235107, 0.7523610591888428, 0.9159848690032959, 0.7642941474914551, 0.827455997467041, 0.6220500469207764, 0.6973979473114014, 0.6701161861419678, 0.7363040447235107, 1.0149171352386475, 0.6946320533752441, 0.9765570163726807, 0.6639299392700195, 0.8508059978485107, 0.6610519886016846, 0.6663539409637451, 0.7621588706970215, 0.6798191070556641, 1.1711180210113525, 0.8571979999542236, 0.6900200843811035, 1.1626811027526855, 0.8817038536071777, 0.8003149032592773, 0.8220069408416748, 0.83001708984375, 0.6870760917663574, 0.6792089939117432, 0.9399528503417969, 0.6524560451507568, 0.6808309555053711, 0.804919958114624, 0.731849193572998, 0.5970759391784668, 0.6289620399475098, 0.8055651187896729, 1.1071739196777344, 0.9203121662139893, 0.8522610664367676, 0.6983702182769775, 1.3160839080810547, 1.2683329582214355, 0.6922838687896729, 0.651170015335083, 0.6778500080108643, 0.7993869781494141, 1.3374030590057373, 1.2936241626739502, 0.7887990474700928, 0.6381258964538574, 0.6766748428344727, 0.8380060195922852, 0.7477130889892578, 0.6921329498291016, 0.8545849323272705, 1.05800199508667, 0.6420679092407227, 0.7597670555114746, 0.8559961318969727, 0.663938045501709, 1.0042238235473633, 0.8385770320892334, 0.685352087020874, 0.6524298191070557, 0.5939171314239502, 0.5778849124908447, 0.6828510761260986, 0.8944261074066162, 0.8962569236755371, 0.9721810817718506, 0.8749818801879883, 0.9556119441986084, 1.2936890125274658, 0.6015539169311523, 0.7939050197601318, 0.6808040142059326, 1.2233848571777344, 0.882641077041626, 0.8313491344451904, 0.6216440200805664, 0.9927370548248291, 1.1932718753814697, 0.8330519199371338, 1.5554678440093994, 0.6442058086395264, 0.6963090896606445, 0.6833178997039795, 0.6679558753967285, 0.7216989994049072, 0.6528410911560059, 0.6107110977172852, 0.5817430019378662, 0.6428310871124268, 0.6417510509490967, 0.8143889904022217, 0.6699578762054443, 0.7216701507568359, 0.7936959266662598, 1.2403218746185303, 0.770906925201416, 0.6562709808349609, 0.6983799934387207, 0.8200321197509766, 0.776190996170044, 0.7968931198120117, 0.9257400035858154, 1.0120389461517334, 0.8602728843688965, 0.917133092880249, 0.6907479763031006, 0.6777517795562744, 0.7745468616485596, 0.6467061042785645, 0.6774590015411377, 0.6929030418395996, 0.6520199775695801, 0.6712419986724854, 0.6133921146392822, 1.2393231391906738, 0.7807018756866455, 0.6050248146057129, 1.3182590007781982, 0.668036937713623, 0.901190996170044, 0.8235092163085938, 0.7400481700897217, 0.752802848815918, 1.222944974899292, 0.6597061157226562, 0.7012951374053955, 0.8866360187530518, 0.8742449283599854, 0.9199850559234619, 0.6967840194702148, 1.0096790790557861, 0.6569569110870361, 0.8505301475524902, 0.6987569332122803, 0.6688768863677979, 0.6861929893493652, 0.6505279541015625, 0.6968460083007812, 0.6147880554199219, 0.8784551620483398, 0.603173017501831, 0.6305408477783203, 0.7390620708465576, 0.6361610889434814, 0.6896660327911377, 0.6832671165466309, 0.6756289005279541, 0.700084924697876, 0.706610918045044, 0.7218809127807617, 0.5853381156921387, 0.6642739772796631, 0.6682829856872559, 1.3539330959320068, 0.8186209201812744, 0.6909408569335938, 0.6135690212249756, 0.9467980861663818, 0.6544241905212402, 0.682772159576416, 0.6568160057067871, 0.6444439888000488, 0.6546900272369385, 0.6810309886932373, 0.6915881633758545, 0.6906039714813232, 1.1770000457763672, 0.706409215927124, 0.8679280281066895, 0.6540160179138184, 0.8712141513824463, 0.6482241153717041, 0.6791269779205322, 0.7709860801696777, 0.9921250343322754, 0.8143589496612549, 0.6804468631744385, 0.6930270195007324, 0.677314043045044, 0.6066200733184814, 0.6216402053833008, 0.745276927947998, 0.7934310436248779, 0.6357619762420654, 0.9039919376373291, 0.6467409133911133, 0.9813299179077148, 0.8380091190338135, 1.1583950519561768, 1.1275789737701416, 1.1177690029144287, 1.275251865386963, 0.7889108657836914, 0.7819058895111084, 0.7363429069519043, 0.6900680065155029, 0.644636869430542, 0.7334480285644531, 0.7494089603424072, 1.1598999500274658, 1.3573939800262451, 0.676292896270752, 1.4136509895324707, 0.6637108325958252, 0.642157793045044, 0.9622490406036377, 0.6871390342712402, 1.042118787765503, 0.8006150722503662, 0.660768985748291, 0.6760659217834473, 0.7007150650024414, 0.9346539974212646, 0.6636290550231934, 0.8984229564666748, 0.6539740562438965, 0.6301209926605225, 0.891603946685791, 0.9193441867828369, 0.9251918792724609, 0.8747339248657227, 0.7921397686004639, 1.0752079486846924, 1.1712749004364014, 0.6427440643310547, 0.8440718650817871, 0.7118229866027832, 0.6390249729156494, 0.6193051338195801, 0.6624720096588135, 0.6206939220428467, 0.9263811111450195, 0.8623120784759521, 0.6879041194915771, 0.6150197982788086, 0.8477699756622314, 0.6190638542175293, 1.219447135925293, 0.8177599906921387, 0.8101000785827637, 0.8663170337677002, 0.607262134552002, 0.6737668514251709, 0.7582371234893799, 1.411228895187378, 0.8122200965881348, 0.6784811019897461, 0.6393301486968994, 0.6829400062561035, 0.9966251850128174, 0.712609052658081, 0.8509178161621094, 0.7387790679931641, 0.6483981609344482, 0.8982889652252197, 0.8765110969543457, 0.8519229888916016, 0.8524830341339111, 0.9996709823608398, 0.7669100761413574, 0.7802691459655762, 0.6246349811553955, 0.9059958457946777, 0.8740599155426025, 0.7863399982452393, 0.7366740703582764, 0.6170949935913086, 1.5508298873901367, 1.3537399768829346, 0.6292190551757812, 0.7813870906829834, 0.8732168674468994, 0.6329019069671631, 0.7612810134887695, 0.7866039276123047, 0.6367950439453125, 0.6322190761566162, 0.7556178569793701, 0.6623661518096924, 0.8097789287567139, 0.6969671249389648, 0.7744319438934326, 0.6646969318389893, 1.1384711265563965, 0.753244161605835, 0.6793060302734375, 0.8614060878753662, 0.839257001876831, 1.2147910594940186, 0.6831510066986084, 0.6381919384002686, 0.6256330013275146, 0.6337699890136719, 0.662722110748291, 0.6862928867340088, 0.6999959945678711, 0.65311598777771, 0.784156084060669, 0.6158969402313232, 0.9755980968475342, 0.6355931758880615, 0.7624709606170654, 0.7597520351409912, 0.6419880390167236, 0.680340051651001, 0.8579039573669434, 0.7810049057006836, 0.6665198802947998, 1.2491838932037354, 0.7113220691680908, 0.8418159484863281, 0.6756801605224609, 0.5497000217437744, 0.6636250019073486, 0.731848955154419, 0.6871938705444336, 0.6744229793548584, 0.632627010345459, 0.6141459941864014, 0.654742956161499, 0.6457910537719727, 0.6681280136108398, 0.7842321395874023, 0.8178329467773438, 0.6945838928222656, 0.7298581600189209, 0.8408539295196533, 0.7605159282684326, 0.6378569602966309, 0.9591569900512695, 0.6639389991760254, 0.5937180519104004, 0.6066498756408691, 1.2788128852844238, 0.7919211387634277, 0.646604061126709, 0.7821781635284424, 0.6254899501800537, 0.6977989673614502, 0.6710638999938965, 1.137012004852295, 0.71030592918396, 0.7743809223175049, 0.774590015411377, 0.6631159782409668, 0.6731739044189453, 1.0729260444641113, 0.6497750282287598, 0.6512701511383057, 0.6678149700164795, 0.700998067855835, 0.7280328273773193, 0.7675189971923828, 0.573983907699585, 0.6871647834777832, 0.9162411689758301, 0.9881930351257324, 1.0775949954986572, 0.6234889030456543, 0.7110569477081299, 0.7934420108795166, 0.6430630683898926, 0.8622028827667236, 1.272231101989746, 0.6879158020019531, 0.7658920288085938, 0.6698570251464844, 0.9132840633392334, 0.6687240600585938, 0.6743011474609375, 0.5997970104217529, 0.6231980323791504, 0.6525368690490723, 0.6041219234466553, 0.8740799427032471, 0.8078758716583252, 0.5843050479888916, 0.9579119682312012, 0.7245650291442871, 0.7755041122436523, 1.0137388706207275, 0.7415890693664551, 0.7212841510772705, 0.5671069622039795, 0.6359200477600098, 0.7731449604034424, 0.9409351348876953, 1.0343589782714844, 0.7971580028533936, 0.7933871746063232, 0.6386070251464844, 0.6504659652709961, 0.5875310897827148, 0.7585568428039551, 0.8741540908813477, 0.5530991554260254, 1.2414860725402832, 0.8630027770996094, 0.6434810161590576, 0.6759769916534424, 0.8309140205383301, 0.8500401973724365, 0.616314172744751, 0.6459290981292725, 1.0063118934631348, 0.7489190101623535, 0.6712591648101807, 0.8709919452667236, 1.2171828746795654, 0.6404199600219727, 1.1902170181274414, 1.222987174987793, 0.8626570701599121, 0.9108290672302246, 0.8824200630187988, 0.6555089950561523, 0.6452491283416748, 0.7492489814758301, 1.0280218124389648, 0.8871960639953613, 0.6281368732452393, 0.8159999847412109, 0.6631419658660889, 0.5564131736755371, 1.082550048828125, 1.310364007949829, 0.7663619518280029, 0.8578360080718994, 0.616671085357666, 0.6434791088104248, 0.6679198741912842, 0.648961067199707, 0.6374220848083496, 0.6461691856384277, 1.2008130550384521, 0.7782940864562988, 0.7988388538360596, 0.840843915939331, 0.6390237808227539, 0.5891661643981934, 0.5913500785827637, 0.600031852722168, 0.6466429233551025, 0.6870388984680176, 0.662506103515625, 0.8737940788269043, 0.7567298412322998, 0.6051828861236572, 1.1732618808746338, 0.6224629878997803, 0.6298139095306396, 0.63704514503479, 0.6004641056060791, 0.5929479598999023, 0.6337978839874268, 1.2372469902038574, 1.0302119255065918, 0.8601438999176025, 1.2011969089508057, 0.8523290157318115, 0.6316518783569336, 1.204434871673584, 0.857043981552124, 0.7733938694000244, 0.8592240810394287, 1.0848798751831055, 0.9525279998779297, 0.755958080291748, 0.6634829044342041, 0.7367589473724365, 0.7986199855804443, 0.6474819183349609, 0.7566440105438232, 0.6593079566955566, 0.913470983505249, 0.8884909152984619, 0.8016998767852783, 0.6591320037841797, 0.7472920417785645, 0.8243751525878906, 0.5982861518859863, 1.1044931411743164, 0.6537470817565918, 0.8619821071624756, 1.1347849369049072, 0.7043719291687012, 0.6672039031982422, 0.7051429748535156, 0.8406281471252441, 1.251629114151001, 0.6152851581573486, 0.614171028137207, 0.8542311191558838, 0.8609631061553955, 0.9198689460754395, 0.8034100532531738, 0.7368090152740479, 0.6773040294647217, 1.1913321018218994, 0.8444728851318359, 0.8115270137786865, 0.6133339405059814, 1.2853050231933594, 0.7727780342102051, 0.6039400100708008, 1.5825121402740479, 0.8570749759674072, 0.6369211673736572, 0.73095703125, 0.9047520160675049, 0.7107808589935303, 0.7133290767669678, 0.748521089553833, 1.2036941051483154, 0.6228170394897461, 0.701401948928833, 0.6416001319885254, 0.7883210182189941, 0.8976690769195557, 0.610969066619873, 0.9264788627624512, 1.1403858661651611, 0.7385499477386475, 0.635983943939209, 0.7907240390777588, 1.2778730392456055, 0.6918079853057861, 0.6344311237335205, 0.6202671527862549, 0.8585970401763916, 1.1186258792877197, 0.9902710914611816, 0.6435229778289795, 0.9215998649597168, 0.7756550312042236, 0.6327619552612305, 1.0475192070007324, 0.6768429279327393, 1.1175780296325684, 0.7234880924224854, 0.6232609748840332, 0.6016378402709961, 0.6713840961456299, 0.6796150207519531, 0.6397302150726318, 0.8554399013519287, 0.6266839504241943, 0.6658408641815186, 0.6717097759246826, 0.7539901733398438, 0.6370029449462891, 0.9803941249847412, 0.5953378677368164, 0.9273390769958496, 0.6175589561462402, 0.6473369598388672, 0.7851078510284424, 0.6182630062103271, 0.682121992111206, 0.6502628326416016, 0.6286280155181885, 0.7933309078216553, 1.1245908737182617, 1.2445881366729736, 0.6650378704071045, 0.785783052444458, 0.8254849910736084, 0.651526927947998, 0.9006979465484619, 0.6646220684051514, 0.691741943359375, 0.6606981754302979]</t>
+    <t>[0.12257504463195801, 0.1226191520690918, 0.12262296676635742, 0.12265205383300781, 0.12266302108764648, 0.1227118968963623, 0.12272310256958008, 0.12281608581542969, 0.12282180786132812, 0.12282681465148926, 0.12288188934326172, 0.12296509742736816, 0.12297797203063965, 0.12300515174865723, 0.12301802635192871, 0.12314796447753906, 0.12340784072875977, 0.12343907356262207, 0.1235969066619873, 0.12375783920288086, 0.1242060661315918, 0.12423896789550781, 0.12440013885498047, 0.12441515922546387, 0.12450480461120605, 0.12468385696411133, 0.12482118606567383, 0.12485694885253906, 0.12507915496826172, 0.1253058910369873, 0.12550806999206543, 0.12554192543029785, 0.12580204010009766, 0.12613487243652344, 0.1262350082397461, 0.12629294395446777, 0.1263139247894287, 0.12640905380249023, 0.12671494483947754, 0.12693214416503906, 0.1270761489868164, 0.12720608711242676, 0.1273338794708252, 0.12737202644348145, 0.12740516662597656, 0.12769293785095215, 0.12775111198425293, 0.12775683403015137, 0.12784790992736816, 0.12798404693603516, 0.1280498504638672, 0.12814879417419434, 0.12815499305725098, 0.1282029151916504, 0.1282191276550293, 0.12828898429870605, 0.128371000289917, 0.1284468173980713, 0.12849688529968262, 0.12860798835754395, 0.12867093086242676, 0.12867093086242676, 0.12868189811706543, 0.12874197959899902, 0.12878203392028809, 0.1288599967956543, 0.12895417213439941, 0.12897801399230957, 0.12909293174743652, 0.12911701202392578, 0.1292121410369873, 0.12921595573425293, 0.1292710304260254, 0.129302978515625, 0.1293330192565918, 0.12935113906860352, 0.12953782081604004, 0.12954020500183105, 0.12955284118652344, 0.12955284118652344, 0.1295640468597412, 0.1295909881591797, 0.12959694862365723, 0.12963390350341797, 0.12965917587280273, 0.12974905967712402, 0.1298990249633789, 0.1299450397491455, 0.12996196746826172, 0.12997889518737793, 0.12999296188354492, 0.13004207611083984, 0.13015508651733398, 0.13016486167907715, 0.1301741600036621, 0.1302509307861328, 0.13025593757629395, 0.13033318519592285, 0.1303400993347168, 0.13036680221557617, 0.1303701400756836, 0.13037681579589844, 0.13042402267456055, 0.1304929256439209, 0.13050389289855957, 0.13054203987121582, 0.1307520866394043, 0.13080501556396484, 0.13080692291259766, 0.13088202476501465, 0.1309199333190918, 0.1309359073638916, 0.1309671401977539, 0.13103890419006348, 0.13103914260864258, 0.13106298446655273, 0.13107800483703613, 0.13111090660095215, 0.13115906715393066, 0.13117599487304688, 0.1312110424041748, 0.1312727928161621, 0.13127398490905762, 0.13129281997680664, 0.13131403923034668, 0.13131499290466309, 0.13134288787841797, 0.13135004043579102, 0.13135099411010742, 0.13139986991882324, 0.13140010833740234, 0.13142609596252441, 0.13144707679748535, 0.13149785995483398, 0.13152694702148438, 0.131544828414917, 0.13155198097229004, 0.13156986236572266, 0.13167500495910645, 0.1316990852355957, 0.1317129135131836, 0.13172101974487305, 0.1317288875579834, 0.13179993629455566, 0.13191509246826172, 0.13192296028137207, 0.13193392753601074, 0.13196802139282227, 0.13200902938842773, 0.13203716278076172, 0.1320478916168213, 0.13208413124084473, 0.13209295272827148, 0.13211512565612793, 0.13212800025939941, 0.13214516639709473, 0.1321570873260498, 0.13221120834350586, 0.1322309970855713, 0.13226699829101562, 0.13226795196533203, 0.1322767734527588, 0.13228106498718262, 0.13228297233581543, 0.13242197036743164, 0.1324300765991211, 0.13245606422424316, 0.13248109817504883, 0.13250207901000977, 0.13267803192138672, 0.13271093368530273, 0.132735013961792, 0.13274908065795898, 0.13277101516723633, 0.13278818130493164, 0.1327958106994629, 0.13279986381530762, 0.13285088539123535, 0.1329200267791748, 0.13299298286437988, 0.1329970359802246, 0.1330111026763916, 0.13302302360534668, 0.1330869197845459, 0.13318800926208496, 0.1332080364227295, 0.13323402404785156, 0.13324213027954102, 0.13327693939208984, 0.13333606719970703, 0.13334083557128906, 0.13338184356689453, 0.13341903686523438, 0.1334240436553955, 0.13342690467834473, 0.13349294662475586, 0.13350701332092285, 0.13351798057556152, 0.13352704048156738, 0.133544921875, 0.1335618495941162, 0.1336050033569336, 0.13363099098205566, 0.13364100456237793, 0.13365411758422852, 0.13365721702575684, 0.13374090194702148, 0.13374805450439453, 0.13377785682678223, 0.13378000259399414, 0.13378596305847168, 0.13382601737976074, 0.13386201858520508, 0.13386297225952148, 0.13387680053710938, 0.13399004936218262, 0.13399791717529297, 0.1340799331665039, 0.13409686088562012, 0.13419103622436523, 0.1342329978942871, 0.13428497314453125, 0.13428688049316406, 0.13435792922973633, 0.13437294960021973, 0.1344001293182373, 0.13443613052368164, 0.13446712493896484, 0.13448786735534668, 0.134490966796875, 0.13453292846679688, 0.1345381736755371, 0.1345829963684082, 0.13460898399353027, 0.13461589813232422, 0.13465595245361328, 0.13466382026672363, 0.13466691970825195, 0.1346721649169922, 0.1346888542175293, 0.13470983505249023, 0.13472819328308105, 0.13475918769836426, 0.1347649097442627, 0.13477301597595215, 0.13477611541748047, 0.1348409652709961, 0.13493895530700684, 0.1349620819091797, 0.13500404357910156, 0.13513684272766113, 0.1351768970489502, 0.1351938247680664, 0.13521504402160645, 0.13526487350463867, 0.13527917861938477, 0.13531804084777832, 0.1353309154510498, 0.13543200492858887, 0.13543701171875, 0.1355609893798828, 0.13565301895141602, 0.13572001457214355, 0.13575291633605957, 0.13579797744750977, 0.13587093353271484, 0.13599109649658203, 0.13599419593811035, 0.13604998588562012, 0.13608694076538086, 0.13610291481018066, 0.13623309135437012, 0.13626503944396973, 0.13627004623413086, 0.13627409934997559, 0.13629913330078125, 0.1363050937652588, 0.13631510734558105, 0.13631796836853027, 0.136322021484375, 0.13634490966796875, 0.1363849639892578, 0.13645100593566895, 0.13646197319030762, 0.13649392127990723, 0.13666200637817383, 0.13666820526123047, 0.1366710662841797, 0.13678216934204102, 0.13684797286987305, 0.13704180717468262, 0.13705205917358398, 0.1370530128479004, 0.13712406158447266, 0.13715696334838867, 0.1371610164642334, 0.13716602325439453, 0.13724493980407715, 0.13730406761169434, 0.1373610496520996, 0.13736486434936523, 0.137376070022583, 0.13747906684875488, 0.13753914833068848, 0.13756895065307617, 0.13759708404541016, 0.13765692710876465, 0.1377100944519043, 0.13775300979614258, 0.13785004615783691, 0.13785099983215332, 0.13785696029663086, 0.13786721229553223, 0.13793110847473145, 0.13799500465393066, 0.13800501823425293, 0.13804101943969727, 0.13809895515441895, 0.1382138729095459, 0.13828086853027344, 0.13834190368652344, 0.1383528709411621, 0.13836407661437988, 0.13837003707885742, 0.13840508460998535, 0.1384119987487793, 0.1384749412536621, 0.13855290412902832, 0.13856983184814453, 0.13860797882080078, 0.13863396644592285, 0.13865399360656738, 0.13869810104370117, 0.13870882987976074, 0.13873696327209473, 0.13875579833984375, 0.1387619972229004, 0.1387929916381836, 0.13886618614196777, 0.13887500762939453, 0.13891315460205078, 0.13891887664794922, 0.13893795013427734, 0.13895893096923828, 0.13904714584350586, 0.13905096054077148, 0.1390528678894043, 0.13907194137573242, 0.13908791542053223, 0.13929986953735352, 0.13930797576904297, 0.1393129825592041, 0.1393420696258545, 0.13937687873840332, 0.13944005966186523, 0.1394491195678711, 0.1394939422607422, 0.1394948959350586, 0.13953113555908203, 0.1395881175994873, 0.13974213600158691, 0.13975095748901367, 0.13978195190429688, 0.13980603218078613, 0.13988018035888672, 0.13988399505615234, 0.13989591598510742, 0.13994121551513672, 0.1399519443511963, 0.14000487327575684, 0.14001893997192383, 0.14015603065490723, 0.14017081260681152, 0.14019489288330078, 0.14032912254333496, 0.1403350830078125, 0.14034104347229004, 0.14035892486572266, 0.1403820514678955, 0.14039182662963867, 0.14040708541870117, 0.14046597480773926, 0.1404879093170166, 0.14049005508422852, 0.1405649185180664, 0.14068913459777832, 0.1407489776611328, 0.14075398445129395, 0.14075994491577148, 0.14079689979553223, 0.1408398151397705, 0.1408860683441162, 0.1409590244293213, 0.14098215103149414, 0.1409900188446045, 0.14103388786315918, 0.1410510540008545, 0.14105796813964844, 0.1410670280456543, 0.141099214553833, 0.14110803604125977, 0.14121389389038086, 0.14121794700622559, 0.1412370204925537, 0.1413130760192871, 0.1413710117340088, 0.14139604568481445, 0.14143705368041992, 0.14153504371643066, 0.14157605171203613, 0.14165592193603516, 0.14176511764526367, 0.14176607131958008, 0.1418437957763672, 0.1418900489807129, 0.14196109771728516, 0.1419978141784668, 0.14202189445495605, 0.1420450210571289, 0.1420459747314453, 0.14204883575439453, 0.14217782020568848, 0.14223814010620117, 0.14230108261108398, 0.14231204986572266, 0.1423630714416504, 0.1423640251159668, 0.14243197441101074, 0.142441987991333, 0.14245009422302246, 0.1425189971923828, 0.14252591133117676, 0.14271903038024902, 0.14273500442504883, 0.14275312423706055, 0.14277100563049316, 0.1427769660949707, 0.1428360939025879, 0.14284491539001465, 0.14284610748291016, 0.1428818702697754, 0.1429300308227539, 0.1429460048675537, 0.14294695854187012, 0.1429910659790039, 0.14304494857788086, 0.1430819034576416, 0.14310288429260254, 0.14310407638549805, 0.1431260108947754, 0.14320802688598633, 0.14323186874389648, 0.14326214790344238, 0.14326810836791992, 0.14330482482910156, 0.1433429718017578, 0.14345002174377441, 0.14345908164978027, 0.14351797103881836, 0.14354181289672852, 0.1435840129852295, 0.14361095428466797, 0.14362406730651855, 0.14371299743652344, 0.14377784729003906, 0.14384913444519043, 0.1439039707183838, 0.14397907257080078, 0.14408302307128906, 0.14419293403625488, 0.1441960334777832, 0.1442420482635498, 0.1442430019378662, 0.14432406425476074, 0.14432716369628906, 0.14438819885253906, 0.14446687698364258, 0.14448189735412598, 0.1445009708404541, 0.14450979232788086, 0.14453482627868652, 0.14456510543823242, 0.1446700096130371, 0.14470696449279785, 0.14470791816711426, 0.14475703239440918, 0.14477896690368652, 0.14479613304138184, 0.14481687545776367, 0.14486312866210938, 0.1448650360107422, 0.14487385749816895, 0.14488482475280762, 0.14488983154296875, 0.144942045211792, 0.14499306678771973, 0.1450061798095703, 0.14506196975708008, 0.14508819580078125, 0.14517498016357422, 0.14523696899414062, 0.14525198936462402, 0.14534401893615723, 0.14536190032958984, 0.14536595344543457, 0.1453688144683838, 0.14538288116455078, 0.14549803733825684, 0.1455230712890625, 0.1455380916595459, 0.14568209648132324, 0.14571094512939453, 0.14583206176757812, 0.1458749771118164, 0.1458899974822998, 0.14591693878173828, 0.14594197273254395, 0.14594697952270508, 0.145982027053833, 0.14600896835327148, 0.1460402011871338, 0.14605212211608887, 0.14606690406799316, 0.1460738182067871, 0.14609289169311523, 0.14616799354553223, 0.14618515968322754, 0.14628815650939941, 0.14631104469299316, 0.14631390571594238, 0.14632415771484375, 0.14634418487548828, 0.14641594886779785, 0.14642095565795898, 0.14645099639892578, 0.14646315574645996, 0.1464850902557373, 0.14652299880981445, 0.14657187461853027, 0.14664101600646973, 0.14667010307312012, 0.1466989517211914, 0.14671802520751953, 0.1467571258544922, 0.146806001663208, 0.14682483673095703, 0.14684414863586426, 0.1468491554260254, 0.1468501091003418, 0.14686799049377441, 0.146881103515625, 0.14693999290466309, 0.1469559669494629, 0.1470170021057129, 0.14705109596252441, 0.147064208984375, 0.1470651626586914, 0.1470651626586914, 0.14707684516906738, 0.1470959186553955, 0.1471250057220459, 0.14714288711547852, 0.14723706245422363, 0.14730000495910645, 0.14742588996887207, 0.14743900299072266, 0.14743995666503906, 0.14744901657104492, 0.14746880531311035, 0.14748692512512207, 0.14753103256225586, 0.1475849151611328, 0.14759397506713867, 0.14760494232177734, 0.14761805534362793, 0.14763116836547852, 0.14766693115234375, 0.14770197868347168, 0.1477200984954834, 0.1477341651916504, 0.14774012565612793, 0.14774203300476074, 0.14774298667907715, 0.14777112007141113, 0.1477959156036377, 0.14783191680908203, 0.14785408973693848, 0.1478579044342041, 0.14787697792053223, 0.1478898525238037, 0.14809489250183105, 0.14810395240783691, 0.14815592765808105, 0.14820218086242676, 0.1482219696044922, 0.14827990531921387, 0.14831805229187012, 0.14832282066345215, 0.14835000038146973, 0.14835095405578613, 0.14839506149291992, 0.14839601516723633, 0.14841699600219727, 0.14844393730163574, 0.14847397804260254, 0.14849495887756348, 0.1484999656677246, 0.14850711822509766, 0.14850807189941406, 0.14852595329284668, 0.14853501319885254, 0.1485588550567627, 0.14858293533325195, 0.14859795570373535, 0.14860200881958008, 0.14863085746765137, 0.14863801002502441, 0.14865589141845703, 0.14868903160095215, 0.1486949920654297, 0.1488180160522461, 0.1489090919494629, 0.14891600608825684, 0.14901208877563477, 0.14903998374938965, 0.1490788459777832, 0.14910387992858887, 0.14913415908813477, 0.14923787117004395, 0.1492469310760498, 0.14927411079406738, 0.14932608604431152, 0.1493368148803711, 0.14934301376342773, 0.14937996864318848, 0.1493818759918213, 0.1493830680847168, 0.14938592910766602, 0.14939117431640625, 0.14941906929016113, 0.14948701858520508, 0.1495819091796875, 0.1496589183807373, 0.14966106414794922, 0.14966392517089844, 0.14973902702331543, 0.14978504180908203, 0.14978504180908203, 0.14981389045715332, 0.14981889724731445, 0.14983105659484863, 0.14983296394348145, 0.149885892868042, 0.14989399909973145, 0.1499168872833252, 0.14992785453796387, 0.14995789527893066, 0.14997196197509766, 0.1499769687652588, 0.1499919891357422, 0.15000009536743164, 0.15000200271606445, 0.15006113052368164, 0.15007615089416504, 0.15008807182312012, 0.15010404586791992, 0.15012502670288086, 0.15015888214111328, 0.15029120445251465, 0.15036821365356445, 0.15037202835083008, 0.15037989616394043, 0.15038204193115234, 0.15040898323059082, 0.1504499912261963, 0.1504509449005127, 0.1505119800567627, 0.15052390098571777, 0.1505439281463623, 0.1505749225616455, 0.15059208869934082, 0.1506040096282959, 0.15061402320861816, 0.15071392059326172, 0.1507279872894287, 0.15075898170471191, 0.15078186988830566, 0.15084290504455566, 0.15084314346313477, 0.15088295936584473, 0.15092706680297852, 0.15100884437561035, 0.15101003646850586, 0.15104007720947266, 0.15105319023132324, 0.15114378929138184, 0.15126705169677734, 0.15127992630004883, 0.15129899978637695, 0.15131092071533203, 0.15131902694702148, 0.15134906768798828, 0.15142011642456055, 0.1514599323272705, 0.15148210525512695, 0.15152907371520996, 0.15156197547912598, 0.15157318115234375, 0.151594877243042, 0.1518080234527588, 0.15195703506469727, 0.15197396278381348, 0.15203404426574707, 0.15204191207885742, 0.1520709991455078, 0.15209698677062988, 0.15210604667663574, 0.15212202072143555, 0.1521611213684082, 0.15224218368530273, 0.15224790573120117, 0.15236115455627441, 0.1524200439453125, 0.15244698524475098, 0.15247011184692383, 0.15249896049499512, 0.15257000923156738, 0.15260791778564453, 0.15262198448181152, 0.1526319980621338, 0.15269780158996582, 0.15280485153198242, 0.15281891822814941, 0.1528339385986328, 0.15283799171447754, 0.15284204483032227, 0.15303587913513184, 0.1530749797821045, 0.15309691429138184, 0.15319299697875977, 0.15320777893066406, 0.1532151699066162, 0.1533060073852539, 0.15335297584533691, 0.1534709930419922, 0.15350985527038574, 0.15356206893920898, 0.15362000465393066, 0.15366601943969727, 0.15366721153259277, 0.1536879539489746, 0.15377306938171387, 0.153825044631958, 0.15393805503845215, 0.15396809577941895, 0.1539750099182129, 0.15406513214111328, 0.15407395362854004, 0.15410614013671875, 0.15411615371704102, 0.1541299819946289, 0.15413308143615723, 0.15414094924926758, 0.15420913696289062, 0.15424585342407227, 0.15436291694641113, 0.15439319610595703, 0.15459895133972168, 0.15474390983581543, 0.1547529697418213, 0.15476489067077637, 0.15476703643798828, 0.15477895736694336, 0.15484619140625, 0.15491080284118652, 0.15502095222473145, 0.1551210880279541, 0.1551361083984375, 0.15515398979187012, 0.15518403053283691, 0.15523481369018555, 0.1556408405303955, 0.15564298629760742, 0.15564799308776855, 0.1556551456451416, 0.15567517280578613, 0.1556990146636963, 0.15579700469970703, 0.15593504905700684, 0.15617895126342773, 0.156235933303833, 0.1562800407409668, 0.15631389617919922, 0.15634512901306152, 0.1564161777496338, 0.1564328670501709, 0.15657901763916016, 0.15660405158996582, 0.1566150188446045, 0.15664291381835938, 0.15669798851013184, 0.15689706802368164, 0.15693283081054688, 0.15695405006408691, 0.15700697898864746, 0.15713787078857422, 0.15716099739074707, 0.1571640968322754, 0.15723586082458496, 0.15735793113708496, 0.157365083694458, 0.15749597549438477, 0.1576979160308838, 0.15770602226257324, 0.15774011611938477, 0.15779519081115723, 0.1578981876373291, 0.1580181121826172, 0.1580338478088379, 0.1580519676208496, 0.15810179710388184, 0.1581878662109375, 0.15819001197814941, 0.15822505950927734, 0.15831518173217773, 0.1583850383758545, 0.15866994857788086, 0.1587669849395752, 0.1587989330291748, 0.158843994140625, 0.1589219570159912, 0.1589510440826416, 0.1590120792388916, 0.1591029167175293, 0.15913891792297363, 0.1592850685119629, 0.15961480140686035, 0.15970277786254883, 0.15974688529968262, 0.15978598594665527, 0.1598520278930664, 0.159898042678833, 0.1599738597869873, 0.1599750518798828, 0.15999317169189453, 0.16008996963500977, 0.1601090431213379, 0.16014599800109863, 0.16018891334533691, 0.16024184226989746, 0.16031289100646973, 0.16032695770263672, 0.16075801849365234, 0.16077804565429688, 0.16078615188598633, 0.16080784797668457, 0.16081500053405762, 0.16086316108703613, 0.16098904609680176, 0.16114497184753418, 0.1611640453338623, 0.16118597984313965, 0.16124796867370605, 0.1612861156463623, 0.1618959903717041, 0.16197896003723145, 0.16203808784484863, 0.16213011741638184, 0.1624128818511963, 0.16254901885986328, 0.16256093978881836, 0.1626439094543457, 0.16269516944885254, 0.16279196739196777, 0.162977933883667, 0.16318297386169434, 0.16325092315673828, 0.16329216957092285, 0.16337895393371582, 0.16340184211730957, 0.16356205940246582, 0.16359806060791016, 0.1636359691619873, 0.16373682022094727, 0.1638021469116211, 0.16416215896606445, 0.16442108154296875, 0.16450905799865723, 0.16459107398986816, 0.1647500991821289, 0.1647629737854004, 0.1649320125579834, 0.16509699821472168, 0.16516900062561035, 0.1651778221130371, 0.1652050018310547, 0.1655740737915039, 0.1656661033630371, 0.16588592529296875, 0.16602802276611328, 0.16606497764587402, 0.1660780906677246, 0.16617298126220703, 0.16617417335510254, 0.16733098030090332, 0.16746306419372559, 0.16751980781555176, 0.16753911972045898, 0.16780304908752441, 0.16782903671264648, 0.16785001754760742, 0.16804790496826172, 0.16831707954406738, 0.16867494583129883, 0.16898584365844727, 0.16965413093566895, 0.16972994804382324, 0.16977691650390625, 0.17008090019226074, 0.17008495330810547, 0.17026090621948242, 0.17026495933532715, 0.17031598091125488, 0.17039203643798828, 0.17065787315368652, 0.17103290557861328, 0.171051025390625, 0.17145681381225586, 0.17200088500976562, 0.17284393310546875, 0.1730029582977295, 0.17366504669189453, 0.17369818687438965, 0.17371797561645508, 0.17380309104919434, 0.17385005950927734, 0.17413806915283203, 0.1742720603942871, 0.174299955368042, 0.174483060836792, 0.17467403411865234, 0.1747150421142578, 0.17484688758850098, 0.1753101348876953, 0.1762399673461914, 0.17652201652526855, 0.1771841049194336, 0.17741608619689941, 0.1776719093322754, 0.17800593376159668, 0.17885088920593262, 0.17908501625061035, 0.17974090576171875, 0.17977190017700195, 0.18017911911010742, 0.18147802352905273, 0.18195700645446777, 0.18274998664855957, 0.18287897109985352, 0.18297696113586426, 0.18459820747375488, 0.18512415885925293, 0.1857151985168457, 0.18587589263916016, 0.1870570182800293, 0.18728899955749512, 0.18777704238891602, 0.18817400932312012, 0.1885969638824463, 0.18942904472351074, 0.1894969940185547, 0.18978404998779297, 0.19011402130126953, 0.19015908241271973, 0.1909348964691162, 0.19126105308532715, 0.1916799545288086, 0.19203805923461914, 0.19208407402038574, 0.19336819648742676]</t>
+  </si>
+  <si>
+    <t>[0.09655594825744629, 0.09656000137329102, 0.09665322303771973, 0.0970909595489502, 0.09713196754455566, 0.0973811149597168, 0.09753584861755371, 0.09756207466125488, 0.09771203994750977, 0.09772396087646484, 0.09778714179992676, 0.09794092178344727, 0.09813594818115234, 0.09825611114501953, 0.09875607490539551, 0.09916114807128906, 0.09941411018371582, 0.09969186782836914, 0.09976506233215332, 0.10001397132873535, 0.10018396377563477, 0.10020995140075684, 0.1003258228302002, 0.10040807723999023, 0.10042500495910645, 0.10045289993286133, 0.10047101974487305, 0.1004939079284668, 0.10051584243774414, 0.10055899620056152, 0.10056304931640625, 0.10057187080383301, 0.10058307647705078, 0.10065317153930664, 0.1006920337677002, 0.10076212882995605, 0.10079097747802734, 0.1008000373840332, 0.10081005096435547, 0.10089898109436035, 0.10090184211730957, 0.10090398788452148, 0.10090899467468262, 0.10097312927246094, 0.10097503662109375, 0.10100793838500977, 0.10100984573364258, 0.10104513168334961, 0.10107088088989258, 0.10108280181884766, 0.10111403465270996, 0.10113787651062012, 0.10114383697509766, 0.10115289688110352, 0.10117411613464355, 0.1012430191040039, 0.10124611854553223, 0.10124802589416504, 0.10125589370727539, 0.10126113891601562, 0.10126781463623047, 0.10128903388977051, 0.10129308700561523, 0.10130596160888672, 0.1013181209564209, 0.10134100914001465, 0.10134291648864746, 0.10135412216186523, 0.10135984420776367, 0.10136604309082031, 0.1013798713684082, 0.10139298439025879, 0.10139703750610352, 0.10141706466674805, 0.10142087936401367, 0.10142803192138672, 0.10145092010498047, 0.10145401954650879, 0.1014859676361084, 0.10152292251586914, 0.10152602195739746, 0.10155606269836426, 0.10156798362731934, 0.10156798362731934, 0.10157489776611328, 0.10158586502075195, 0.10160493850708008, 0.10161304473876953, 0.10162591934204102, 0.10162997245788574, 0.10164690017700195, 0.10165905952453613, 0.1016690731048584, 0.10167288780212402, 0.10167789459228516, 0.10167884826660156, 0.10170722007751465, 0.10172009468078613, 0.10172700881958008, 0.1017448902130127, 0.10176587104797363, 0.10177803039550781, 0.10177898406982422, 0.10178494453430176, 0.10179686546325684, 0.10180783271789551, 0.10180902481079102, 0.10180997848510742, 0.10182023048400879, 0.10182404518127441, 0.10184502601623535, 0.1018528938293457, 0.10186600685119629, 0.10187101364135742, 0.10190606117248535, 0.10190701484680176, 0.10190892219543457, 0.10192394256591797, 0.10192418098449707, 0.1019289493560791, 0.10194182395935059, 0.10197901725769043, 0.10197901725769043, 0.10199093818664551, 0.10199499130249023, 0.10199809074401855, 0.10199809074401855, 0.10200119018554688, 0.10200309753417969, 0.1020197868347168, 0.1020209789276123, 0.10203695297241211, 0.10205197334289551, 0.10210394859313965, 0.10210609436035156, 0.10210990905761719, 0.1021120548248291, 0.10211491584777832, 0.10212898254394531, 0.10213398933410645, 0.10213708877563477, 0.1021420955657959, 0.1021430492401123, 0.10216188430786133, 0.10216498374938965, 0.10220599174499512, 0.10220789909362793, 0.10221385955810547, 0.10223102569580078, 0.10224509239196777, 0.10225200653076172, 0.10226988792419434, 0.1022799015045166, 0.10228204727172852, 0.10230112075805664, 0.10230183601379395, 0.1023108959197998, 0.10232806205749512, 0.10235214233398438, 0.10235309600830078, 0.1023550033569336, 0.10237383842468262, 0.10240793228149414, 0.10241508483886719, 0.10242509841918945, 0.10242795944213867, 0.10243892669677734, 0.10244011878967285, 0.10244107246398926, 0.10245108604431152, 0.10245895385742188, 0.10246396064758301, 0.10246992111206055, 0.10247802734375, 0.10248184204101562, 0.10249114036560059, 0.10249185562133789, 0.10250306129455566, 0.10250997543334961, 0.10252594947814941, 0.10252904891967773, 0.10253214836120605, 0.10253500938415527, 0.10254597663879395, 0.10255002975463867, 0.10255789756774902, 0.10258603096008301, 0.10258698463439941, 0.10258817672729492, 0.10259294509887695, 0.10261297225952148, 0.1026160717010498, 0.10262084007263184, 0.10262203216552734, 0.10262298583984375, 0.10263800621032715, 0.10263895988464355, 0.10265588760375977, 0.10266685485839844, 0.10267901420593262, 0.10269522666931152, 0.10269594192504883, 0.10270214080810547, 0.10271120071411133, 0.10271716117858887, 0.10272598266601562, 0.10272979736328125, 0.10273098945617676, 0.10274004936218262, 0.10274887084960938, 0.10277915000915527, 0.10278201103210449, 0.10278987884521484, 0.10279011726379395, 0.10280990600585938, 0.10281205177307129, 0.10281705856323242, 0.10282397270202637, 0.10282492637634277, 0.10282516479492188, 0.10283303260803223, 0.10283398628234863, 0.10283398628234863, 0.10285592079162598, 0.1028599739074707, 0.10286498069763184, 0.10286617279052734, 0.10287308692932129, 0.10289502143859863, 0.10290217399597168, 0.10290789604187012, 0.10293698310852051, 0.10293793678283691, 0.10293889045715332, 0.10294198989868164, 0.1029520034790039, 0.10295295715332031, 0.10295510292053223, 0.10295605659484863, 0.10296082496643066, 0.10297012329101562, 0.10298299789428711, 0.10298395156860352, 0.10300207138061523, 0.1030130386352539, 0.10301589965820312, 0.10302495956420898, 0.1030280590057373, 0.10304117202758789, 0.1030421257019043, 0.10305213928222656, 0.1030738353729248, 0.10308194160461426, 0.10309815406799316, 0.10310506820678711, 0.1031179428100586, 0.10312104225158691, 0.10314702987670898, 0.10317111015319824, 0.10318207740783691, 0.10318708419799805, 0.10320305824279785, 0.10321903228759766, 0.10322904586791992, 0.10326004028320312, 0.10326194763183594, 0.10327005386352539, 0.10327601432800293, 0.10328388214111328, 0.10330414772033691, 0.10334110260009766, 0.10336184501647949, 0.10337400436401367, 0.10338997840881348, 0.10340285301208496, 0.10340309143066406, 0.10340309143066406, 0.1034088134765625, 0.1034250259399414, 0.10344791412353516, 0.10345101356506348, 0.10345602035522461, 0.10346508026123047, 0.103485107421875, 0.10351920127868652, 0.10355186462402344, 0.10357093811035156, 0.10357499122619629, 0.1035759449005127, 0.10358500480651855, 0.1036829948425293, 0.10369110107421875, 0.10370206832885742, 0.10372805595397949, 0.10373592376708984, 0.10382604598999023, 0.10383296012878418, 0.1038360595703125, 0.10384511947631836, 0.10385990142822266, 0.10388398170471191, 0.10388684272766113, 0.10394787788391113, 0.10397696495056152, 0.10399198532104492, 0.10404014587402344, 0.10408186912536621, 0.10410618782043457, 0.1042020320892334, 0.10421085357666016, 0.10428786277770996, 0.10429000854492188, 0.10429716110229492, 0.10438704490661621, 0.10439920425415039, 0.10444498062133789, 0.10468101501464844, 0.10471320152282715, 0.10476398468017578, 0.10477209091186523, 0.10478496551513672, 0.10480809211730957, 0.10484981536865234, 0.10495901107788086, 0.10498499870300293, 0.10499215126037598, 0.1049962043762207, 0.10503602027893066, 0.1050710678100586, 0.10511207580566406, 0.10512614250183105, 0.10512709617614746, 0.10518503189086914, 0.10520410537719727, 0.10526895523071289, 0.10528206825256348, 0.10530614852905273, 0.1053171157836914, 0.10533595085144043, 0.10534381866455078, 0.10537195205688477, 0.10538315773010254, 0.1053929328918457, 0.10540509223937988, 0.10542082786560059, 0.10542607307434082, 0.10543584823608398, 0.10545992851257324, 0.10548090934753418, 0.10550403594970703, 0.10553312301635742, 0.10554790496826172, 0.10556197166442871, 0.10557889938354492, 0.10562396049499512, 0.10566210746765137, 0.10566401481628418, 0.10567402839660645, 0.10575509071350098, 0.10575699806213379, 0.1057581901550293, 0.10577511787414551, 0.10577893257141113, 0.10578513145446777, 0.1057898998260498, 0.10579586029052734, 0.10582089424133301, 0.10582304000854492, 0.10583090782165527, 0.10583710670471191, 0.10586285591125488, 0.10590100288391113, 0.10593104362487793, 0.10593199729919434, 0.10595512390136719, 0.10598111152648926, 0.10600519180297852, 0.10604286193847656, 0.10606193542480469, 0.10606622695922852, 0.10606908798217773, 0.10609006881713867, 0.10610198974609375, 0.10610485076904297, 0.10611295700073242, 0.10611486434936523, 0.10624504089355469, 0.10626792907714844, 0.1063530445098877, 0.10635590553283691, 0.10635995864868164, 0.10635995864868164, 0.10636591911315918, 0.10637497901916504, 0.10638093948364258, 0.10639309883117676, 0.10639786720275879, 0.10641312599182129, 0.10643196105957031, 0.10643887519836426, 0.1064610481262207, 0.10646200180053711, 0.10646700859069824, 0.10648488998413086, 0.10651016235351562, 0.10651898384094238, 0.10651993751525879, 0.1065530776977539, 0.10657691955566406, 0.10658478736877441, 0.1065969467163086, 0.10664796829223633, 0.10665678977966309, 0.10666990280151367, 0.10667800903320312, 0.10669207572937012, 0.10669398307800293, 0.10672402381896973, 0.10673093795776367, 0.10674095153808594, 0.10674905776977539, 0.10675311088562012, 0.10677003860473633, 0.10677194595336914, 0.10677194595336914, 0.10677909851074219, 0.10681509971618652, 0.10681700706481934, 0.1068258285522461, 0.10683202743530273, 0.10684394836425781, 0.10684704780578613, 0.106903076171875, 0.10690808296203613, 0.10692286491394043, 0.10692596435546875, 0.10693097114562988, 0.10693907737731934, 0.10700106620788574, 0.10701394081115723, 0.10701584815979004, 0.10703015327453613, 0.10703492164611816, 0.10703516006469727, 0.1070399284362793, 0.10704517364501953, 0.1070549488067627, 0.10706090927124023, 0.10706400871276855, 0.10706400871276855, 0.10706400871276855, 0.1070871353149414, 0.10709810256958008, 0.10710501670837402, 0.10711002349853516, 0.10715413093566895, 0.10715699195861816, 0.10716891288757324, 0.10717296600341797, 0.1071939468383789, 0.10719704627990723, 0.10720515251159668, 0.1072089672088623, 0.10720992088317871, 0.10721111297607422, 0.1072230339050293, 0.10722994804382324, 0.10723114013671875, 0.10723686218261719, 0.1072380542755127, 0.10724496841430664, 0.10727596282958984, 0.10731196403503418, 0.10731315612792969, 0.10732388496398926, 0.10732507705688477, 0.1073300838470459, 0.10734009742736816, 0.10734391212463379, 0.10735678672790527, 0.10737299919128418, 0.10737800598144531, 0.10738301277160645, 0.10738801956176758, 0.10739398002624512, 0.1074061393737793, 0.10740780830383301, 0.10741901397705078, 0.10743284225463867, 0.10743999481201172, 0.1074521541595459, 0.10746908187866211, 0.1074979305267334, 0.1075129508972168, 0.10751485824584961, 0.10751509666442871, 0.10752391815185547, 0.10752391815185547, 0.10754203796386719, 0.1075441837310791, 0.10755205154418945, 0.10756802558898926, 0.10757207870483398, 0.10757803916931152, 0.10757899284362793, 0.10758113861083984, 0.10758495330810547, 0.10761308670043945, 0.10762500762939453, 0.10763311386108398, 0.10764193534851074, 0.10764193534851074, 0.10766410827636719, 0.10768389701843262, 0.1076960563659668, 0.10770297050476074, 0.10770606994628906, 0.10772180557250977, 0.10773420333862305, 0.10773801803588867, 0.10774397850036621, 0.1077871322631836, 0.10779809951782227, 0.10780501365661621, 0.10780692100524902, 0.10781407356262207, 0.10781621932983398, 0.10781693458557129, 0.10781693458557129, 0.10782790184020996, 0.10783100128173828, 0.10784006118774414, 0.1078500747680664, 0.10787391662597656, 0.10788297653198242, 0.10788989067077637, 0.10790491104125977, 0.10794401168823242, 0.10796999931335449, 0.10797595977783203, 0.10800790786743164, 0.10801100730895996, 0.10807204246520996, 0.10808920860290527, 0.1080939769744873, 0.10810112953186035, 0.10811519622802734, 0.10814094543457031, 0.10814213752746582, 0.10814285278320312, 0.10814690589904785, 0.10816502571105957, 0.10820603370666504, 0.10820817947387695, 0.10821199417114258, 0.10822200775146484, 0.10822892189025879, 0.10825991630554199, 0.1082611083984375, 0.10827898979187012, 0.10828399658203125, 0.1082909107208252, 0.10829710960388184, 0.1083059310913086, 0.10832595825195312, 0.1083371639251709, 0.10833883285522461, 0.10834789276123047, 0.108367919921875, 0.10837697982788086, 0.10838890075683594, 0.10840678215026855, 0.10841488838195801, 0.10841703414916992, 0.10843515396118164, 0.10853981971740723, 0.10856914520263672, 0.10862302780151367, 0.10867619514465332, 0.10868501663208008, 0.10870599746704102, 0.10871219635009766, 0.10871696472167969, 0.10873293876647949, 0.10874295234680176, 0.10874700546264648, 0.10878300666809082, 0.10882806777954102, 0.10882997512817383, 0.1088409423828125, 0.10885310173034668, 0.10886883735656738, 0.1088869571685791, 0.10889506340026855, 0.10889697074890137, 0.10889697074890137, 0.10893893241882324, 0.10900092124938965, 0.10910701751708984, 0.10922384262084961, 0.10933494567871094, 0.1093599796295166, 0.10936498641967773, 0.10951495170593262, 0.10965394973754883, 0.10966205596923828, 0.10970807075500488, 0.10971903800964355, 0.10978913307189941, 0.10983395576477051, 0.10988283157348633, 0.10989212989807129, 0.10994386672973633, 0.11002612113952637, 0.11012005805969238, 0.11015701293945312, 0.11023998260498047, 0.11031723022460938, 0.11034321784973145, 0.11034917831420898, 0.110382080078125, 0.11041903495788574, 0.11046195030212402, 0.11048197746276855, 0.11051106452941895, 0.11052393913269043, 0.11052918434143066, 0.11053991317749023, 0.11054778099060059, 0.11058998107910156, 0.1106560230255127, 0.11066102981567383, 0.11067605018615723, 0.11069297790527344, 0.11073493957519531, 0.11073708534240723, 0.11076593399047852, 0.11077618598937988, 0.1107940673828125, 0.11081194877624512, 0.11096382141113281, 0.11096715927124023, 0.11107182502746582, 0.11107993125915527, 0.11107993125915527, 0.11108088493347168, 0.11108899116516113, 0.1111290454864502, 0.11113309860229492, 0.1112070083618164, 0.11121392250061035, 0.11124110221862793, 0.11127495765686035, 0.11130404472351074, 0.1113271713256836, 0.11136507987976074, 0.11140298843383789, 0.1114051342010498, 0.11145496368408203, 0.1114659309387207, 0.11152219772338867, 0.11153078079223633, 0.11158609390258789, 0.11159110069274902, 0.11163091659545898, 0.11163902282714844, 0.11167192459106445, 0.11167383193969727, 0.11167788505554199, 0.1116938591003418, 0.11169600486755371, 0.11170005798339844, 0.11170101165771484, 0.11173105239868164, 0.11175990104675293, 0.11177992820739746, 0.11180686950683594, 0.1118321418762207, 0.11186695098876953, 0.11187100410461426, 0.11188387870788574, 0.11194086074829102, 0.11194586753845215, 0.1119542121887207, 0.11196303367614746, 0.11196398735046387, 0.111968994140625, 0.11202597618103027, 0.11203384399414062, 0.11205101013183594, 0.11205196380615234, 0.1120598316192627, 0.11214685440063477, 0.11215806007385254, 0.11216211318969727, 0.1121668815612793, 0.11217999458312988, 0.1121821403503418, 0.1121828556060791, 0.11218690872192383, 0.112213134765625, 0.11224007606506348, 0.11230897903442383, 0.11230897903442383, 0.11233997344970703, 0.11234402656555176, 0.11235594749450684, 0.11235809326171875, 0.11237311363220215, 0.11237406730651855, 0.11238312721252441, 0.11238408088684082, 0.11238908767700195, 0.11243391036987305, 0.11243605613708496, 0.1124410629272461, 0.11244320869445801, 0.11246109008789062, 0.11250805854797363, 0.11250996589660645, 0.11253690719604492, 0.11256814002990723, 0.11257290840148926, 0.11257314682006836, 0.1126101016998291, 0.1126410961151123, 0.11264300346374512, 0.11264705657958984, 0.11268901824951172, 0.1127159595489502, 0.11272501945495605, 0.11272597312927246, 0.11273598670959473, 0.11273598670959473, 0.11274099349975586, 0.11275100708007812, 0.11275482177734375, 0.11282896995544434, 0.1128380298614502, 0.11287093162536621, 0.11287498474121094, 0.11287593841552734, 0.11290597915649414, 0.11291313171386719, 0.1129150390625, 0.11292600631713867, 0.11293697357177734, 0.11295890808105469, 0.11296892166137695, 0.11298108100891113, 0.11300301551818848, 0.11301207542419434, 0.11303400993347168, 0.11304402351379395, 0.11305093765258789, 0.1130530834197998, 0.11306905746459961, 0.11307001113891602, 0.11312985420227051, 0.11313390731811523, 0.11317706108093262, 0.11319088935852051, 0.11319708824157715, 0.1132209300994873, 0.11322307586669922, 0.11323404312133789, 0.11324000358581543, 0.1132659912109375, 0.11326909065246582, 0.11327695846557617, 0.11329007148742676, 0.11330604553222656, 0.11334896087646484, 0.11339402198791504, 0.11340498924255371, 0.11342096328735352, 0.11347198486328125, 0.11355090141296387, 0.11356282234191895, 0.11356902122497559, 0.11361217498779297, 0.11362290382385254, 0.11362814903259277, 0.11369895935058594, 0.11371397972106934, 0.11372613906860352, 0.11376118659973145, 0.11377692222595215, 0.1138300895690918, 0.11383199691772461, 0.11389994621276855, 0.11390805244445801, 0.11390995979309082, 0.11390995979309082, 0.11391496658325195, 0.11395406723022461, 0.11400008201599121, 0.11401796340942383, 0.11402511596679688, 0.11403012275695801, 0.11410808563232422, 0.1141510009765625, 0.1141810417175293, 0.11423587799072266, 0.11424016952514648, 0.11424088478088379, 0.11424994468688965, 0.11429405212402344, 0.11436319351196289, 0.11436986923217773, 0.11437511444091797, 0.1144568920135498, 0.11456584930419922, 0.1145789623260498, 0.1145930290222168, 0.11464309692382812, 0.11469292640686035, 0.11476016044616699, 0.11478781700134277, 0.11481118202209473, 0.11484885215759277, 0.11485600471496582, 0.11500310897827148, 0.11504006385803223, 0.1150507926940918, 0.11518383026123047, 0.11528182029724121, 0.11551523208618164, 0.11553001403808594, 0.11555695533752441, 0.11570000648498535, 0.11572003364562988, 0.11572599411010742, 0.11586284637451172, 0.11594605445861816, 0.11613297462463379, 0.11614203453063965, 0.11621904373168945, 0.11627078056335449, 0.11630392074584961, 0.11632800102233887, 0.11633801460266113, 0.11634397506713867, 0.11636090278625488, 0.11636805534362793, 0.11637997627258301, 0.11640286445617676, 0.11643314361572266, 0.11644887924194336, 0.1164858341217041, 0.11648797988891602, 0.11656618118286133, 0.11661100387573242, 0.11671996116638184, 0.1168050765991211, 0.11694097518920898, 0.11705279350280762, 0.1171410083770752, 0.11715507507324219, 0.11717891693115234, 0.11724400520324707, 0.11730813980102539, 0.11734986305236816, 0.11740517616271973, 0.11744093894958496, 0.11747503280639648, 0.11749601364135742, 0.11752796173095703, 0.11752820014953613, 0.11757493019104004, 0.11766695976257324, 0.11774182319641113, 0.11774492263793945, 0.11780214309692383, 0.11783814430236816, 0.11796092987060547, 0.11805510520935059, 0.1180570125579834, 0.1180880069732666, 0.11810588836669922, 0.11812782287597656, 0.11813998222351074, 0.11826610565185547, 0.1183779239654541, 0.11839509010314941, 0.11844897270202637, 0.11857795715332031, 0.1185920238494873, 0.11860895156860352, 0.11861491203308105, 0.1187279224395752, 0.1187889575958252, 0.11881089210510254, 0.11885619163513184, 0.11897397041320801, 0.11909103393554688, 0.1191098690032959, 0.11911702156066895, 0.11940288543701172, 0.11942791938781738, 0.11943602561950684, 0.11945486068725586, 0.1195991039276123, 0.11964797973632812, 0.11974310874938965, 0.11988115310668945, 0.11992311477661133, 0.12013792991638184, 0.12059807777404785, 0.12060284614562988, 0.12103796005249023, 0.12110400199890137, 0.12135505676269531, 0.12144112586975098, 0.1214900016784668, 0.12150907516479492, 0.12163996696472168, 0.1218419075012207, 0.12185096740722656, 0.12194299697875977, 0.1220240592956543, 0.12209391593933105, 0.12221312522888184, 0.12222099304199219, 0.1222999095916748, 0.1223459243774414, 0.12238597869873047, 0.12241101264953613, 0.12242794036865234, 0.12252187728881836, 0.12258601188659668, 0.12259888648986816, 0.12282896041870117, 0.12285590171813965, 0.12299203872680664, 0.12301397323608398, 0.12312197685241699, 0.12318801879882812, 0.12354397773742676, 0.12376117706298828, 0.12381196022033691, 0.12390398979187012, 0.12411999702453613, 0.1241769790649414, 0.12426900863647461, 0.12427401542663574, 0.12468814849853516, 0.12475705146789551, 0.12505602836608887, 0.12526416778564453, 0.1253972053527832, 0.12567996978759766, 0.12569689750671387, 0.12603998184204102, 0.12616491317749023, 0.1271209716796875, 0.12712788581848145, 0.12717604637145996, 0.1274409294128418, 0.12746286392211914, 0.12760686874389648, 0.12838506698608398, 0.12899494171142578, 0.1292409896850586, 0.12987518310546875, 0.12990379333496094, 0.13130497932434082, 0.1313619613647461, 0.13231396675109863, 0.1334669589996338, 0.13535499572753906, 0.14399385452270508, 0.16040682792663574, 0.16089797019958496, 0.16294503211975098, 0.16382884979248047, 0.1667940616607666, 0.17123699188232422, 0.17270517349243164, 0.17334914207458496]</t>
+  </si>
+  <si>
+    <t>[0.11208796501159668, 0.11211109161376953, 0.11231112480163574, 0.11233210563659668, 0.11236906051635742, 0.11268305778503418, 0.11294198036193848, 0.11304211616516113, 0.11324501037597656, 0.11327600479125977, 0.11329507827758789, 0.11353015899658203, 0.11362195014953613, 0.11371302604675293, 0.1137690544128418, 0.11382484436035156, 0.11454010009765625, 0.11687088012695312, 0.11694693565368652, 0.11695194244384766, 0.11718511581420898, 0.11720705032348633, 0.11732816696166992, 0.11749601364135742, 0.11757302284240723, 0.11758780479431152, 0.11759090423583984, 0.11766600608825684, 0.11769485473632812, 0.1177060604095459, 0.11771678924560547, 0.11772298812866211, 0.11782312393188477, 0.11782503128051758, 0.11786699295043945, 0.11788201332092285, 0.11788606643676758, 0.11791300773620605, 0.11793398857116699, 0.11796307563781738, 0.11797595024108887, 0.11797809600830078, 0.11798381805419922, 0.11803793907165527, 0.11804080009460449, 0.11805200576782227, 0.11806416511535645, 0.11806893348693848, 0.11809897422790527, 0.11811590194702148, 0.11821889877319336, 0.1182548999786377, 0.11826801300048828, 0.11828899383544922, 0.11831021308898926, 0.11831188201904297, 0.11831998825073242, 0.11832094192504883, 0.11835908889770508, 0.11846208572387695, 0.1184990406036377, 0.11852002143859863, 0.1185297966003418, 0.11855411529541016, 0.11856389045715332, 0.11858296394348145, 0.11861705780029297, 0.11862707138061523, 0.11862897872924805, 0.11863088607788086, 0.11864590644836426, 0.11866188049316406, 0.11872410774230957, 0.1187291145324707, 0.11878299713134766, 0.11879396438598633, 0.11881017684936523, 0.11882281303405762, 0.11883187294006348, 0.11885786056518555, 0.11886000633239746, 0.1188650131225586, 0.11896014213562012, 0.1190040111541748, 0.11900901794433594, 0.11904215812683105, 0.11910200119018555, 0.11911892890930176, 0.11928582191467285, 0.11940693855285645, 0.11942005157470703, 0.11953210830688477, 0.11963486671447754, 0.11996102333068848, 0.12016677856445312, 0.12027192115783691, 0.12066006660461426, 0.12173104286193848, 0.12188100814819336, 0.12190103530883789, 0.1219182014465332, 0.12197494506835938, 0.1219940185546875, 0.12208890914916992, 0.12210392951965332, 0.12216591835021973, 0.12220501899719238, 0.12221193313598633, 0.12222981452941895, 0.12224411964416504, 0.12224912643432617, 0.12228608131408691, 0.12229681015014648, 0.1223001480102539, 0.12230300903320312, 0.12233209609985352, 0.12237119674682617, 0.12240219116210938, 0.12241816520690918, 0.12248015403747559, 0.12248396873474121, 0.12249207496643066, 0.12249302864074707, 0.12249493598937988, 0.12254595756530762, 0.12255501747131348, 0.12258410453796387, 0.12266778945922852, 0.12266921997070312, 0.12273406982421875, 0.12274003028869629, 0.12274003028869629, 0.12274503707885742, 0.12274789810180664, 0.1227729320526123, 0.12278103828430176, 0.12279510498046875, 0.12284207344055176, 0.12284994125366211, 0.12288498878479004, 0.12289285659790039, 0.12291288375854492, 0.12292909622192383, 0.12295103073120117, 0.12295103073120117, 0.12297201156616211, 0.12299609184265137, 0.12300300598144531, 0.12302589416503906, 0.12302994728088379, 0.12307095527648926, 0.12310314178466797, 0.12310600280761719, 0.12311482429504395, 0.12314915657043457, 0.12315201759338379, 0.12315487861633301, 0.12317991256713867, 0.12320518493652344, 0.12321090698242188, 0.12325119972229004, 0.12333083152770996, 0.1233360767364502, 0.12336397171020508, 0.12340998649597168, 0.12341499328613281, 0.12342405319213867, 0.12343502044677734, 0.12343692779541016, 0.12346506118774414, 0.12349891662597656, 0.12351703643798828, 0.12355899810791016, 0.1235659122467041, 0.12360191345214844, 0.12360787391662598, 0.12361693382263184, 0.12365007400512695, 0.12368106842041016, 0.12369108200073242, 0.12370681762695312, 0.12372398376464844, 0.12372589111328125, 0.12372779846191406, 0.12373709678649902, 0.12373805046081543, 0.12373995780944824, 0.12374496459960938, 0.12375211715698242, 0.1237630844116211, 0.1237640380859375, 0.12378287315368652, 0.12382698059082031, 0.12383008003234863, 0.12386488914489746, 0.12391996383666992, 0.12392497062683105, 0.12393689155578613, 0.12395596504211426, 0.12402796745300293, 0.12402987480163574, 0.12403607368469238, 0.12405109405517578, 0.12405109405517578, 0.12407088279724121, 0.12408614158630371, 0.12413406372070312, 0.12414002418518066, 0.12414908409118652, 0.12415409088134766, 0.1241769790649414, 0.12417721748352051, 0.12417817115783691, 0.12418699264526367, 0.1242361068725586, 0.1242361068725586, 0.1242520809173584, 0.1243278980255127, 0.12434506416320801, 0.12434506416320801, 0.1244361400604248, 0.12444496154785156, 0.12449979782104492, 0.12451791763305664, 0.12453103065490723, 0.12462902069091797, 0.12469100952148438, 0.1246941089630127, 0.12478899955749512, 0.12484502792358398, 0.12511491775512695, 0.12530899047851562, 0.1253950595855713, 0.1254110336303711, 0.12541794776916504, 0.12544798851013184, 0.12546992301940918, 0.12567806243896484, 0.12587308883666992, 0.1258831024169922, 0.1262378692626953, 0.12664103507995605, 0.12665987014770508, 0.12674999237060547, 0.12677502632141113, 0.12683486938476562, 0.12689805030822754, 0.12691307067871094, 0.1269218921661377, 0.12700200080871582, 0.12700891494750977, 0.12706589698791504, 0.12708711624145508, 0.1270911693572998, 0.1271510124206543, 0.1271979808807373, 0.12737202644348145, 0.12739109992980957, 0.1273970603942871, 0.12739801406860352, 0.12741804122924805, 0.12741899490356445, 0.1274399757385254, 0.12745881080627441, 0.1274869441986084, 0.12749791145324707, 0.12752413749694824, 0.12752985954284668, 0.1275310516357422, 0.12754392623901367, 0.12755799293518066, 0.12757205963134766, 0.12765097618103027, 0.12765884399414062, 0.12767696380615234, 0.1276988983154297, 0.1277010440826416, 0.12770986557006836, 0.12778115272521973, 0.1278378963470459, 0.12786412239074707, 0.12787485122680664, 0.12790703773498535, 0.12792110443115234, 0.12792706489562988, 0.12794113159179688, 0.12796616554260254, 0.12796688079833984, 0.12797784805297852, 0.12803888320922852, 0.12803888320922852, 0.12804317474365234, 0.12805891036987305, 0.1280689239501953, 0.1280810832977295, 0.1280839443206787, 0.1280839443206787, 0.12808895111083984, 0.1280958652496338, 0.1280970573425293, 0.12811613082885742, 0.12811613082885742, 0.12812089920043945, 0.12815499305725098, 0.1281571388244629, 0.12816596031188965, 0.12817907333374023, 0.12818217277526855, 0.1281890869140625, 0.12820196151733398, 0.1282041072845459, 0.12821507453918457, 0.12821602821350098, 0.12822508811950684, 0.1282360553741455, 0.12824392318725586, 0.12827610969543457, 0.12830400466918945, 0.12832188606262207, 0.12837910652160645, 0.12839317321777344, 0.12839698791503906, 0.12840914726257324, 0.12841105461120605, 0.128432035446167, 0.1284351348876953, 0.12844085693359375, 0.12844586372375488, 0.1284489631652832, 0.12845587730407715, 0.12845706939697266, 0.12847113609313965, 0.12848496437072754, 0.1285099983215332, 0.12854886054992676, 0.12855195999145508, 0.1285569667816162, 0.1285569667816162, 0.1285710334777832, 0.12857294082641602, 0.12857508659362793, 0.12859511375427246, 0.12861013412475586, 0.12861204147338867, 0.1286180019378662, 0.1286180019378662, 0.1286451816558838, 0.12865114212036133, 0.1286602020263672, 0.12866806983947754, 0.12867093086242676, 0.12868595123291016, 0.12871384620666504, 0.12871599197387695, 0.12874698638916016, 0.1287670135498047, 0.1288139820098877, 0.12881898880004883, 0.12883710861206055, 0.12887287139892578, 0.1288759708404541, 0.1288762092590332, 0.12888288497924805, 0.12888312339782715, 0.1289050579071045, 0.12893390655517578, 0.12897300720214844, 0.12899398803710938, 0.1289968490600586, 0.12900090217590332, 0.12900209426879883, 0.12900495529174805, 0.12905311584472656, 0.1290907859802246, 0.12911295890808105, 0.1291351318359375, 0.12914395332336426, 0.12915492057800293, 0.12916111946105957, 0.12920594215393066, 0.12921404838562012, 0.1292431354522705, 0.12927722930908203, 0.12928318977355957, 0.12929105758666992, 0.1293179988861084, 0.12932085990905762, 0.12932610511779785, 0.12932801246643066, 0.1293470859527588, 0.12937617301940918, 0.12941288948059082, 0.12945985794067383, 0.12948393821716309, 0.12952113151550293, 0.12955403327941895, 0.12955498695373535, 0.12957000732421875, 0.12965106964111328, 0.1296539306640625, 0.1296839714050293, 0.12969589233398438, 0.129713773727417, 0.1297159194946289, 0.12979793548583984, 0.12980103492736816, 0.12987399101257324, 0.12990999221801758, 0.12993192672729492, 0.13001585006713867, 0.13002896308898926, 0.13003087043762207, 0.13007807731628418, 0.13013100624084473, 0.13019800186157227, 0.13033103942871094, 0.13040518760681152, 0.13051486015319824, 0.13055682182312012, 0.13058781623840332, 0.1306779384613037, 0.13074707984924316, 0.13074707984924316, 0.13085484504699707, 0.13091707229614258, 0.13130712509155273, 0.13132596015930176, 0.1315140724182129, 0.13151812553405762, 0.1315629482269287, 0.13163399696350098, 0.13165903091430664, 0.13174200057983398, 0.13196802139282227, 0.13200807571411133, 0.13205194473266602, 0.13217616081237793, 0.1321871280670166, 0.13225388526916504, 0.13228678703308105, 0.1323840618133545, 0.13238811492919922, 0.13240790367126465, 0.13243484497070312, 0.13249802589416504, 0.13254094123840332, 0.13254404067993164, 0.13256096839904785, 0.13256287574768066, 0.13259196281433105, 0.13266205787658691, 0.1326911449432373, 0.1327509880065918, 0.1327829360961914, 0.1328139305114746, 0.13285398483276367, 0.13286399841308594, 0.1328749656677246, 0.13292503356933594, 0.13292598724365234, 0.13294005393981934, 0.13294315338134766, 0.13296294212341309, 0.13304710388183594, 0.13307690620422363, 0.13307690620422363, 0.13308095932006836, 0.13308310508728027, 0.1331028938293457, 0.13312292098999023, 0.13314604759216309, 0.13317298889160156, 0.13319802284240723, 0.1332089900970459, 0.13321399688720703, 0.13329815864562988, 0.13330316543579102, 0.1333479881286621, 0.13335013389587402, 0.1333620548248291, 0.13337993621826172, 0.13338899612426758, 0.13339495658874512, 0.13339996337890625, 0.13341784477233887, 0.13341903686523438, 0.13343286514282227, 0.13349199295043945, 0.13349294662475586, 0.13349604606628418, 0.1334991455078125, 0.133558988571167, 0.13356804847717285, 0.1335740089416504, 0.13364601135253906, 0.13371896743774414, 0.13372087478637695, 0.13373708724975586, 0.13379311561584473, 0.13381481170654297, 0.13381695747375488, 0.13385701179504395, 0.13388991355895996, 0.13389301300048828, 0.13390111923217773, 0.1339108943939209, 0.13393020629882812, 0.13393878936767578, 0.13395214080810547, 0.13396310806274414, 0.13406014442443848, 0.1340639591217041, 0.13407206535339355, 0.13408589363098145, 0.13410305976867676, 0.1341109275817871, 0.13411688804626465, 0.13414382934570312, 0.13415908813476562, 0.13418197631835938, 0.13423585891723633, 0.13423585891723633, 0.13434100151062012, 0.13437414169311523, 0.13437891006469727, 0.13439393043518066, 0.13443899154663086, 0.13462114334106445, 0.13471508026123047, 0.13472604751586914, 0.13476204872131348, 0.1347970962524414, 0.1347970962524414, 0.13488507270812988, 0.13498401641845703, 0.13506293296813965, 0.13508987426757812, 0.13517403602600098, 0.1352081298828125, 0.13523483276367188, 0.13534188270568848, 0.13536500930786133, 0.13540911674499512, 0.13541197776794434, 0.13542604446411133, 0.1355760097503662, 0.13565897941589355, 0.13575506210327148, 0.1357579231262207, 0.13576006889343262, 0.13591504096984863, 0.1359879970550537, 0.13602089881896973, 0.13603615760803223, 0.13625097274780273, 0.1363081932067871, 0.13633513450622559, 0.13656878471374512, 0.1366109848022461, 0.1367340087890625, 0.1368238925933838, 0.13684988021850586, 0.13686513900756836, 0.13690876960754395, 0.1369152069091797, 0.13720989227294922, 0.13723111152648926, 0.13729286193847656, 0.13746190071105957, 0.13751602172851562, 0.1377110481262207, 0.1377251148223877, 0.13773703575134277, 0.13775205612182617, 0.13782715797424316, 0.13800501823425293, 0.1380748748779297, 0.13808202743530273, 0.13809895515441895, 0.1381089687347412, 0.13820505142211914, 0.1383199691772461, 0.13842105865478516, 0.13846707344055176, 0.13849806785583496, 0.13859200477600098, 0.13861489295959473, 0.13862085342407227, 0.138671875, 0.13872480392456055, 0.13873004913330078, 0.13885116577148438, 0.1388540267944336, 0.1388700008392334, 0.13887906074523926, 0.1389601230621338, 0.13901686668395996, 0.13925695419311523, 0.13925790786743164, 0.13929200172424316, 0.13954806327819824, 0.13979792594909668, 0.1398019790649414, 0.1398789882659912, 0.14020085334777832, 0.14039206504821777, 0.14042901992797852, 0.14047694206237793, 0.1405019760131836, 0.14055609703063965, 0.14077115058898926, 0.1408710479736328, 0.14090895652770996, 0.1410679817199707, 0.14113593101501465, 0.14124202728271484, 0.1412980556488037, 0.14152884483337402, 0.14172601699829102, 0.14181780815124512, 0.14182305335998535, 0.14186596870422363, 0.14194393157958984, 0.14214301109313965, 0.14220905303955078, 0.1422581672668457, 0.14253592491149902, 0.14277195930480957, 0.14287900924682617, 0.14290595054626465, 0.1429300308227539, 0.14296388626098633, 0.1430339813232422, 0.14319086074829102, 0.14327287673950195, 0.143326997756958, 0.1434328556060791, 0.14355111122131348, 0.1436309814453125, 0.14363598823547363, 0.14383602142333984, 0.14389586448669434, 0.14398503303527832, 0.14421701431274414, 0.14427900314331055, 0.14433693885803223, 0.14435887336730957, 0.1446528434753418, 0.14481592178344727, 0.1451730728149414, 0.1452620029449463, 0.1452629566192627, 0.14535284042358398, 0.1454029083251953, 0.1454150676727295, 0.14565801620483398, 0.14566397666931152, 0.14573407173156738, 0.1457350254058838, 0.14574193954467773, 0.14583897590637207, 0.14584994316101074, 0.14589595794677734, 0.1459331512451172, 0.14607691764831543, 0.14621210098266602, 0.14659500122070312, 0.1466081142425537, 0.14688801765441895, 0.1470041275024414, 0.14713215827941895, 0.14737892150878906, 0.14751601219177246, 0.14757585525512695, 0.1475989818572998, 0.14766693115234375, 0.14787507057189941, 0.14800405502319336, 0.14810490608215332, 0.14819717407226562, 0.14823412895202637, 0.14824509620666504, 0.14833402633666992, 0.14848709106445312, 0.148665189743042, 0.14874792098999023, 0.1488020420074463, 0.14892220497131348, 0.14895081520080566, 0.1489720344543457, 0.14931893348693848, 0.14936399459838867, 0.14942288398742676, 0.14944100379943848, 0.14963197708129883, 0.14966297149658203, 0.14980578422546387, 0.1499340534210205, 0.14993882179260254, 0.15012502670288086, 0.15029692649841309, 0.15125679969787598, 0.1513078212738037, 0.15133309364318848, 0.1513810157775879, 0.1514720916748047, 0.15147995948791504, 0.15152382850646973, 0.15169000625610352, 0.15174198150634766, 0.15176796913146973, 0.1518559455871582, 0.1523730754852295, 0.1523730754852295, 0.1525249481201172, 0.15285205841064453, 0.15286707878112793, 0.15299296379089355, 0.15303301811218262, 0.15323090553283691, 0.1532909870147705, 0.15340805053710938, 0.15345978736877441, 0.15346407890319824, 0.15349221229553223, 0.1535189151763916, 0.15361785888671875, 0.1536850929260254, 0.1539630889892578, 0.15400290489196777, 0.15408802032470703, 0.15421009063720703, 0.1542520523071289, 0.15429115295410156, 0.15432190895080566, 0.15437817573547363, 0.15446805953979492, 0.15467500686645508, 0.1547257900238037, 0.1547260284423828, 0.15480709075927734, 0.15491199493408203, 0.15494990348815918, 0.1549670696258545, 0.15522503852844238, 0.15525507926940918, 0.15528082847595215, 0.15532708168029785, 0.15547394752502441, 0.15550899505615234, 0.15569782257080078, 0.1560380458831787, 0.1560840606689453, 0.15631318092346191, 0.156541109085083, 0.1567678451538086, 0.15687799453735352, 0.15713286399841309, 0.15723299980163574, 0.15723490715026855, 0.15745902061462402, 0.15750384330749512, 0.15770602226257324, 0.15802597999572754, 0.15810203552246094, 0.158156156539917, 0.15816497802734375, 0.1582190990447998, 0.15823578834533691, 0.15826797485351562, 0.15835309028625488, 0.15839290618896484, 0.1585381031036377, 0.15855884552001953, 0.1586000919342041, 0.1586441993713379, 0.15871405601501465, 0.15875887870788574, 0.1589369773864746, 0.15897798538208008, 0.1590709686279297, 0.15918493270874023, 0.15928292274475098, 0.15935897827148438, 0.15939617156982422, 0.1596059799194336, 0.15963101387023926, 0.15975308418273926, 0.15983200073242188, 0.1598520278930664, 0.16008615493774414, 0.1601579189300537, 0.16022515296936035, 0.16023015975952148, 0.16027617454528809, 0.16028618812561035, 0.16044116020202637, 0.16053390502929688, 0.16063284873962402, 0.16066408157348633, 0.16081690788269043, 0.16087603569030762, 0.16091513633728027, 0.16094183921813965, 0.1610109806060791, 0.16104888916015625, 0.16106295585632324, 0.16109204292297363, 0.16111183166503906, 0.16118502616882324, 0.16118907928466797, 0.16118979454040527, 0.16128802299499512, 0.16142702102661133, 0.16163182258605957, 0.16179203987121582, 0.16184091567993164, 0.16184401512145996, 0.16216182708740234, 0.1621689796447754, 0.1621711254119873, 0.16223597526550293, 0.162276029586792, 0.1622769832611084, 0.1623528003692627, 0.1623539924621582, 0.1623859405517578, 0.16248798370361328, 0.16255998611450195, 0.16266894340515137, 0.16269898414611816, 0.1627500057220459, 0.16278696060180664, 0.1630558967590332, 0.16308808326721191, 0.16318702697753906, 0.1633319854736328, 0.16333293914794922, 0.16349005699157715, 0.16354608535766602, 0.16372895240783691, 0.16375184059143066, 0.16376805305480957, 0.16390395164489746, 0.16398310661315918, 0.1642301082611084, 0.16428112983703613, 0.16429901123046875, 0.1643228530883789, 0.16437292098999023, 0.16445422172546387, 0.16458797454833984, 0.16462492942810059, 0.16495394706726074, 0.16504812240600586, 0.16510581970214844, 0.16515898704528809, 0.16524696350097656, 0.16543793678283691, 0.16553115844726562, 0.16559696197509766, 0.16563892364501953, 0.16574907302856445, 0.16582512855529785, 0.16604900360107422, 0.1660628318786621, 0.16610097885131836, 0.16620516777038574, 0.16654419898986816, 0.16664600372314453, 0.16674304008483887, 0.16674399375915527, 0.16686797142028809, 0.16692900657653809, 0.16696596145629883, 0.16707491874694824, 0.16708803176879883, 0.16723990440368652, 0.16730499267578125, 0.1676788330078125, 0.1677560806274414, 0.16786909103393555, 0.16787004470825195, 0.16790986061096191, 0.16819214820861816, 0.1681978702545166, 0.168349027633667, 0.16855907440185547, 0.16857600212097168, 0.1688680648803711, 0.1690969467163086, 0.16922998428344727, 0.16923213005065918, 0.1694800853729248, 0.16961288452148438, 0.16976594924926758, 0.17009687423706055, 0.17014384269714355, 0.17031288146972656, 0.17037296295166016, 0.17046618461608887, 0.17052507400512695, 0.1706240177154541, 0.17069602012634277, 0.17101097106933594, 0.17103886604309082, 0.1710948944091797, 0.17126202583312988, 0.17129898071289062, 0.17133808135986328, 0.1713409423828125, 0.1721649169921875, 0.17240095138549805, 0.17241287231445312, 0.1724708080291748, 0.17283201217651367, 0.17325806617736816, 0.17333602905273438, 0.17336106300354004, 0.17346692085266113, 0.17376303672790527, 0.1739192008972168, 0.1745920181274414, 0.1750330924987793, 0.17520594596862793, 0.1752328872680664, 0.17540192604064941, 0.17578721046447754, 0.17586493492126465, 0.17647695541381836, 0.17659997940063477, 0.17663002014160156, 0.17667102813720703, 0.17679309844970703, 0.17858409881591797, 0.17890596389770508, 0.17911386489868164, 0.1792290210723877, 0.17924213409423828, 0.17969584465026855, 0.17970585823059082, 0.18022704124450684, 0.18066191673278809, 0.18090200424194336, 0.18108105659484863, 0.18126797676086426, 0.18160510063171387, 0.1819009780883789, 0.18210482597351074, 0.1821739673614502, 0.18244099617004395, 0.18269610404968262, 0.18321800231933594, 0.18361401557922363, 0.18380308151245117, 0.18494606018066406, 0.18506193161010742, 0.18533897399902344, 0.18534493446350098, 0.18564605712890625, 0.18589401245117188, 0.18669605255126953, 0.19023799896240234, 0.19181394577026367, 0.19196581840515137, 0.1923542022705078, 0.19280791282653809, 0.19312596321105957, 0.19379186630249023, 0.1942131519317627, 0.19519710540771484, 0.1957108974456787, 0.1962289810180664, 0.19668793678283691, 0.19671106338500977, 0.19676494598388672, 0.1978318691253662, 0.1989600658416748, 0.19988107681274414, 0.20244789123535156]</t>
+  </si>
+  <si>
+    <t>[0.07880592346191406, 0.07882499694824219, 0.07883405685424805, 0.07885003089904785, 0.07887101173400879, 0.07888197898864746, 0.07888603210449219, 0.07889294624328613, 0.07891583442687988, 0.07894301414489746, 0.07899308204650879, 0.07899689674377441, 0.07901787757873535, 0.07903385162353516, 0.07906198501586914, 0.0790870189666748, 0.07921600341796875, 0.07929801940917969, 0.07946491241455078, 0.07952213287353516, 0.07954096794128418, 0.07955503463745117, 0.07958006858825684, 0.07962894439697266, 0.07966804504394531, 0.07969498634338379, 0.07971692085266113, 0.07973909378051758, 0.07976198196411133, 0.0797719955444336, 0.07980990409851074, 0.07987689971923828, 0.07988405227661133, 0.07988595962524414, 0.07992291450500488, 0.07994699478149414, 0.07996201515197754, 0.07996511459350586, 0.07998514175415039, 0.08000302314758301, 0.0800180435180664, 0.08001899719238281, 0.0800318717956543, 0.0800478458404541, 0.0800478458404541, 0.08004903793334961, 0.08009099960327148, 0.08014202117919922, 0.08015298843383789, 0.08020210266113281, 0.0802299976348877, 0.08024001121520996, 0.08024096488952637, 0.08024811744689941, 0.08028292655944824, 0.08029699325561523, 0.0803079605102539, 0.08037185668945312, 0.0803828239440918, 0.08043408393859863, 0.08043813705444336, 0.08043909072875977, 0.08044981956481934, 0.08050894737243652, 0.08053112030029297, 0.08053898811340332, 0.08060312271118164, 0.08063912391662598, 0.08064794540405273, 0.0806879997253418, 0.08073115348815918, 0.08077216148376465, 0.08079099655151367, 0.08084988594055176, 0.08085393905639648, 0.08085799217224121, 0.08088302612304688, 0.08092999458312988, 0.08094406127929688, 0.08095812797546387, 0.08096694946289062, 0.08098196983337402, 0.08101391792297363, 0.08102083206176758, 0.08102297782897949, 0.08103513717651367, 0.08107590675354004, 0.08110499382019043, 0.08110618591308594, 0.08110904693603516, 0.08116888999938965, 0.0812370777130127, 0.08124089241027832, 0.08126688003540039, 0.08130288124084473, 0.08136487007141113, 0.08138704299926758, 0.08147215843200684, 0.08164381980895996, 0.0816650390625, 0.08210301399230957, 0.08212804794311523, 0.08238816261291504, 0.0825350284576416, 0.08260321617126465, 0.08266210556030273, 0.08300495147705078, 0.0833749771118164, 0.08341693878173828, 0.08342885971069336, 0.08351612091064453, 0.08351707458496094, 0.0836038589477539, 0.08361315727233887, 0.08363199234008789, 0.08367300033569336, 0.08367395401000977, 0.08367586135864258, 0.08368492126464844, 0.08370280265808105, 0.0837249755859375, 0.08373093605041504, 0.0837409496307373, 0.08374810218811035, 0.08376598358154297, 0.0837709903717041, 0.08380794525146484, 0.08381915092468262, 0.08385801315307617, 0.08386421203613281, 0.08386492729187012, 0.08388280868530273, 0.08388400077819824, 0.08389091491699219, 0.08389115333557129, 0.08389806747436523, 0.08390593528747559, 0.08391213417053223, 0.08391904830932617, 0.08393096923828125, 0.08395600318908691, 0.08396005630493164, 0.08398103713989258, 0.08398222923278809, 0.08399295806884766, 0.08399701118469238, 0.08400893211364746, 0.08401703834533691, 0.08403801918029785, 0.08405208587646484, 0.08406996726989746, 0.08407092094421387, 0.08407902717590332, 0.08409500122070312, 0.08409905433654785, 0.08410000801086426, 0.08410286903381348, 0.08410501480102539, 0.08410501480102539, 0.0841069221496582, 0.08411192893981934, 0.08412694931030273, 0.08413410186767578, 0.08414983749389648, 0.0841519832611084, 0.08415913581848145, 0.08416604995727539, 0.08417296409606934, 0.08420681953430176, 0.08420681953430176, 0.08420801162719727, 0.08420801162719727, 0.0842130184173584, 0.08422517776489258, 0.0842289924621582, 0.08423805236816406, 0.08424210548400879, 0.08424615859985352, 0.08425498008728027, 0.08427119255065918, 0.08427596092224121, 0.08428716659545898, 0.0842900276184082, 0.08431196212768555, 0.08432698249816895, 0.08432912826538086, 0.08432912826538086, 0.08433294296264648, 0.08436298370361328, 0.08436894416809082, 0.08437395095825195, 0.08437705039978027, 0.0843801498413086, 0.08438396453857422, 0.08439016342163086, 0.08439016342163086, 0.08439087867736816, 0.0843961238861084, 0.0844120979309082, 0.08441615104675293, 0.08443212509155273, 0.08443689346313477, 0.08445096015930176, 0.08445501327514648, 0.08446407318115234, 0.08447694778442383, 0.08449006080627441, 0.08449196815490723, 0.08449697494506836, 0.08449816703796387, 0.08450102806091309, 0.0845029354095459, 0.08450984954833984, 0.08451104164123535, 0.08451199531555176, 0.08451509475708008, 0.08452010154724121, 0.08452105522155762, 0.08452606201171875, 0.08452701568603516, 0.08453512191772461, 0.08453798294067383, 0.08454084396362305, 0.0845479965209961, 0.08455300331115723, 0.08457207679748535, 0.08457303047180176, 0.08457398414611816, 0.08457517623901367, 0.08457612991333008, 0.08458185195922852, 0.08458304405212402, 0.08460497856140137, 0.08460879325866699, 0.08462214469909668, 0.08463692665100098, 0.08464598655700684, 0.08465695381164551, 0.08466506004333496, 0.08466601371765137, 0.0846710205078125, 0.08467578887939453, 0.0847010612487793, 0.08470702171325684, 0.08472299575805664, 0.08472514152526855, 0.08474111557006836, 0.08474516868591309, 0.08475184440612793, 0.08475708961486816, 0.08475804328918457, 0.08477091789245605, 0.0847768783569336, 0.08477997779846191, 0.0847940444946289, 0.08479523658752441, 0.08480000495910645, 0.08480119705200195, 0.08480691909790039, 0.08480715751647949, 0.08481216430664062, 0.08481216430664062, 0.0848238468170166, 0.08484888076782227, 0.0848541259765625, 0.08487391471862793, 0.08487510681152344, 0.08489084243774414, 0.08489704132080078, 0.08490109443664551, 0.08491015434265137, 0.08491182327270508, 0.08491206169128418, 0.08491396903991699, 0.08492803573608398, 0.08493208885192871, 0.08493781089782715, 0.08494997024536133, 0.08495187759399414, 0.08495497703552246, 0.08495783805847168, 0.0849759578704834, 0.0849769115447998, 0.08497786521911621, 0.08498120307922363, 0.08499503135681152, 0.08499693870544434, 0.08500099182128906, 0.08500194549560547, 0.08501791954040527, 0.08504199981689453, 0.08504700660705566, 0.08508181571960449, 0.0850830078125, 0.08508610725402832, 0.08509111404418945, 0.08509302139282227, 0.08510398864746094, 0.08510494232177734, 0.08512187004089355, 0.08512210845947266, 0.08513498306274414, 0.08513593673706055, 0.08514904975891113, 0.08515095710754395, 0.08515214920043945, 0.08515810966491699, 0.08516192436218262, 0.08516192436218262, 0.08517193794250488, 0.0851738452911377, 0.08517909049987793, 0.08517909049987793, 0.0851898193359375, 0.08519291877746582, 0.08519601821899414, 0.0852060317993164, 0.08521199226379395, 0.08522701263427734, 0.08522701263427734, 0.08523392677307129, 0.08524703979492188, 0.08525300025939941, 0.08526182174682617, 0.08526301383972168, 0.08526992797851562, 0.0852811336517334, 0.08529901504516602, 0.08529901504516602, 0.08530092239379883, 0.08530402183532715, 0.08530807495117188, 0.08532476425170898, 0.08532905578613281, 0.08533406257629395, 0.08533692359924316, 0.08534097671508789, 0.0853419303894043, 0.08535313606262207, 0.0853581428527832, 0.08536005020141602, 0.08536195755004883, 0.08537697792053223, 0.08537793159484863, 0.0853891372680664, 0.08539915084838867, 0.08540987968444824, 0.0854179859161377, 0.0854179859161377, 0.0854191780090332, 0.08542799949645996, 0.08542895317077637, 0.08543801307678223, 0.08544707298278809, 0.08545804023742676, 0.08546113967895508, 0.08546710014343262, 0.08548092842102051, 0.08548498153686523, 0.08548808097839355, 0.08549904823303223, 0.08550310134887695, 0.08550596237182617, 0.08550906181335449, 0.08551597595214844, 0.08552408218383789, 0.0855250358581543, 0.08552694320678711, 0.08553004264831543, 0.08553194999694824, 0.08554291725158691, 0.08555006980895996, 0.08556199073791504, 0.08556604385375977, 0.08557510375976562, 0.08558297157287598, 0.08558797836303711, 0.08559989929199219, 0.08560395240783691, 0.08564996719360352, 0.08565211296081543, 0.08565998077392578, 0.0856781005859375, 0.08568406105041504, 0.0856928825378418, 0.08569693565368652, 0.08570098876953125, 0.08571290969848633, 0.08571600914001465, 0.08571600914001465, 0.08571982383728027, 0.08573102951049805, 0.08573389053344727, 0.08574414253234863, 0.08574700355529785, 0.08574914932250977, 0.0857539176940918, 0.08575701713562012, 0.08576416969299316, 0.08576703071594238, 0.08582091331481934, 0.08583307266235352, 0.08584904670715332, 0.08586907386779785, 0.08587193489074707, 0.0858919620513916, 0.08589696884155273, 0.08590102195739746, 0.0859079360961914, 0.08591294288635254, 0.08591604232788086, 0.08593106269836426, 0.0859379768371582, 0.08593893051147461, 0.08594608306884766, 0.08594799041748047, 0.08596014976501465, 0.08596587181091309, 0.085968017578125, 0.08597016334533691, 0.08597183227539062, 0.08597302436828613, 0.0859830379486084, 0.08599305152893066, 0.08600616455078125, 0.08602499961853027, 0.08603215217590332, 0.0860440731048584, 0.08604598045349121, 0.0860598087310791, 0.08607602119445801, 0.08608603477478027, 0.08609294891357422, 0.08609890937805176, 0.08609986305236816, 0.08610296249389648, 0.08611893653869629, 0.08612585067749023, 0.08616089820861816, 0.08616399765014648, 0.08617401123046875, 0.08619284629821777, 0.0861971378326416, 0.08619809150695801, 0.08624887466430664, 0.08625006675720215, 0.08625292778015137, 0.08625507354736328, 0.08625912666320801, 0.08626484870910645, 0.08627104759216309, 0.08627700805664062, 0.08628106117248535, 0.08628106117248535, 0.08629202842712402, 0.08629298210144043, 0.08632516860961914, 0.08632707595825195, 0.08637285232543945, 0.08638882637023926, 0.08639097213745117, 0.08639192581176758, 0.08639717102050781, 0.08639907836914062, 0.08640313148498535, 0.08643913269042969, 0.08647394180297852, 0.08649611473083496, 0.08649706840515137, 0.08650398254394531, 0.08650684356689453, 0.08652710914611816, 0.08656096458435059, 0.08658885955810547, 0.08663797378540039, 0.08664202690124512, 0.08667206764221191, 0.08667278289794922, 0.08669209480285645, 0.08669209480285645, 0.08672499656677246, 0.08674311637878418, 0.08676004409790039, 0.08680605888366699, 0.08684992790222168, 0.08686304092407227, 0.08692193031311035, 0.08698797225952148, 0.08700394630432129, 0.08702707290649414, 0.08702707290649414, 0.08704614639282227, 0.08705520629882812, 0.08705687522888184, 0.08710289001464844, 0.08712983131408691, 0.08713221549987793, 0.08716797828674316, 0.0871880054473877, 0.08725690841674805, 0.08726811408996582, 0.08728790283203125, 0.0873110294342041, 0.0873570442199707, 0.08738994598388672, 0.0875999927520752, 0.08760404586791992, 0.08766508102416992, 0.08771491050720215, 0.08778095245361328, 0.08787202835083008, 0.08789610862731934, 0.08793377876281738, 0.08796811103820801, 0.08798003196716309, 0.08798384666442871, 0.0880129337310791, 0.08803701400756836, 0.08806586265563965, 0.08809208869934082, 0.08815813064575195, 0.08821892738342285, 0.08827090263366699, 0.08827400207519531, 0.08827805519104004, 0.08832693099975586, 0.08833885192871094, 0.08834385871887207, 0.08838081359863281, 0.08839178085327148, 0.0883939266204834, 0.0883951187133789, 0.08839893341064453, 0.08844995498657227, 0.08846211433410645, 0.08850598335266113, 0.08852410316467285, 0.08858418464660645, 0.08858609199523926, 0.08864998817443848, 0.08867287635803223, 0.08867907524108887, 0.08868980407714844, 0.08869600296020508, 0.08869695663452148, 0.08870601654052734, 0.08872509002685547, 0.08873605728149414, 0.08874893188476562, 0.0887598991394043, 0.08877110481262207, 0.08877205848693848, 0.08883500099182129, 0.08883500099182129, 0.0888361930847168, 0.08886313438415527, 0.08887982368469238, 0.08890509605407715, 0.08890914916992188, 0.08892297744750977, 0.08892297744750977, 0.0889430046081543, 0.08894610404968262, 0.0889589786529541, 0.08896517753601074, 0.08897686004638672, 0.08898115158081055, 0.08898305892944336, 0.08899712562561035, 0.08900094032287598, 0.08907103538513184, 0.08908605575561523, 0.08909392356872559, 0.08910393714904785, 0.08911013603210449, 0.08911514282226562, 0.08913993835449219, 0.08914613723754883, 0.08915591239929199, 0.08920907974243164, 0.08922386169433594, 0.08923196792602539, 0.08927011489868164, 0.08933782577514648, 0.08933901786804199, 0.08935093879699707, 0.08935213088989258, 0.08935904502868652, 0.08936595916748047, 0.08937501907348633, 0.08937597274780273, 0.08938407897949219, 0.08941292762756348, 0.0894160270690918, 0.0894620418548584, 0.08946514129638672, 0.08950495719909668, 0.08950495719909668, 0.08950996398925781, 0.08951306343078613, 0.08951401710510254, 0.08951902389526367, 0.08953118324279785, 0.08953595161437988, 0.08955001831054688, 0.08956694602966309, 0.08958697319030762, 0.08958983421325684, 0.08960509300231934, 0.0896291732788086, 0.08963704109191895, 0.08964085578918457, 0.0896449089050293, 0.08965301513671875, 0.0896749496459961, 0.08970189094543457, 0.08973097801208496, 0.0897531509399414, 0.08975696563720703, 0.08976316452026367, 0.08978605270385742, 0.0897970199584961, 0.08982276916503906, 0.08985400199890137, 0.08986091613769531, 0.08986997604370117, 0.0898740291595459, 0.08987998962402344, 0.0898890495300293, 0.08989095687866211, 0.08991694450378418, 0.08992505073547363, 0.08992886543273926, 0.08993101119995117, 0.08994603157043457, 0.08995199203491211, 0.08995294570922852, 0.09001016616821289, 0.09003591537475586, 0.09004998207092285, 0.09005999565124512, 0.09007906913757324, 0.09008598327636719, 0.09009981155395508, 0.09011006355285645, 0.09011697769165039, 0.09012889862060547, 0.09013605117797852, 0.09014296531677246, 0.09015202522277832, 0.09018802642822266, 0.09020686149597168, 0.09021592140197754, 0.09021902084350586, 0.09023809432983398, 0.09026908874511719, 0.09027314186096191, 0.09027695655822754, 0.09030413627624512, 0.09033083915710449, 0.09033513069152832, 0.09035110473632812, 0.09035992622375488, 0.09037280082702637, 0.09041500091552734, 0.09041500091552734, 0.0904228687286377, 0.0904231071472168, 0.0904240608215332, 0.09043216705322266, 0.09043622016906738, 0.09044098854064941, 0.09044408798217773, 0.09045195579528809, 0.09045600891113281, 0.09050703048706055, 0.09053707122802734, 0.09056591987609863, 0.09057903289794922, 0.09058904647827148, 0.0905921459197998, 0.09060907363891602, 0.0906219482421875, 0.0906381607055664, 0.09065604209899902, 0.09066891670227051, 0.09068703651428223, 0.09069204330444336, 0.09072613716125488, 0.0907740592956543, 0.09078407287597656, 0.09080290794372559, 0.09080791473388672, 0.09081101417541504, 0.09081101417541504, 0.09081602096557617, 0.0908501148223877, 0.0908651351928711, 0.09087300300598145, 0.09090089797973633, 0.09090685844421387, 0.09090900421142578, 0.09091782569885254, 0.09093880653381348, 0.09095406532287598, 0.0909578800201416, 0.09097695350646973, 0.09097695350646973, 0.09103608131408691, 0.09107112884521484, 0.09111499786376953, 0.09113907814025879, 0.09116697311401367, 0.09116816520690918, 0.09119105339050293, 0.09119200706481934, 0.09121012687683105, 0.09122395515441895, 0.09122896194458008, 0.09126496315002441, 0.09126615524291992, 0.09126782417297363, 0.09128403663635254, 0.09128689765930176, 0.09133315086364746, 0.09136605262756348, 0.09137105941772461, 0.09138202667236328, 0.09143805503845215, 0.09144711494445801, 0.09144997596740723, 0.09145808219909668, 0.09150004386901855, 0.09151911735534668, 0.0915219783782959, 0.09161090850830078, 0.09171104431152344, 0.09171199798583984, 0.0917360782623291, 0.09174489974975586, 0.09175491333007812, 0.09177398681640625, 0.09177517890930176, 0.09179806709289551, 0.09181404113769531, 0.09183311462402344, 0.09188485145568848, 0.09192180633544922, 0.09198117256164551, 0.09203195571899414, 0.09203910827636719, 0.09215593338012695, 0.09225106239318848, 0.09233403205871582, 0.09244608879089355, 0.09254598617553711, 0.0926060676574707, 0.09282684326171875, 0.09288191795349121, 0.09302282333374023, 0.09309506416320801, 0.09310293197631836, 0.09318280220031738, 0.09325098991394043, 0.09326410293579102, 0.09329795837402344, 0.09330010414123535, 0.09332108497619629, 0.09343814849853516, 0.09344005584716797, 0.09349393844604492, 0.09350180625915527, 0.0935049057006836, 0.09355497360229492, 0.09356093406677246, 0.0936439037322998, 0.09365200996398926, 0.09366011619567871, 0.09368395805358887, 0.09371113777160645, 0.09372615814208984, 0.09373712539672852, 0.09380006790161133, 0.09382915496826172, 0.09385299682617188, 0.09388494491577148, 0.09390091896057129, 0.09396505355834961, 0.09396600723266602, 0.09398508071899414, 0.0939939022064209, 0.09400010108947754, 0.09402298927307129, 0.09403014183044434, 0.09413504600524902, 0.0941770076751709, 0.09417915344238281, 0.09420204162597656, 0.09422111511230469, 0.09422588348388672, 0.09424304962158203, 0.09428596496582031, 0.09428620338439941, 0.0943300724029541, 0.09433794021606445, 0.0943448543548584, 0.09437417984008789, 0.09437990188598633, 0.09439206123352051, 0.09439611434936523, 0.09442591667175293, 0.0944662094116211, 0.09448480606079102, 0.09449005126953125, 0.09450316429138184, 0.09452414512634277, 0.09454894065856934, 0.09455990791320801, 0.0945899486541748, 0.09459900856018066, 0.09460115432739258, 0.09461188316345215, 0.09462308883666992, 0.09462690353393555, 0.09464883804321289, 0.09466099739074707, 0.09469914436340332, 0.0947108268737793, 0.09477806091308594, 0.09478116035461426, 0.09478282928466797, 0.09483695030212402, 0.09485483169555664, 0.09485697746276855, 0.09487295150756836, 0.09490704536437988, 0.09491515159606934, 0.09496188163757324, 0.09498214721679688, 0.0950479507446289, 0.0950767993927002, 0.0950770378112793, 0.0950779914855957, 0.09508609771728516, 0.0950930118560791, 0.09511709213256836, 0.09513711929321289, 0.09514093399047852, 0.09519004821777344, 0.09519410133361816, 0.09523296356201172, 0.09523916244506836, 0.09526181221008301, 0.0953371524810791, 0.09535598754882812, 0.09543204307556152, 0.0954439640045166, 0.09551405906677246, 0.09562492370605469, 0.0956718921661377, 0.09567403793334961, 0.09567809104919434, 0.09580588340759277, 0.09583306312561035, 0.0958859920501709, 0.09590387344360352, 0.09593892097473145, 0.09593915939331055, 0.09594488143920898, 0.0959620475769043, 0.09600281715393066, 0.0960090160369873, 0.09602022171020508, 0.09607791900634766, 0.0960841178894043, 0.0961160659790039, 0.09613895416259766, 0.09616398811340332, 0.09616804122924805, 0.0962378978729248, 0.09623885154724121, 0.09637284278869629, 0.09648585319519043, 0.09650897979736328, 0.09653806686401367, 0.09665203094482422, 0.09669899940490723, 0.09670090675354004, 0.09672713279724121, 0.0967409610748291, 0.09677314758300781, 0.09677791595458984, 0.09700822830200195, 0.09709286689758301, 0.0972449779510498, 0.09733414649963379, 0.09751009941101074, 0.09753108024597168, 0.09754300117492676, 0.0975949764251709, 0.0975959300994873, 0.09763503074645996, 0.09763693809509277, 0.09771108627319336, 0.09771990776062012, 0.09792399406433105, 0.09802412986755371, 0.09809994697570801, 0.09816694259643555, 0.09820795059204102, 0.09825801849365234, 0.09826397895812988, 0.09840798377990723, 0.09850311279296875, 0.09854483604431152, 0.09862995147705078, 0.09907293319702148, 0.0992288589477539, 0.0992588996887207, 0.09926104545593262, 0.09928297996520996, 0.09929609298706055, 0.09943795204162598, 0.09946179389953613, 0.09949398040771484, 0.09965300559997559, 0.09967708587646484, 0.09978699684143066, 0.09984898567199707, 0.099884033203125, 0.09993100166320801, 0.10001587867736816, 0.10021615028381348, 0.10025191307067871, 0.10026001930236816, 0.10035586357116699, 0.10038900375366211, 0.10042405128479004, 0.10046911239624023, 0.1005549430847168, 0.1006159782409668, 0.10061907768249512, 0.10094213485717773, 0.10097002983093262, 0.1011199951171875, 0.10129594802856445, 0.10145902633666992, 0.10165810585021973, 0.10182714462280273, 0.10203790664672852, 0.1029350757598877, 0.10307598114013672, 0.10344099998474121, 0.10364079475402832, 0.1040029525756836, 0.10453104972839355, 0.10456991195678711, 0.10464787483215332, 0.1051177978515625, 0.10517597198486328, 0.10536599159240723, 0.10552501678466797, 0.10605001449584961, 0.10621094703674316, 0.10695695877075195, 0.10719585418701172, 0.10774612426757812, 0.10804510116577148, 0.10870194435119629, 0.10972404479980469, 0.11049604415893555, 0.11419105529785156, 0.1475820541381836, 0.15177297592163086, 0.15210914611816406, 0.1523289680480957, 0.15250897407531738, 0.15271496772766113, 0.1551799774169922, 0.15545201301574707]</t>
+  </si>
+  <si>
+    <t>[0.08759307861328125, 0.08773279190063477, 0.08870482444763184, 0.0888528823852539, 0.08938002586364746, 0.0894160270690918, 0.08948016166687012, 0.08954381942749023, 0.08964204788208008, 0.0896449089050293, 0.08968186378479004, 0.08978915214538574, 0.08979296684265137, 0.0897979736328125, 0.08980488777160645, 0.0898439884185791, 0.08985614776611328, 0.08986783027648926, 0.08987283706665039, 0.0899200439453125, 0.08994793891906738, 0.08995890617370605, 0.08999204635620117, 0.09002304077148438, 0.09003782272338867, 0.0900731086730957, 0.09020018577575684, 0.0902860164642334, 0.09033799171447754, 0.09033894538879395, 0.0903470516204834, 0.09043002128601074, 0.09043097496032715, 0.09043693542480469, 0.09045004844665527, 0.09046220779418945, 0.09051299095153809, 0.09052205085754395, 0.09060502052307129, 0.09065794944763184, 0.09069108963012695, 0.09072208404541016, 0.0907289981842041, 0.09081506729125977, 0.090911865234375, 0.09091997146606445, 0.09104490280151367, 0.09111213684082031, 0.09114480018615723, 0.09115886688232422, 0.09117007255554199, 0.09117794036865234, 0.09121203422546387, 0.09125304222106934, 0.0912630558013916, 0.09133005142211914, 0.09135818481445312, 0.09137797355651855, 0.0914008617401123, 0.09140205383300781, 0.09140515327453613, 0.09142303466796875, 0.0914299488067627, 0.0914309024810791, 0.09145092964172363, 0.09145188331604004, 0.09145498275756836, 0.09145903587341309, 0.09150409698486328, 0.09151005744934082, 0.09163403511047363, 0.09163808822631836, 0.09164309501647949, 0.09166789054870605, 0.09169316291809082, 0.09169483184814453, 0.0917048454284668, 0.09170985221862793, 0.09174489974975586, 0.09175610542297363, 0.09176492691040039, 0.09180593490600586, 0.0918278694152832, 0.09186601638793945, 0.09186601638793945, 0.09190917015075684, 0.09192681312561035, 0.09198307991027832, 0.09198617935180664, 0.0920259952545166, 0.09203290939331055, 0.09204292297363281, 0.09204483032226562, 0.0920569896697998, 0.09214115142822266, 0.0921640396118164, 0.09226608276367188, 0.09227180480957031, 0.09229111671447754, 0.09236001968383789, 0.09244012832641602, 0.09245705604553223, 0.0924990177154541, 0.09252214431762695, 0.09252786636352539, 0.09258008003234863, 0.09259319305419922, 0.09260082244873047, 0.09263110160827637, 0.09267783164978027, 0.09270596504211426, 0.09274411201477051, 0.09279417991638184, 0.09281206130981445, 0.09282493591308594, 0.09283900260925293, 0.09301018714904785, 0.09308004379272461, 0.09308600425720215, 0.09331703186035156, 0.09332394599914551, 0.09335494041442871, 0.09341597557067871, 0.09344482421875, 0.09352707862854004, 0.0936129093170166, 0.09371113777160645, 0.09372115135192871, 0.09383296966552734, 0.09384298324584961, 0.09391188621520996, 0.09391903877258301, 0.09394311904907227, 0.09403395652770996, 0.09404778480529785, 0.09409904479980469, 0.09418296813964844, 0.09420013427734375, 0.09421205520629883, 0.09421992301940918, 0.0942678451538086, 0.09434390068054199, 0.09434700012207031, 0.09434890747070312, 0.09434914588928223, 0.0943601131439209, 0.0944070816040039, 0.09442400932312012, 0.09443187713623047, 0.09443306922912598, 0.09444499015808105, 0.09446883201599121, 0.09447002410888672, 0.09448099136352539, 0.09448099136352539, 0.09451699256896973, 0.09452986717224121, 0.09457921981811523, 0.09461498260498047, 0.0946199893951416, 0.09462094306945801, 0.0946340560913086, 0.09464192390441895, 0.09465312957763672, 0.09467792510986328, 0.09468889236450195, 0.09469294548034668, 0.0947120189666748, 0.09481096267700195, 0.09481382369995117, 0.09483695030212402, 0.09486699104309082, 0.09487104415893555, 0.09487295150756836, 0.09487509727478027, 0.09487700462341309, 0.09488201141357422, 0.09489011764526367, 0.09489798545837402, 0.09489798545837402, 0.09491086006164551, 0.09491610527038574, 0.09492897987365723, 0.09492897987365723, 0.09496402740478516, 0.09496402740478516, 0.09498190879821777, 0.09499096870422363, 0.09499597549438477, 0.095001220703125, 0.09500789642333984, 0.09501004219055176, 0.09502387046813965, 0.09502792358398438, 0.09503889083862305, 0.09504008293151855, 0.0950479507446289, 0.09504890441894531, 0.09505081176757812, 0.0950629711151123, 0.09506392478942871, 0.09508299827575684, 0.09509897232055664, 0.09510016441345215, 0.09511613845825195, 0.09512519836425781, 0.09512782096862793, 0.09513998031616211, 0.09514188766479492, 0.09514713287353516, 0.09514808654785156, 0.0951540470123291, 0.09516596794128418, 0.09519004821777344, 0.09519290924072266, 0.0951991081237793, 0.09522104263305664, 0.09524703025817871, 0.09524917602539062, 0.09525108337402344, 0.09525799751281738, 0.09526705741882324, 0.09526705741882324, 0.09527802467346191, 0.09528493881225586, 0.09528923034667969, 0.09530806541442871, 0.09531807899475098, 0.0953221321105957, 0.09533190727233887, 0.09535098075866699, 0.0953519344329834, 0.09536409378051758, 0.09537315368652344, 0.09539294242858887, 0.09539794921875, 0.09541201591491699, 0.09542298316955566, 0.09544110298156738, 0.09546589851379395, 0.09546995162963867, 0.09547090530395508, 0.09547185897827148, 0.09547996520996094, 0.09549999237060547, 0.09551000595092773, 0.09551119804382324, 0.09552812576293945, 0.09553098678588867, 0.09553289413452148, 0.0955350399017334, 0.09555196762084961, 0.09555602073669434, 0.09557294845581055, 0.09557795524597168, 0.0955820083618164, 0.09558391571044922, 0.09558510780334473, 0.0955960750579834, 0.09559893608093262, 0.09560680389404297, 0.09561491012573242, 0.09561514854431152, 0.09561800956726074, 0.09561896324157715, 0.09562897682189941, 0.09562921524047852, 0.09563398361206055, 0.09565401077270508, 0.09566307067871094, 0.09566712379455566, 0.0956888198852539, 0.09572196006774902, 0.09572315216064453, 0.09574604034423828, 0.0957498550415039, 0.09576201438903809, 0.09576797485351562, 0.09576892852783203, 0.09577107429504395, 0.09577703475952148, 0.09578108787536621, 0.09578490257263184, 0.09583210945129395, 0.09583401679992676, 0.09583497047424316, 0.09584188461303711, 0.09585309028625488, 0.09586000442504883, 0.09586596488952637, 0.09587311744689941, 0.09587788581848145, 0.09588003158569336, 0.0959022045135498, 0.09590697288513184, 0.09591007232666016, 0.09591889381408691, 0.09592485427856445, 0.09594297409057617, 0.09595394134521484, 0.09595394134521484, 0.09596586227416992, 0.09597206115722656, 0.09597206115722656, 0.09597516059875488, 0.09598207473754883, 0.09598493576049805, 0.09602212905883789, 0.0960540771484375, 0.09606409072875977, 0.09606504440307617, 0.09606719017028809, 0.09608292579650879, 0.09612584114074707, 0.0961451530456543, 0.09614682197570801, 0.09617900848388672, 0.09618115425109863, 0.09618711471557617, 0.09619998931884766, 0.09620308876037598, 0.09620404243469238, 0.0962369441986084, 0.09624099731445312, 0.09624099731445312, 0.09625697135925293, 0.09628796577453613, 0.09630203247070312, 0.09631609916687012, 0.09631800651550293, 0.09632992744445801, 0.09633207321166992, 0.09633684158325195, 0.09634280204772949, 0.09634709358215332, 0.09635496139526367, 0.09635591506958008, 0.09635591506958008, 0.09636092185974121, 0.09636902809143066, 0.09637689590454102, 0.09638094902038574, 0.09640288352966309, 0.09640312194824219, 0.09646296501159668, 0.09646415710449219, 0.0964670181274414, 0.09647202491760254, 0.09648418426513672, 0.09648799896240234, 0.0964961051940918, 0.0964970588684082, 0.09651803970336914, 0.09652209281921387, 0.09654092788696289, 0.09658098220825195, 0.0966029167175293, 0.09660887718200684, 0.0966181755065918, 0.09662103652954102, 0.09662199020385742, 0.0966339111328125, 0.0966348648071289, 0.09663891792297363, 0.0966498851776123, 0.09665298461914062, 0.09666013717651367, 0.09666585922241211, 0.09670901298522949, 0.09671592712402344, 0.09672784805297852, 0.09674501419067383, 0.09675979614257812, 0.09676003456115723, 0.0967710018157959, 0.09677290916442871, 0.09679293632507324, 0.09679388999938965, 0.09679508209228516, 0.09681391716003418, 0.09681987762451172, 0.09683108329772949, 0.09683609008789062, 0.09683895111083984, 0.09686517715454102, 0.09687089920043945, 0.09688210487365723, 0.09689497947692871, 0.09690499305725098, 0.09692502021789551, 0.09692811965942383, 0.0969398021697998, 0.09694314002990723, 0.09695196151733398, 0.09696197509765625, 0.09696793556213379, 0.09697699546813965, 0.09699392318725586, 0.09701108932495117, 0.09701991081237793, 0.09702396392822266, 0.0970299243927002, 0.0970299243927002, 0.09706807136535645, 0.0970768928527832, 0.09708285331726074, 0.09708309173583984, 0.09711098670959473, 0.09713006019592285, 0.09713387489318848, 0.09716296195983887, 0.09717106819152832, 0.09717297554016113, 0.09719085693359375, 0.09721088409423828, 0.09723997116088867, 0.09723997116088867, 0.09724187850952148, 0.09724593162536621, 0.09728097915649414, 0.09728407859802246, 0.09731006622314453, 0.09734487533569336, 0.09734582901000977, 0.09737300872802734, 0.09737491607666016, 0.09737801551818848, 0.09737992286682129, 0.09738802909851074, 0.0974118709564209, 0.09743380546569824, 0.09744596481323242, 0.09744691848754883, 0.09744787216186523, 0.09746503829956055, 0.09747481346130371, 0.09752488136291504, 0.09752893447875977, 0.09757184982299805, 0.09760022163391113, 0.09760189056396484, 0.09760689735412598, 0.09761214256286621, 0.09763908386230469, 0.09764599800109863, 0.09769606590270996, 0.09770083427429199, 0.0977020263671875, 0.09772014617919922, 0.09772586822509766, 0.09772682189941406, 0.09774398803710938, 0.09775304794311523, 0.09775710105895996, 0.09776186943054199, 0.09776592254638672, 0.09777092933654785, 0.09777092933654785, 0.09778404235839844, 0.09779095649719238, 0.09780406951904297, 0.09783720970153809, 0.09784793853759766, 0.09786009788513184, 0.09789013862609863, 0.09789514541625977, 0.0979619026184082, 0.09796404838562012, 0.09797120094299316, 0.0980229377746582, 0.0980229377746582, 0.09806108474731445, 0.09806203842163086, 0.09807300567626953, 0.09808993339538574, 0.0980980396270752, 0.09814286231994629, 0.09816718101501465, 0.09822702407836914, 0.09824609756469727, 0.09825897216796875, 0.09831404685974121, 0.09838700294494629, 0.09840178489685059, 0.09844803810119629, 0.09845495223999023, 0.09845614433288574, 0.0984659194946289, 0.09854507446289062, 0.09856200218200684, 0.09857392311096191, 0.09860897064208984, 0.0986640453338623, 0.09866499900817871, 0.09866619110107422, 0.09867382049560547, 0.09868097305297852, 0.09868192672729492, 0.09879899024963379, 0.09880399703979492, 0.09891319274902344, 0.09892606735229492, 0.0989530086517334, 0.09895515441894531, 0.09897089004516602, 0.0989830493927002, 0.09902501106262207, 0.0990297794342041, 0.09911894798278809, 0.09913110733032227, 0.09916090965270996, 0.09919190406799316, 0.0992269515991211, 0.09923601150512695, 0.09931206703186035, 0.09933900833129883, 0.09937095642089844, 0.0993800163269043, 0.09944009780883789, 0.0994560718536377, 0.09945893287658691, 0.09946012496948242, 0.09949994087219238, 0.09949994087219238, 0.09951400756835938, 0.09951400756835938, 0.09952688217163086, 0.09952712059020996, 0.09957695007324219, 0.09958291053771973, 0.09958887100219727, 0.0996088981628418, 0.09964108467102051, 0.09964585304260254, 0.09965014457702637, 0.09965181350708008, 0.09968686103820801, 0.09968709945678711, 0.09972596168518066, 0.09973788261413574, 0.09974384307861328, 0.09976911544799805, 0.09977102279663086, 0.09980010986328125, 0.09980487823486328, 0.09983086585998535, 0.09984207153320312, 0.09985089302062988, 0.09989309310913086, 0.09990501403808594, 0.09990787506103516, 0.09991192817687988, 0.09992098808288574, 0.09992289543151855, 0.09993410110473633, 0.0999760627746582, 0.09998106956481934, 0.10002303123474121, 0.10002493858337402, 0.10002589225769043, 0.1000368595123291, 0.1000528335571289, 0.10005307197570801, 0.10005712509155273, 0.10005903244018555, 0.1000678539276123, 0.10008502006530762, 0.10008716583251953, 0.10009002685546875, 0.1000969409942627, 0.10011792182922363, 0.10011982917785645, 0.10012388229370117, 0.10015201568603516, 0.10015606880187988, 0.10016012191772461, 0.10016107559204102, 0.1001729965209961, 0.10018205642700195, 0.10018396377563477, 0.10019207000732422, 0.1002199649810791, 0.10024905204772949, 0.10028290748596191, 0.10029315948486328, 0.10029387474060059, 0.1002969741821289, 0.10030388832092285, 0.10033106803894043, 0.10034298896789551, 0.10035085678100586, 0.10035395622253418, 0.10036993026733398, 0.10039305686950684, 0.10039782524108887, 0.1004030704498291, 0.10040593147277832, 0.10041093826293945, 0.10042095184326172, 0.10042500495910645, 0.10043907165527344, 0.1004800796508789, 0.10051202774047852, 0.10053300857543945, 0.10053896903991699, 0.10054683685302734, 0.10055398941040039, 0.1005549430847168, 0.10056400299072266, 0.10057187080383301, 0.1006009578704834, 0.10060906410217285, 0.10061383247375488, 0.10063695907592773, 0.10064005851745605, 0.10065984725952148, 0.10069012641906738, 0.10069704055786133, 0.10069799423217773, 0.1007089614868164, 0.10073113441467285, 0.10076785087585449, 0.10078096389770508, 0.10079097747802734, 0.1008141040802002, 0.10082197189331055, 0.10086798667907715, 0.10087299346923828, 0.10088801383972168, 0.10090303421020508, 0.10093498229980469, 0.10094094276428223, 0.10094809532165527, 0.10094904899597168, 0.10095095634460449, 0.1009669303894043, 0.10097193717956543, 0.10099315643310547, 0.10099387168884277, 0.10100889205932617, 0.10102605819702148, 0.10103106498718262, 0.10104107856750488, 0.10104990005493164, 0.10105204582214355, 0.10106992721557617, 0.10110020637512207, 0.1011350154876709, 0.10113787651062012, 0.10115408897399902, 0.10116195678710938, 0.10116791725158691, 0.10117101669311523, 0.10117983818054199, 0.10120606422424316, 0.10120606422424316, 0.1012110710144043, 0.10121488571166992, 0.10121607780456543, 0.10122084617614746, 0.10122895240783691, 0.10123014450073242, 0.10123395919799805, 0.10125494003295898, 0.1012580394744873, 0.10129904747009277, 0.10133790969848633, 0.10134100914001465, 0.10134291648864746, 0.101348876953125, 0.10135889053344727, 0.10139012336730957, 0.10139107704162598, 0.10139894485473633, 0.10140800476074219, 0.1014089584350586, 0.10143303871154785, 0.1014549732208252, 0.10149383544921875, 0.10151100158691406, 0.10152602195739746, 0.10152602195739746, 0.10155892372131348, 0.10156702995300293, 0.10157084465026855, 0.1015939712524414, 0.10161900520324707, 0.10162496566772461, 0.10168600082397461, 0.10170197486877441, 0.10172486305236816, 0.10178112983703613, 0.10179281234741211, 0.10179686546325684, 0.10180497169494629, 0.10180997848510742, 0.10181999206542969, 0.10185408592224121, 0.10185790061950684, 0.10185909271240234, 0.10186600685119629, 0.10187411308288574, 0.10189199447631836, 0.10189509391784668, 0.10189580917358398, 0.10190916061401367, 0.10191607475280762, 0.1019289493560791, 0.10192990303039551, 0.10197210311889648, 0.10202693939208984, 0.10203099250793457, 0.10203695297241211, 0.1020810604095459, 0.10208988189697266, 0.1020960807800293, 0.1021127700805664, 0.1021270751953125, 0.10212922096252441, 0.10216593742370605, 0.10216689109802246, 0.10218214988708496, 0.10221219062805176, 0.10222005844116211, 0.10222196578979492, 0.10224390029907227, 0.10225510597229004, 0.10228586196899414, 0.10229206085205078, 0.10231494903564453, 0.10236501693725586, 0.10238885879516602, 0.10240793228149414, 0.10240912437438965, 0.10242199897766113, 0.10245585441589355, 0.10245680809020996, 0.1025078296661377, 0.10254406929016113, 0.10255289077758789, 0.1025538444519043, 0.10256719589233398, 0.10257291793823242, 0.10262012481689453, 0.10271215438842773, 0.1027381420135498, 0.1027529239654541, 0.10276913642883301, 0.10278797149658203, 0.10279011726379395, 0.10280609130859375, 0.10284614562988281, 0.1029050350189209, 0.10294198989868164, 0.1029510498046875, 0.10296797752380371, 0.10297989845275879, 0.1030130386352539, 0.10304403305053711, 0.10310983657836914, 0.10312509536743164, 0.10313606262207031, 0.10313987731933594, 0.10319089889526367, 0.10319399833679199, 0.10322785377502441, 0.10341501235961914, 0.10344910621643066, 0.10345196723937988, 0.10347890853881836, 0.10351991653442383, 0.10352015495300293, 0.10355997085571289, 0.1038200855255127, 0.10385990142822266, 0.10386300086975098, 0.10390996932983398, 0.10400700569152832, 0.10400795936584473, 0.10408496856689453, 0.10416102409362793, 0.1041719913482666, 0.1042330265045166, 0.10435986518859863, 0.10436606407165527, 0.10440182685852051, 0.10441994667053223, 0.10445094108581543, 0.10450387001037598, 0.10454297065734863, 0.10454416275024414, 0.10454607009887695, 0.10460591316223145, 0.10466289520263672, 0.10470700263977051, 0.10471200942993164, 0.10473489761352539, 0.10487079620361328, 0.10494208335876465, 0.10515999794006348, 0.10523414611816406, 0.10539889335632324, 0.10542082786560059, 0.1054229736328125, 0.10543704032897949, 0.10547494888305664, 0.1055150032043457, 0.10555815696716309, 0.10556292533874512, 0.10557794570922852, 0.10571599006652832, 0.10572218894958496, 0.10573101043701172, 0.10580015182495117, 0.10581612586975098, 0.10581612586975098, 0.10584187507629395, 0.10589098930358887, 0.10599398612976074, 0.10601806640625, 0.10603117942810059, 0.10606098175048828, 0.1060788631439209, 0.10611200332641602, 0.1061549186706543, 0.1061849594116211, 0.10621380805969238, 0.10625505447387695, 0.10642290115356445, 0.10644292831420898, 0.10644316673278809, 0.10648894309997559, 0.1065211296081543, 0.10653495788574219, 0.10654187202453613, 0.1065518856048584, 0.10656309127807617, 0.106597900390625, 0.10660982131958008, 0.10665202140808105, 0.1068270206451416, 0.10690903663635254, 0.10691690444946289, 0.10693693161010742, 0.10693907737731934, 0.10694003105163574, 0.10697698593139648, 0.10711503028869629, 0.10713815689086914, 0.10716390609741211, 0.10722088813781738, 0.10728216171264648, 0.1072988510131836, 0.10730385780334473, 0.10730409622192383, 0.10732507705688477, 0.1073760986328125, 0.10738086700439453, 0.10745382308959961, 0.10751891136169434, 0.10752606391906738, 0.10757207870483398, 0.10760998725891113, 0.10762381553649902, 0.10763692855834961, 0.1077117919921875, 0.1078190803527832, 0.10782694816589355, 0.1078641414642334, 0.10788106918334961, 0.1078948974609375, 0.10794496536254883, 0.10795092582702637, 0.10806393623352051, 0.10813593864440918, 0.10816788673400879, 0.10818099975585938, 0.10819697380065918, 0.10831189155578613, 0.1083378791809082, 0.10842704772949219, 0.10846090316772461, 0.10848188400268555, 0.10854101181030273, 0.10855388641357422, 0.10858798027038574, 0.10858917236328125, 0.108612060546875, 0.10866999626159668, 0.10872197151184082, 0.10878610610961914, 0.1089630126953125, 0.10898089408874512, 0.10904502868652344, 0.10912394523620605, 0.10917997360229492, 0.10924911499023438, 0.10930585861206055, 0.10935592651367188, 0.10940003395080566, 0.10942316055297852, 0.1094520092010498, 0.10945606231689453, 0.10972309112548828, 0.10992097854614258, 0.10993313789367676, 0.11022210121154785, 0.11027002334594727, 0.11027717590332031, 0.11029505729675293, 0.11035013198852539, 0.11036801338195801, 0.11040115356445312, 0.11050701141357422, 0.1105809211730957, 0.11059308052062988, 0.11063814163208008, 0.1106569766998291, 0.11084294319152832, 0.11089801788330078, 0.11093616485595703, 0.11104106903076172, 0.1111910343170166, 0.11123204231262207, 0.11130499839782715, 0.11132192611694336, 0.11134696006774902, 0.11159396171569824, 0.11165785789489746, 0.11183691024780273, 0.11183810234069824, 0.11186695098876953, 0.11194086074829102, 0.11195492744445801, 0.1120460033416748, 0.1120750904083252, 0.11210203170776367, 0.11220598220825195, 0.11225605010986328, 0.11227607727050781, 0.11231708526611328, 0.11240482330322266, 0.11243391036987305, 0.11249804496765137, 0.1127011775970459, 0.11296200752258301, 0.1130528450012207, 0.11306405067443848, 0.11323809623718262, 0.1133110523223877, 0.11339211463928223, 0.11358380317687988, 0.11485886573791504, 0.11487603187561035, 0.11490297317504883, 0.1150820255279541, 0.11511588096618652, 0.11530399322509766, 0.11565589904785156, 0.11631488800048828, 0.11639904975891113, 0.11653900146484375, 0.11664295196533203, 0.11666202545166016, 0.11669206619262695, 0.11686396598815918, 0.11738896369934082, 0.11742305755615234, 0.1177060604095459, 0.11779308319091797, 0.11845016479492188, 0.11895608901977539, 0.11941695213317871, 0.11971282958984375, 0.12009906768798828, 0.12187695503234863, 0.1221780776977539, 0.122589111328125, 0.1233069896697998, 0.1753239631652832]</t>
+  </si>
+  <si>
+    <t>[0.11429500579833984, 0.11457991600036621, 0.11458110809326172, 0.11466503143310547, 0.11467719078063965, 0.11468291282653809, 0.11473488807678223, 0.11482501029968262, 0.11483407020568848, 0.11487197875976562, 0.11488604545593262, 0.1148979663848877, 0.11496090888977051, 0.11501693725585938, 0.11506295204162598, 0.1150670051574707, 0.1151120662689209, 0.11511778831481934, 0.11513710021972656, 0.11515593528747559, 0.11515593528747559, 0.11516094207763672, 0.11517214775085449, 0.11519384384155273, 0.11522793769836426, 0.11533284187316895, 0.11536288261413574, 0.1153709888458252, 0.11537981033325195, 0.11542701721191406, 0.11550116539001465, 0.11550784111022949, 0.11551713943481445, 0.11553096771240234, 0.11562705039978027, 0.11564803123474121, 0.11573600769042969, 0.11574506759643555, 0.11577486991882324, 0.11577606201171875, 0.1158139705657959, 0.11582303047180176, 0.11584115028381348, 0.11590313911437988, 0.1159670352935791, 0.11604714393615723, 0.11609101295471191, 0.11610603332519531, 0.1161658763885498, 0.11623597145080566, 0.1163320541381836, 0.11644792556762695, 0.11647486686706543, 0.11647605895996094, 0.1164851188659668, 0.11660003662109375, 0.11667203903198242, 0.11670589447021484, 0.11684894561767578, 0.11689615249633789, 0.1169121265411377, 0.11700081825256348, 0.11703920364379883, 0.1171579360961914, 0.11716914176940918, 0.11723208427429199, 0.11725497245788574, 0.11730504035949707, 0.11733794212341309, 0.11735105514526367, 0.11744904518127441, 0.11746096611022949, 0.11747980117797852, 0.11748409271240234, 0.11752581596374512, 0.11754107475280762, 0.11754393577575684, 0.11758804321289062, 0.11767816543579102, 0.11769390106201172, 0.11770296096801758, 0.11771392822265625, 0.1177370548248291, 0.11775612831115723, 0.11781001091003418, 0.11782479286193848, 0.11782693862915039, 0.1180570125579834, 0.11809992790222168, 0.11817216873168945, 0.11821103096008301, 0.11821603775024414, 0.11823487281799316, 0.11832499504089355, 0.11850905418395996, 0.1185150146484375, 0.11851811408996582, 0.1185600757598877, 0.11861085891723633, 0.11867094039916992, 0.11867594718933105, 0.11867904663085938, 0.1186988353729248, 0.11870813369750977, 0.11874699592590332, 0.11875200271606445, 0.11875510215759277, 0.1187899112701416, 0.1188209056854248, 0.11888599395751953, 0.11891508102416992, 0.11899089813232422, 0.11913704872131348, 0.11925888061523438, 0.11927413940429688, 0.11928391456604004, 0.11942601203918457, 0.11945295333862305, 0.11952400207519531, 0.11954498291015625, 0.11956119537353516, 0.11957979202270508, 0.11958098411560059, 0.11960291862487793, 0.11961793899536133, 0.11963200569152832, 0.11963605880737305, 0.1196889877319336, 0.11974787712097168, 0.11975693702697754, 0.11978793144226074, 0.11980700492858887, 0.11984086036682129, 0.11984896659851074, 0.11986613273620605, 0.11993002891540527, 0.11994004249572754, 0.1199648380279541, 0.11997199058532715, 0.12002015113830566, 0.12003517150878906, 0.12006187438964844, 0.12007689476013184, 0.12008213996887207, 0.12009286880493164, 0.12009906768798828, 0.1201331615447998, 0.12014579772949219, 0.1201930046081543, 0.12022900581359863, 0.12024998664855957, 0.1202690601348877, 0.12031698226928711, 0.12033390998840332, 0.12037515640258789, 0.12039303779602051, 0.12040495872497559, 0.12041687965393066, 0.12043905258178711, 0.12044501304626465, 0.12044596672058105, 0.12049317359924316, 0.12050700187683105, 0.12051010131835938, 0.12052416801452637, 0.12054204940795898, 0.1205759048461914, 0.12058305740356445, 0.12059497833251953, 0.12064099311828613, 0.12065005302429199, 0.12067294120788574, 0.12073302268981934, 0.12074899673461914, 0.12077617645263672, 0.12079882621765137, 0.12081599235534668, 0.1208949089050293, 0.12090206146240234, 0.12092208862304688, 0.12093186378479004, 0.12093210220336914, 0.12102079391479492, 0.12102913856506348, 0.12103891372680664, 0.12104511260986328, 0.12105798721313477, 0.12109708786010742, 0.12111711502075195, 0.12115311622619629, 0.12119293212890625, 0.12119698524475098, 0.12122201919555664, 0.12122917175292969, 0.12127399444580078, 0.12130093574523926, 0.12133002281188965, 0.12143898010253906, 0.12143993377685547, 0.12146711349487305, 0.1214749813079834, 0.1215970516204834, 0.1216428279876709, 0.12164616584777832, 0.1216590404510498, 0.12167000770568848, 0.12168002128601074, 0.12169098854064941, 0.12169599533081055, 0.12169790267944336, 0.12172603607177734, 0.12175202369689941, 0.12178397178649902, 0.12179422378540039, 0.12181997299194336, 0.12183213233947754, 0.12187790870666504, 0.12188601493835449, 0.12192392349243164, 0.12192392349243164, 0.12192893028259277, 0.1219329833984375, 0.12194204330444336, 0.12194991111755371, 0.12198114395141602, 0.12198591232299805, 0.1219949722290039, 0.1220090389251709, 0.12208390235900879, 0.12213587760925293, 0.12213921546936035, 0.12216901779174805, 0.12217593193054199, 0.12221193313598633, 0.1222231388092041, 0.12224102020263672, 0.12224292755126953, 0.12226009368896484, 0.12228083610534668, 0.12234997749328613, 0.1223750114440918, 0.1224050521850586, 0.12240791320800781, 0.12244892120361328, 0.12248897552490234, 0.12251019477844238, 0.1225130558013916, 0.12253212928771973, 0.12253594398498535, 0.12256884574890137, 0.12260818481445312, 0.12264394760131836, 0.12265682220458984, 0.12268400192260742, 0.12270212173461914, 0.12271714210510254, 0.12273287773132324, 0.1227560043334961, 0.1227879524230957, 0.12279796600341797, 0.12280392646789551, 0.12280392646789551, 0.12281608581542969, 0.12287306785583496, 0.12288999557495117, 0.12289690971374512, 0.12290501594543457, 0.12291598320007324, 0.12291812896728516, 0.12293577194213867, 0.12294697761535645, 0.12301301956176758, 0.12303304672241211, 0.12303304672241211, 0.12305784225463867, 0.12307381629943848, 0.12308096885681152, 0.12308692932128906, 0.12312602996826172, 0.1231529712677002, 0.12317109107971191, 0.12317204475402832, 0.12318897247314453, 0.12324905395507812, 0.12329292297363281, 0.12331199645996094, 0.1233220100402832, 0.12332797050476074, 0.12332916259765625, 0.12335586547851562, 0.12337303161621094, 0.12337422370910645, 0.12339210510253906, 0.12342000007629395, 0.12343215942382812, 0.12343811988830566, 0.12344717979431152, 0.12344789505004883, 0.12345099449157715, 0.12346196174621582, 0.12347292900085449, 0.12349796295166016, 0.12350702285766602, 0.12351799011230469, 0.12352705001831055, 0.12353897094726562, 0.12354493141174316, 0.12354612350463867, 0.12356185913085938, 0.12356305122375488, 0.12366795539855957, 0.12366914749145508, 0.12369084358215332, 0.12369203567504883, 0.12369680404663086, 0.12370491027832031, 0.12372994422912598, 0.12373685836791992, 0.12374019622802734, 0.12378191947937012, 0.12381601333618164, 0.12381887435913086, 0.12383890151977539, 0.12384510040283203, 0.12385296821594238, 0.12387394905090332, 0.12389898300170898, 0.12391281127929688, 0.12391805648803711, 0.12394189834594727, 0.12395191192626953, 0.12396812438964844, 0.1239938735961914, 0.12399482727050781, 0.12406301498413086, 0.12412285804748535, 0.12415194511413574, 0.12416195869445801, 0.12416291236877441, 0.12417006492614746, 0.12417793273925781, 0.12417912483215332, 0.1242070198059082, 0.12420797348022461, 0.12423491477966309, 0.12424421310424805, 0.12425804138183594, 0.12428712844848633, 0.12429213523864746, 0.1242978572845459, 0.1243290901184082, 0.12434792518615723, 0.12439703941345215, 0.12439799308776855, 0.12439990043640137, 0.12440609931945801, 0.12440705299377441, 0.12440991401672363, 0.12442803382873535, 0.12443017959594727, 0.12443208694458008, 0.12444400787353516, 0.12448692321777344, 0.12451815605163574, 0.12453699111938477, 0.12455296516418457, 0.12456989288330078, 0.12457108497619629, 0.1245720386505127, 0.12464594841003418, 0.12464618682861328, 0.12467503547668457, 0.12474203109741211, 0.12474489212036133, 0.12474799156188965, 0.12477302551269531, 0.12479114532470703, 0.1248009204864502, 0.12481904029846191, 0.12482309341430664, 0.12482404708862305, 0.12482810020446777, 0.12483692169189453, 0.12485098838806152, 0.12485218048095703, 0.12485504150390625, 0.12485885620117188, 0.12488889694213867, 0.12490105628967285, 0.12490606307983398, 0.12491106986999512, 0.1249239444732666, 0.12494993209838867, 0.12495803833007812, 0.12497901916503906, 0.12499213218688965, 0.1249990463256836, 0.1250147819519043, 0.12502598762512207, 0.12505602836608887, 0.12506604194641113, 0.12509393692016602, 0.12511396408081055, 0.12513399124145508, 0.1251540184020996, 0.12517404556274414, 0.12521815299987793, 0.12523293495178223, 0.12524795532226562, 0.12525010108947754, 0.12525200843811035, 0.12526202201843262, 0.12526917457580566, 0.12528395652770996, 0.1253070831298828, 0.12531304359436035, 0.12536406517028809, 0.12537693977355957, 0.12537884712219238, 0.12537884712219238, 0.12539291381835938, 0.1253969669342041, 0.1254138946533203, 0.12542319297790527, 0.12542319297790527, 0.12545490264892578, 0.12550687789916992, 0.12552309036254883, 0.12554693222045898, 0.12556982040405273, 0.12558293342590332, 0.1256098747253418, 0.12563300132751465, 0.12563681602478027, 0.1256399154663086, 0.1256411075592041, 0.12565994262695312, 0.12566590309143066, 0.1256709098815918, 0.12567901611328125, 0.12568187713623047, 0.12569618225097656, 0.12569904327392578, 0.12575197219848633, 0.12575888633728027, 0.12577390670776367, 0.12578988075256348, 0.1257939338684082, 0.12581992149353027, 0.12583613395690918, 0.12584400177001953, 0.12584900856018066, 0.12586402893066406, 0.12589597702026367, 0.1259598731994629, 0.1259779930114746, 0.12598609924316406, 0.12599611282348633, 0.12601208686828613, 0.126054048538208, 0.12605500221252441, 0.12605810165405273, 0.12607693672180176, 0.12609505653381348, 0.12610983848571777, 0.1261138916015625, 0.12612605094909668, 0.12614893913269043, 0.1262218952178955, 0.12624096870422363, 0.12624311447143555, 0.12626099586486816, 0.12627577781677246, 0.12636995315551758, 0.12639212608337402, 0.12639808654785156, 0.1264021396636963, 0.12641501426696777, 0.12642312049865723, 0.12642383575439453, 0.1264359951019287, 0.12644600868225098, 0.12645602226257324, 0.12645912170410156, 0.12648415565490723, 0.12649798393249512, 0.12649798393249512, 0.12651515007019043, 0.12652087211608887, 0.12654685974121094, 0.12655901908874512, 0.12656307220458984, 0.12656807899475098, 0.12660813331604004, 0.12664008140563965, 0.1266498565673828, 0.12667107582092285, 0.1266789436340332, 0.1266798973083496, 0.12668704986572266, 0.1266918182373047, 0.12671303749084473, 0.1267259120941162, 0.12674212455749512, 0.1267540454864502, 0.1267869472503662, 0.12679100036621094, 0.1268298625946045, 0.12683606147766113, 0.1268448829650879, 0.12686705589294434, 0.12688612937927246, 0.12691497802734375, 0.12691903114318848, 0.1269240379333496, 0.1269369125366211, 0.12694978713989258, 0.12702488899230957, 0.12702608108520508, 0.1270298957824707, 0.12704205513000488, 0.1270430088043213, 0.12706279754638672, 0.12706398963928223, 0.12709593772888184, 0.12709712982177734, 0.12709784507751465, 0.12711000442504883, 0.1271200180053711, 0.12712717056274414, 0.1271381378173828, 0.1272740364074707, 0.1272749900817871, 0.12727618217468262, 0.12727904319763184, 0.12732219696044922, 0.12732696533203125, 0.12733793258666992, 0.1273510456085205, 0.12737202644348145, 0.12739801406860352, 0.12742018699645996, 0.12742185592651367, 0.12743115425109863, 0.12747502326965332, 0.12749505043029785, 0.12754487991333008, 0.12756991386413574, 0.1276240348815918, 0.12763094902038574, 0.1276710033416748, 0.12767410278320312, 0.12769198417663574, 0.1277470588684082, 0.12777209281921387, 0.12778520584106445, 0.12779521942138672, 0.12781810760498047, 0.12784814834594727, 0.1278688907623291, 0.12788105010986328, 0.12788796424865723, 0.12789487838745117, 0.12790608406066895, 0.12791705131530762, 0.12792015075683594, 0.12792396545410156, 0.12793707847595215, 0.12794709205627441, 0.12795281410217285, 0.12796306610107422, 0.12797880172729492, 0.12799501419067383, 0.12800192832946777, 0.12804603576660156, 0.1280498504638672, 0.12807321548461914, 0.12807798385620117, 0.12807989120483398, 0.1280829906463623, 0.1280970573425293, 0.12810111045837402, 0.12810516357421875, 0.12813806533813477, 0.12813901901245117, 0.1281421184539795, 0.12814784049987793, 0.12814998626708984, 0.12815308570861816, 0.12818098068237305, 0.12819314002990723, 0.12819504737854004, 0.12821197509765625, 0.1282341480255127, 0.1282358169555664, 0.12824606895446777, 0.12824797630310059, 0.1282520294189453, 0.12827396392822266, 0.12828898429870605, 0.1282939910888672, 0.12830209732055664, 0.12831711769104004, 0.12832999229431152, 0.12833714485168457, 0.12834620475769043, 0.12835097312927246, 0.12835192680358887, 0.1283559799194336, 0.12840700149536133, 0.12840700149536133, 0.12840819358825684, 0.1284170150756836, 0.12842702865600586, 0.12844491004943848, 0.1284470558166504, 0.12845802307128906, 0.12847399711608887, 0.12849998474121094, 0.12849998474121094, 0.12851691246032715, 0.1285240650177002, 0.1285572052001953, 0.12857508659362793, 0.12858200073242188, 0.12859201431274414, 0.12862801551818848, 0.12862801551818848, 0.12863707542419434, 0.1286470890045166, 0.12867283821105957, 0.12868094444274902, 0.12869501113891602, 0.12871789932250977, 0.12874698638916016, 0.1287519931793213, 0.12876009941101074, 0.12876200675964355, 0.12880682945251465, 0.1288130283355713, 0.12882113456726074, 0.12887096405029297, 0.12889409065246582, 0.12889790534973145, 0.1289219856262207, 0.12893104553222656, 0.12894296646118164, 0.1289501190185547, 0.1289839744567871, 0.1290111541748047, 0.12901902198791504, 0.12906503677368164, 0.12907099723815918, 0.12907886505126953, 0.1290888786315918, 0.12909913063049316, 0.12910819053649902, 0.12910985946655273, 0.12914800643920898, 0.12917184829711914, 0.1291821002960205, 0.12923288345336914, 0.1292591094970703, 0.12926697731018066, 0.12930011749267578, 0.12935304641723633, 0.1293630599975586, 0.12939691543579102, 0.12940287590026855, 0.1294081211090088, 0.12941789627075195, 0.12942099571228027, 0.1294558048248291, 0.12948894500732422, 0.129500150680542, 0.12950515747070312, 0.12950587272644043, 0.12953400611877441, 0.12953615188598633, 0.1296370029449463, 0.12967801094055176, 0.12969088554382324, 0.12971091270446777, 0.12971806526184082, 0.12972283363342285, 0.1297459602355957, 0.1297779083251953, 0.12978291511535645, 0.12980103492736816, 0.12981605529785156, 0.12981605529785156, 0.12981796264648438, 0.1298351287841797, 0.12984704971313477, 0.12987208366394043, 0.12989306449890137, 0.12990713119506836, 0.12996506690979004, 0.12998390197753906, 0.13002300262451172, 0.13002800941467285, 0.13005590438842773, 0.13011503219604492, 0.13015484809875488, 0.13017797470092773, 0.13020086288452148, 0.1303098201751709, 0.13033795356750488, 0.130385160446167, 0.13039398193359375, 0.13042593002319336, 0.13043498992919922, 0.1304919719696045, 0.13053107261657715, 0.13056087493896484, 0.13057494163513184, 0.13062214851379395, 0.1306300163269043, 0.1306450366973877, 0.1306459903717041, 0.1307680606842041, 0.13077187538146973, 0.1307971477508545, 0.13085103034973145, 0.13085412979125977, 0.13095903396606445, 0.13097500801086426, 0.13101792335510254, 0.131026029586792, 0.1310269832611084, 0.13105416297912598, 0.13108396530151367, 0.131087064743042, 0.13111400604248047, 0.13112592697143555, 0.1311638355255127, 0.13116884231567383, 0.13117003440856934, 0.1311941146850586, 0.13122296333312988, 0.131242036819458, 0.13125205039978027, 0.13128209114074707, 0.1312849521636963, 0.1313188076019287, 0.13141107559204102, 0.13141107559204102, 0.13142108917236328, 0.13145899772644043, 0.13151192665100098, 0.13158082962036133, 0.13161110877990723, 0.13161206245422363, 0.13166093826293945, 0.13166308403015137, 0.1316699981689453, 0.13169002532958984, 0.13170099258422852, 0.13176703453063965, 0.1317739486694336, 0.1318361759185791, 0.13184809684753418, 0.13185906410217285, 0.1318650245666504, 0.13187003135681152, 0.13187384605407715, 0.13188910484313965, 0.1319119930267334, 0.13192200660705566, 0.1319291591644287, 0.13193893432617188, 0.1319880485534668, 0.1320490837097168, 0.13208699226379395, 0.13210391998291016, 0.13212013244628906, 0.13213491439819336, 0.1321561336517334, 0.1321568489074707, 0.13218283653259277, 0.13218402862548828, 0.1321878433227539, 0.13219189643859863, 0.13219690322875977, 0.13220810890197754, 0.13227415084838867, 0.13230204582214355, 0.1323080062866211, 0.13236498832702637, 0.13236784934997559, 0.13242506980895996, 0.13247299194335938, 0.13249588012695312, 0.1325089931488037, 0.13262391090393066, 0.13266396522521973, 0.1327049732208252, 0.13275885581970215, 0.13276100158691406, 0.1327831745147705, 0.13292312622070312, 0.1329479217529297, 0.13296294212341309, 0.13297104835510254, 0.13298416137695312, 0.13301777839660645, 0.13305211067199707, 0.1330552101135254, 0.13305997848510742, 0.13308191299438477, 0.13312292098999023, 0.13313698768615723, 0.13314008712768555, 0.13314080238342285, 0.13318586349487305, 0.13320493698120117, 0.13321304321289062, 0.13321495056152344, 0.1332700252532959, 0.13328099250793457, 0.13330507278442383, 0.13332009315490723, 0.13332200050354004, 0.13335204124450684, 0.13335800170898438, 0.1333611011505127, 0.13339591026306152, 0.1334400177001953, 0.13344192504882812, 0.13344693183898926, 0.13352203369140625, 0.13357186317443848, 0.1335749626159668, 0.1336040496826172, 0.13361191749572754, 0.13366198539733887, 0.13367795944213867, 0.1336989402770996, 0.1337120532989502, 0.1337120532989502, 0.13375401496887207, 0.13376283645629883, 0.1337881088256836, 0.13384413719177246, 0.13388490676879883, 0.13391900062561035, 0.13396286964416504, 0.1339859962463379, 0.13404297828674316, 0.13410282135009766, 0.13412714004516602, 0.1341719627380371, 0.13418984413146973, 0.13419890403747559, 0.13420891761779785, 0.13422513008117676, 0.13433504104614258, 0.13437390327453613, 0.13453102111816406, 0.13453412055969238, 0.1346421241760254, 0.1346750259399414, 0.13474106788635254, 0.134749174118042, 0.13494586944580078, 0.13497090339660645, 0.1351020336151123, 0.1351299285888672, 0.13513684272766113, 0.1351490020751953, 0.13521385192871094, 0.13522100448608398, 0.13535618782043457, 0.13538599014282227, 0.13551998138427734, 0.13554883003234863, 0.1356201171875, 0.1357250213623047, 0.1357870101928711, 0.13584613800048828, 0.13591313362121582, 0.13592791557312012, 0.13599705696105957, 0.13599801063537598, 0.13608193397521973, 0.13608789443969727, 0.13610100746154785, 0.13614892959594727, 0.13615989685058594, 0.1362001895904541, 0.13622379302978516, 0.13629412651062012, 0.13633012771606445, 0.13634920120239258, 0.13636183738708496, 0.13648295402526855, 0.13653898239135742, 0.13656306266784668, 0.13664007186889648, 0.1366589069366455, 0.1366589069366455, 0.13677501678466797, 0.13694286346435547, 0.13695693016052246, 0.13698816299438477, 0.1370549201965332, 0.1371769905090332, 0.13722920417785645, 0.13726592063903809, 0.1373128890991211, 0.13732099533081055, 0.1374819278717041, 0.1374979019165039, 0.13750314712524414, 0.13750600814819336, 0.1375420093536377, 0.13760995864868164, 0.13780593872070312, 0.13796710968017578, 0.1379859447479248, 0.13799214363098145, 0.13800597190856934, 0.13803911209106445, 0.13804292678833008, 0.13805699348449707, 0.1380939483642578, 0.13811802864074707, 0.138153076171875, 0.13815999031066895, 0.13820409774780273, 0.13830804824829102, 0.13848495483398438, 0.13849186897277832, 0.13851499557495117, 0.1386110782623291, 0.13862180709838867, 0.138624906539917, 0.13862895965576172, 0.13867712020874023, 0.13876700401306152, 0.13876891136169434, 0.1389760971069336, 0.13921904563903809, 0.1392371654510498, 0.13924217224121094, 0.13958382606506348, 0.13977694511413574, 0.139909029006958, 0.14070487022399902, 0.140733003616333, 0.1409919261932373, 0.14131402969360352, 0.14196205139160156, 0.1420600414276123, 0.1423349380493164, 0.14336895942687988, 0.14375591278076172, 0.14418387413024902, 0.14482903480529785, 0.14602088928222656, 0.14646601676940918, 0.1484220027923584, 0.1519489288330078, 0.19670391082763672, 0.19745397567749023, 0.1985180377960205, 0.1985628604888916, 0.1992809772491455, 0.19964909553527832, 0.20087003707885742, 0.2010509967803955, 0.20210504531860352, 0.20265793800354004, 0.20382118225097656, 0.2041029930114746, 0.204362154006958, 0.20843815803527832, 0.21128511428833008, 0.21163010597229004, 0.21169400215148926]</t>
+  </si>
+  <si>
+    <t>[0.09527802467346191, 0.09536194801330566, 0.09548306465148926, 0.09548497200012207, 0.09580397605895996, 0.09601211547851562, 0.09603190422058105, 0.09612107276916504, 0.09612798690795898, 0.09620213508605957, 0.09645295143127441, 0.09653496742248535, 0.0965418815612793, 0.09677505493164062, 0.09678292274475098, 0.09733986854553223, 0.09745407104492188, 0.0977470874786377, 0.09821105003356934, 0.09829115867614746, 0.09838294982910156, 0.09941816329956055, 0.09949898719787598, 0.09955191612243652, 0.09958004951477051, 0.09958505630493164, 0.09962916374206543, 0.09965801239013672, 0.09973001480102539, 0.09974002838134766, 0.0997469425201416, 0.09975194931030273, 0.0997779369354248, 0.09979486465454102, 0.09981298446655273, 0.09982514381408691, 0.09982585906982422, 0.09987092018127441, 0.09987688064575195, 0.09989404678344727, 0.09995198249816895, 0.09996485710144043, 0.09997415542602539, 0.09997892379760742, 0.09997892379760742, 0.10002303123474121, 0.1000361442565918, 0.10007500648498535, 0.10008597373962402, 0.10008907318115234, 0.10009312629699707, 0.10009598731994629, 0.1000969409942627, 0.10010790824890137, 0.10012102127075195, 0.10013198852539062, 0.10013294219970703, 0.10014700889587402, 0.10014796257019043, 0.10016489028930664, 0.10022592544555664, 0.10023093223571777, 0.10023212432861328, 0.10024189949035645, 0.10024714469909668, 0.10025405883789062, 0.10025501251220703, 0.10025501251220703, 0.10026812553405762, 0.1002950668334961, 0.10030388832092285, 0.10030508041381836, 0.10033011436462402, 0.10033512115478516, 0.10034489631652832, 0.10034704208374023, 0.10035490989685059, 0.10036277770996094, 0.10036492347717285, 0.10037493705749512, 0.10037708282470703, 0.1003868579864502, 0.10040807723999023, 0.10041093826293945, 0.10042405128479004, 0.1004791259765625, 0.10051894187927246, 0.10053205490112305, 0.10059690475463867, 0.10061812400817871, 0.10064101219177246, 0.10066008567810059, 0.1006767749786377, 0.10071492195129395, 0.10072708129882812, 0.10072898864746094, 0.10073518753051758, 0.10076022148132324, 0.10077190399169922, 0.10078692436218262, 0.10080599784851074, 0.10081195831298828, 0.1008460521697998, 0.10085415840148926, 0.10085701942443848, 0.10087299346923828, 0.1008749008178711, 0.10088586807250977, 0.1008920669555664, 0.10089516639709473, 0.10091304779052734, 0.1009221076965332, 0.10092997550964355, 0.10093998908996582, 0.10094785690307617, 0.10097408294677734, 0.1010279655456543, 0.10103988647460938, 0.10111117362976074, 0.10114598274230957, 0.10115790367126465, 0.10118603706359863, 0.10119199752807617, 0.10120987892150879, 0.10121297836303711, 0.10121417045593262, 0.10121822357177734, 0.10122013092041016, 0.10126113891601562, 0.10126495361328125, 0.10126686096191406, 0.10128116607666016, 0.10129094123840332, 0.10130095481872559, 0.10130190849304199, 0.10131597518920898, 0.1013340950012207, 0.10134315490722656, 0.10139918327331543, 0.10140800476074219, 0.10142898559570312, 0.10143899917602539, 0.10144996643066406, 0.10145306587219238, 0.10145902633666992, 0.1015160083770752, 0.10153508186340332, 0.10154414176940918, 0.1015629768371582, 0.10157012939453125, 0.1015779972076416, 0.10159516334533691, 0.10159707069396973, 0.10160279273986816, 0.10162496566772461, 0.10163307189941406, 0.10164284706115723, 0.10164713859558105, 0.10166811943054199, 0.10167098045349121, 0.10167312622070312, 0.10169410705566406, 0.10171794891357422, 0.10173487663269043, 0.10173511505126953, 0.10174202919006348, 0.10175013542175293, 0.10175085067749023, 0.10176301002502441, 0.10178208351135254, 0.10179591178894043, 0.10180807113647461, 0.10181117057800293, 0.10181188583374023, 0.10181593894958496, 0.10181999206542969, 0.1018209457397461, 0.10183000564575195, 0.10185503959655762, 0.10186505317687988, 0.10186600685119629, 0.1018669605255127, 0.10187911987304688, 0.10188794136047363, 0.10189008712768555, 0.10190105438232422, 0.10192298889160156, 0.10193514823913574, 0.10193514823913574, 0.10193800926208496, 0.10194802284240723, 0.10195708274841309, 0.10195779800415039, 0.10199999809265137, 0.1020050048828125, 0.1020059585571289, 0.1020510196685791, 0.10205292701721191, 0.10208892822265625, 0.10210394859313965, 0.10210418701171875, 0.10211682319641113, 0.10212206840515137, 0.10212588310241699, 0.1021268367767334, 0.10214900970458984, 0.10216593742370605, 0.10216903686523438, 0.10217404365539551, 0.1021881103515625, 0.10220098495483398, 0.10221409797668457, 0.10221719741821289, 0.10223007202148438, 0.10224604606628418, 0.10224699974060059, 0.1022500991821289, 0.1022500991821289, 0.10225200653076172, 0.10226106643676758, 0.10226202011108398, 0.10228514671325684, 0.10229682922363281, 0.10229802131652832, 0.1023101806640625, 0.10231590270996094, 0.10232019424438477, 0.1023409366607666, 0.1023859977722168, 0.10238909721374512, 0.10238909721374512, 0.10241198539733887, 0.10242700576782227, 0.10242819786071777, 0.10244894027709961, 0.10246396064758301, 0.10250401496887207, 0.10251212120056152, 0.1025538444519043, 0.10257196426391602, 0.10258293151855469, 0.10259103775024414, 0.10259294509887695, 0.10260510444641113, 0.10260605812072754, 0.10261797904968262, 0.10262680053710938, 0.10263490676879883, 0.10263514518737793, 0.10263800621032715, 0.10267090797424316, 0.10268282890319824, 0.10271883010864258, 0.10273504257202148, 0.10274600982666016, 0.1027529239654541, 0.10276198387145996, 0.10276198387145996, 0.10279202461242676, 0.10279417037963867, 0.10282588005065918, 0.10282707214355469, 0.1028280258178711, 0.10283899307250977, 0.1028740406036377, 0.1028740406036377, 0.1028909683227539, 0.10291600227355957, 0.1029360294342041, 0.10294294357299805, 0.10294413566589355, 0.1029520034790039, 0.10299015045166016, 0.10299110412597656, 0.10300707817077637, 0.10300803184509277, 0.1030120849609375, 0.10301995277404785, 0.10304903984069824, 0.10306596755981445, 0.10310220718383789, 0.1031198501586914, 0.10316801071166992, 0.10320901870727539, 0.10321712493896484, 0.10323882102966309, 0.10324907302856445, 0.10326409339904785, 0.10326886177062988, 0.1033179759979248, 0.1033470630645752, 0.10338592529296875, 0.10342001914978027, 0.10342121124267578, 0.10343098640441895, 0.1034400463104248, 0.10349893569946289, 0.10353207588195801, 0.10354304313659668, 0.10357189178466797, 0.10357213020324707, 0.10361289978027344, 0.10361814498901367, 0.10363292694091797, 0.10366487503051758, 0.10368514060974121, 0.10371685028076172, 0.1038370132446289, 0.10384392738342285, 0.10386180877685547, 0.10390901565551758, 0.10395288467407227, 0.10395693778991699, 0.10397005081176758, 0.10399007797241211, 0.10401105880737305, 0.10413694381713867, 0.1041569709777832, 0.10418701171875, 0.10419178009033203, 0.1042029857635498, 0.10420918464660645, 0.10421419143676758, 0.10425806045532227, 0.10428476333618164, 0.10430502891540527, 0.10431098937988281, 0.10435605049133301, 0.10435795783996582, 0.1043710708618164, 0.10437703132629395, 0.10445213317871094, 0.10447311401367188, 0.10448789596557617, 0.1044919490814209, 0.10449910163879395, 0.10451292991638184, 0.10452508926391602, 0.10454201698303223, 0.1045680046081543, 0.10459303855895996, 0.10461902618408203, 0.10464215278625488, 0.10464596748352051, 0.10465192794799805, 0.10465216636657715, 0.10465502738952637, 0.10466504096984863, 0.10466599464416504, 0.10467100143432617, 0.10471391677856445, 0.10472297668457031, 0.10472607612609863, 0.10473108291625977, 0.1047368049621582, 0.10474205017089844, 0.10475707054138184, 0.1047658920288086, 0.10477900505065918, 0.1047968864440918, 0.10480690002441406, 0.104827880859375, 0.10484099388122559, 0.1048438549041748, 0.10485076904296875, 0.10486006736755371, 0.10487222671508789, 0.10488295555114746, 0.10489201545715332, 0.10489416122436523, 0.10492610931396484, 0.10494804382324219, 0.10497593879699707, 0.10498905181884766, 0.10500693321228027, 0.10503220558166504, 0.1050419807434082, 0.10504913330078125, 0.10508394241333008, 0.10508394241333008, 0.10509705543518066, 0.1051020622253418, 0.10511422157287598, 0.10511898994445801, 0.10513710975646973, 0.10520100593566895, 0.10520386695861816, 0.10522103309631348, 0.10522294044494629, 0.10523796081542969, 0.1052711009979248, 0.10529804229736328, 0.1053321361541748, 0.10537409782409668, 0.10538506507873535, 0.1053919792175293, 0.10539388656616211, 0.10540890693664551, 0.10541200637817383, 0.1054999828338623, 0.10550713539123535, 0.10553503036499023, 0.10556817054748535, 0.1056208610534668, 0.1056509017944336, 0.10565710067749023, 0.10566210746765137, 0.10572195053100586, 0.10573506355285645, 0.10575103759765625, 0.10579705238342285, 0.10579895973205566, 0.10580801963806152, 0.10584187507629395, 0.10584807395935059, 0.10586309432983398, 0.1058809757232666, 0.10590100288391113, 0.10590481758117676, 0.10595583915710449, 0.10598087310791016, 0.10598611831665039, 0.10601496696472168, 0.10602593421936035, 0.10605788230895996, 0.10605907440185547, 0.10608291625976562, 0.10608506202697754, 0.1061098575592041, 0.10611391067504883, 0.10613489151000977, 0.10613512992858887, 0.10614585876464844, 0.10616207122802734, 0.10616207122802734, 0.10617709159851074, 0.10621404647827148, 0.10622596740722656, 0.10623693466186523, 0.10624003410339355, 0.10628890991210938, 0.10630106925964355, 0.10630512237548828, 0.10631012916564941, 0.10631203651428223, 0.10632610321044922, 0.10634779930114746, 0.10635805130004883, 0.10637688636779785, 0.10637998580932617, 0.10638999938964844, 0.10639095306396484, 0.10639095306396484, 0.10639691352844238, 0.10640311241149902, 0.10644197463989258, 0.10644698143005371, 0.10647106170654297, 0.10647916793823242, 0.10649895668029785, 0.10649895668029785, 0.10650801658630371, 0.10651087760925293, 0.10651397705078125, 0.10655999183654785, 0.10656094551086426, 0.10659980773925781, 0.10661005973815918, 0.10661506652832031, 0.10663104057312012, 0.10665416717529297, 0.10669708251953125, 0.10669994354248047, 0.10672497749328613, 0.10673689842224121, 0.10673904418945312, 0.10674810409545898, 0.10675692558288574, 0.10676002502441406, 0.1067659854888916, 0.10677790641784668, 0.10678410530090332, 0.1067969799041748, 0.10680103302001953, 0.10680413246154785, 0.10681295394897461, 0.10685300827026367, 0.10688591003417969, 0.1069488525390625, 0.10695314407348633, 0.10699105262756348, 0.1070089340209961, 0.10701704025268555, 0.10702300071716309, 0.10703492164611816, 0.10704493522644043, 0.10705995559692383, 0.10706305503845215, 0.10707211494445801, 0.10707497596740723, 0.10707712173461914, 0.10708498954772949, 0.10708498954772949, 0.10709595680236816, 0.10711789131164551, 0.10713720321655273, 0.10713887214660645, 0.1071479320526123, 0.10715794563293457, 0.1071770191192627, 0.10717916488647461, 0.10721588134765625, 0.10721611976623535, 0.10721707344055176, 0.10723400115966797, 0.10723400115966797, 0.10724401473999023, 0.10724616050720215, 0.10724997520446777, 0.10726404190063477, 0.1072850227355957, 0.10729789733886719, 0.10731291770935059, 0.10733890533447266, 0.10736918449401855, 0.1073760986328125, 0.10738611221313477, 0.10738897323608398, 0.10739302635192871, 0.10739684104919434, 0.10741186141967773, 0.10741400718688965, 0.10741996765136719, 0.10742402076721191, 0.10748600959777832, 0.10752701759338379, 0.10753202438354492, 0.1075429916381836, 0.10755586624145508, 0.10756993293762207, 0.1075739860534668, 0.10757613182067871, 0.10758113861083984, 0.10758399963378906, 0.10761284828186035, 0.1076359748840332, 0.10766005516052246, 0.10766100883483887, 0.1076810359954834, 0.10768795013427734, 0.10770201683044434, 0.10770487785339355, 0.10770702362060547, 0.1077268123626709, 0.10773301124572754, 0.10773491859436035, 0.10774898529052734, 0.1077880859375, 0.10779714584350586, 0.10787105560302734, 0.10788702964782715, 0.10791015625, 0.10794806480407715, 0.10796308517456055, 0.10797691345214844, 0.10804295539855957, 0.1080617904663086, 0.10812687873840332, 0.10816383361816406, 0.10818219184875488, 0.10822701454162598, 0.10824990272521973, 0.10825800895690918, 0.10829710960388184, 0.10834693908691406, 0.10840511322021484, 0.10841989517211914, 0.10846090316772461, 0.10855484008789062, 0.10856389999389648, 0.10859107971191406, 0.10862398147583008, 0.10864806175231934, 0.10865116119384766, 0.10869193077087402, 0.10870099067687988, 0.10872197151184082, 0.1087639331817627, 0.10881900787353516, 0.10883808135986328, 0.10884594917297363, 0.10901093482971191, 0.10901379585266113, 0.10903501510620117, 0.10906195640563965, 0.10906314849853516, 0.10909700393676758, 0.10910296440124512, 0.10910797119140625, 0.1091609001159668, 0.10918998718261719, 0.10924792289733887, 0.10926389694213867, 0.10926604270935059, 0.10928082466125488, 0.10932302474975586, 0.10942888259887695, 0.10943198204040527, 0.1094350814819336, 0.10944104194641113, 0.1094520092010498, 0.10947608947753906, 0.10947704315185547, 0.1094818115234375, 0.10949110984802246, 0.10950708389282227, 0.10952901840209961, 0.10953187942504883, 0.10956001281738281, 0.10956287384033203, 0.10958600044250488, 0.10964012145996094, 0.10965108871459961, 0.10967803001403809, 0.10968780517578125, 0.1096949577331543, 0.10971212387084961, 0.10971903800964355, 0.10973787307739258, 0.10973906517028809, 0.10979294776916504, 0.10981011390686035, 0.10983085632324219, 0.10983800888061523, 0.10985612869262695, 0.1098630428314209, 0.10987305641174316, 0.10987401008605957, 0.10988306999206543, 0.10988712310791016, 0.10989212989807129, 0.1098930835723877, 0.10990095138549805, 0.10992813110351562, 0.10992884635925293, 0.10993099212646484, 0.1099400520324707, 0.10995006561279297, 0.10996508598327637, 0.1099691390991211, 0.1099708080291748, 0.10998201370239258, 0.10998797416687012, 0.11001110076904297, 0.11003589630126953, 0.11003899574279785, 0.11005902290344238, 0.11008596420288086, 0.11010193824768066, 0.11012816429138184, 0.11013102531433105, 0.11014008522033691, 0.11014199256896973, 0.11016297340393066, 0.1101830005645752, 0.11019396781921387, 0.1101992130279541, 0.11020898818969727, 0.1102139949798584, 0.11025786399841309, 0.11028003692626953, 0.11029291152954102, 0.11029887199401855, 0.11034202575683594, 0.11035394668579102, 0.11036396026611328, 0.11039090156555176, 0.11042213439941406, 0.1104280948638916, 0.11046195030212402, 0.11048603057861328, 0.11053013801574707, 0.11053299903869629, 0.11055397987365723, 0.11057615280151367, 0.1106100082397461, 0.11063504219055176, 0.1106419563293457, 0.11066102981567383, 0.1106870174407959, 0.11072587966918945, 0.11073422431945801, 0.11075401306152344, 0.11075711250305176, 0.11079597473144531, 0.11080718040466309, 0.11089491844177246, 0.11092209815979004, 0.11092400550842285, 0.11101198196411133, 0.11107611656188965, 0.11110591888427734, 0.11112618446350098, 0.1111459732055664, 0.11118602752685547, 0.11120891571044922, 0.1112368106842041, 0.11124396324157715, 0.11126208305358887, 0.11128091812133789, 0.11132097244262695, 0.11134910583496094, 0.11136198043823242, 0.11136698722839355, 0.11139106750488281, 0.11139297485351562, 0.1114048957824707, 0.11140584945678711, 0.11141514778137207, 0.11142897605895996, 0.11143302917480469, 0.11144590377807617, 0.11145782470703125, 0.1114809513092041, 0.1114809513092041, 0.11151003837585449, 0.1115109920501709, 0.11152815818786621, 0.11156892776489258, 0.11160802841186523, 0.11166691780090332, 0.1116800308227539, 0.1116800308227539, 0.11168694496154785, 0.1117100715637207, 0.11171698570251465, 0.11174583435058594, 0.111785888671875, 0.1117861270904541, 0.11180996894836426, 0.11181211471557617, 0.11181497573852539, 0.1118459701538086, 0.11184811592102051, 0.11185216903686523, 0.11185503005981445, 0.11188292503356934, 0.11189889907836914, 0.11191487312316895, 0.11191701889038086, 0.1119241714477539, 0.11193680763244629, 0.11194181442260742, 0.11194181442260742, 0.1119527816772461, 0.11197113990783691, 0.11199498176574707, 0.11201000213623047, 0.11202287673950195, 0.11203980445861816, 0.11205697059631348, 0.11208415031433105, 0.11210107803344727, 0.11211109161376953, 0.11212396621704102, 0.11212491989135742, 0.11213111877441406, 0.11214303970336914, 0.11215519905090332, 0.11217403411865234, 0.11218404769897461, 0.11222600936889648, 0.11222720146179199, 0.11223721504211426, 0.1122598648071289, 0.1122748851776123, 0.11228704452514648, 0.1123509407043457, 0.11237812042236328, 0.11240220069885254, 0.11242008209228516, 0.11244702339172363, 0.11246585845947266, 0.11248898506164551, 0.11249685287475586, 0.11252808570861816, 0.11259984970092773, 0.1126258373260498, 0.11263895034790039, 0.11266899108886719, 0.11270403861999512, 0.1127159595489502, 0.1127169132232666, 0.1127169132232666, 0.11274218559265137, 0.11275792121887207, 0.11279606819152832, 0.11280393600463867, 0.11290097236633301, 0.11291003227233887, 0.11295199394226074, 0.11296391487121582, 0.11296796798706055, 0.11301398277282715, 0.11301803588867188, 0.11303901672363281, 0.11305880546569824, 0.11309981346130371, 0.11313295364379883, 0.1131429672241211, 0.11315298080444336, 0.11324906349182129, 0.1132500171661377, 0.11337518692016602, 0.11337900161743164, 0.1135871410369873, 0.11365795135498047, 0.11370611190795898, 0.11371207237243652, 0.11382603645324707, 0.11382603645324707, 0.11392402648925781, 0.11392784118652344, 0.11396098136901855, 0.11396288871765137, 0.11397790908813477, 0.11398696899414062, 0.11400389671325684, 0.11400699615478516, 0.11404895782470703, 0.11416101455688477, 0.11416411399841309, 0.11423301696777344, 0.11423301696777344, 0.1143338680267334, 0.11438608169555664, 0.11443209648132324, 0.11458897590637207, 0.11459112167358398, 0.11463499069213867, 0.11464095115661621, 0.11467719078063965, 0.1147310733795166, 0.11476016044616699, 0.1147611141204834, 0.11479806900024414, 0.11480021476745605, 0.1148519515991211, 0.11486005783081055, 0.11496710777282715, 0.11499214172363281, 0.11499214172363281, 0.11500883102416992, 0.11502504348754883, 0.11503100395202637, 0.11510801315307617, 0.11514997482299805, 0.11537790298461914, 0.11542487144470215, 0.11562299728393555, 0.11565589904785156, 0.1157081127166748, 0.11571192741394043, 0.11577701568603516, 0.11577987670898438, 0.11578106880187988, 0.11589598655700684, 0.1159670352935791, 0.11601710319519043, 0.11612677574157715, 0.1161959171295166, 0.11620116233825684, 0.11621212959289551, 0.11627697944641113, 0.11634612083435059, 0.11649203300476074, 0.11654090881347656, 0.11659502983093262, 0.11660909652709961, 0.11670804023742676, 0.11679196357727051, 0.1168818473815918, 0.11689090728759766, 0.11690402030944824, 0.11694502830505371, 0.11703705787658691, 0.11705589294433594, 0.11706113815307617, 0.1171271800994873, 0.11715102195739746, 0.1172170639038086, 0.11724209785461426, 0.11726093292236328, 0.11726617813110352, 0.11727714538574219, 0.11733293533325195, 0.11733603477478027, 0.11735105514526367, 0.11748695373535156, 0.11797499656677246, 0.11820292472839355, 0.11824297904968262, 0.11829900741577148, 0.11841893196105957, 0.11843204498291016, 0.11846518516540527, 0.11847901344299316, 0.11848187446594238, 0.1184999942779541, 0.11881494522094727, 0.11887598037719727, 0.11896204948425293, 0.11899518966674805, 0.1190180778503418, 0.11903595924377441, 0.1190800666809082, 0.11910700798034668, 0.11911392211914062, 0.11911416053771973, 0.11913299560546875, 0.11922287940979004, 0.11923599243164062, 0.11947298049926758, 0.11950087547302246, 0.11957812309265137, 0.11970782279968262, 0.11978507041931152, 0.11998891830444336, 0.12001514434814453, 0.12026286125183105, 0.12058496475219727, 0.12061095237731934, 0.1207430362701416, 0.12112808227539062, 0.12118196487426758, 0.12125515937805176, 0.12135100364685059, 0.1213531494140625, 0.12144303321838379, 0.12146282196044922, 0.1215059757232666, 0.12151598930358887, 0.12161803245544434, 0.12170696258544922, 0.12179088592529297, 0.12185096740722656, 0.12212991714477539, 0.12227606773376465, 0.12272405624389648, 0.12316203117370605, 0.12316513061523438, 0.12335896492004395, 0.12350296974182129, 0.12358689308166504, 0.12378120422363281, 0.12378907203674316, 0.12389898300170898, 0.12480401992797852, 0.12484407424926758, 0.12542009353637695, 0.12547588348388672, 0.12552499771118164, 0.12557196617126465, 0.1257801055908203, 0.1260690689086914, 0.12624406814575195, 0.12641000747680664, 0.1264188289642334, 0.12670087814331055, 0.1267530918121338, 0.12682890892028809, 0.1276531219482422, 0.12810516357421875, 0.1284019947052002, 0.12867212295532227, 0.12895917892456055, 0.1295771598815918, 0.13099384307861328, 0.13202500343322754, 0.19588208198547363]</t>
   </si>
 </sst>
 </file>
